--- a/financials/FRT/FRT.xlsx
+++ b/financials/FRT/FRT.xlsx
@@ -12,6 +12,7 @@
     <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Dự báo tăng trưởng" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Hiệu quả thực hiện kế hoạch" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="167" formatCode="0.00\x"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,14 +49,12 @@
     </font>
     <font>
       <name val="Tahoma"/>
-      <charset val="1"/>
       <family val="2"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Tahoma"/>
-      <charset val="1"/>
       <family val="2"/>
       <i val="1"/>
       <color rgb="FF808080"/>
@@ -63,20 +62,17 @@
     </font>
     <font>
       <name val="Tahoma"/>
-      <charset val="1"/>
       <family val="2"/>
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Tahoma"/>
-      <charset val="1"/>
       <family val="2"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Tahoma"/>
-      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="10"/>
@@ -85,19 +81,44 @@
       <name val="Tahoma"/>
       <charset val="1"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <family val="2"/>
       <color rgb="FF008000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF7030A0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
       <family val="2"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <color rgb="FF7030A0"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -107,6 +128,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.7999816888943144"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -178,7 +205,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -188,35 +215,49 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="6" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="10" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="41" fontId="14" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
@@ -235,6 +276,14 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6604,14 +6653,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.77734375" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="3" customWidth="1" min="10" max="10"/>
+    <col width="17.21875" customWidth="1" min="2" max="2"/>
+    <col width="18.21875" customWidth="1" min="9" max="9"/>
+    <col width="20.5546875" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="8.88671875" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6652,6 +6702,9 @@
         <f>balance_sheet!I1</f>
         <v/>
       </c>
+      <c r="J1" s="6" t="n">
+        <v>2026</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -6665,31 +6718,31 @@
         </is>
       </c>
       <c r="C2" s="8">
-        <f>IFERROR(C$39/((C$24+B$24)/2),"n/a")</f>
+        <f>IFERROR(C$52/((C$39+B$39)/2),"n/a")</f>
         <v/>
       </c>
       <c r="D2" s="8">
-        <f>IFERROR(D$39/((D$24+C$24)/2),"n/a")</f>
+        <f>IFERROR(D$52/((D$39+C$39)/2),"n/a")</f>
         <v/>
       </c>
       <c r="E2" s="8">
-        <f>IFERROR(E$39/((E$24+D$24)/2),"n/a")</f>
+        <f>IFERROR(E$52/((E$39+D$39)/2),"n/a")</f>
         <v/>
       </c>
       <c r="F2" s="8">
-        <f>IFERROR(F$39/((F$24+E$24)/2),"n/a")</f>
+        <f>IFERROR(F$52/((F$39+E$39)/2),"n/a")</f>
         <v/>
       </c>
       <c r="G2" s="8">
-        <f>IFERROR(G$39/((G$24+F$24)/2),"n/a")</f>
+        <f>IFERROR(G$52/((G$39+F$39)/2),"n/a")</f>
         <v/>
       </c>
       <c r="H2" s="8">
-        <f>IFERROR(H$39/((H$24+G$24)/2),"n/a")</f>
+        <f>IFERROR(H$52/((H$39+G$39)/2),"n/a")</f>
         <v/>
       </c>
       <c r="I2" s="8">
-        <f>IFERROR(I$39/((I$24+H$24)/2),"n/a")</f>
+        <f>IFERROR(I$52/((I$39+H$39)/2),"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6705,31 +6758,31 @@
         </is>
       </c>
       <c r="C3" s="8">
-        <f>IFERROR(C$38/((C$25+B$25)/2),"n/a")</f>
+        <f>IFERROR(C$51/((C$31+B$31)/2),"n/a")</f>
         <v/>
       </c>
       <c r="D3" s="8">
-        <f>IFERROR(D$38/((D$25+C$25)/2),"n/a")</f>
+        <f>IFERROR(D$51/((D$31+C$31)/2),"n/a")</f>
         <v/>
       </c>
       <c r="E3" s="8">
-        <f>IFERROR(E$38/((E$25+D$25)/2),"n/a")</f>
+        <f>IFERROR(E$51/((E$31+D$31)/2),"n/a")</f>
         <v/>
       </c>
       <c r="F3" s="8">
-        <f>IFERROR(F$38/((F$25+E$25)/2),"n/a")</f>
+        <f>IFERROR(F$51/((F$31+E$31)/2),"n/a")</f>
         <v/>
       </c>
       <c r="G3" s="8">
-        <f>IFERROR(G$38/((G$25+F$25)/2),"n/a")</f>
+        <f>IFERROR(G$51/((G$31+F$31)/2),"n/a")</f>
         <v/>
       </c>
       <c r="H3" s="8">
-        <f>IFERROR(H$38/((H$25+G$25)/2),"n/a")</f>
+        <f>IFERROR(H$51/((H$31+G$31)/2),"n/a")</f>
         <v/>
       </c>
       <c r="I3" s="8">
-        <f>IFERROR(I$38/((I$25+H$25)/2),"n/a")</f>
+        <f>IFERROR(I$51/((I$31+H$31)/2),"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6745,31 +6798,35 @@
         </is>
       </c>
       <c r="C4" s="8">
-        <f>IFERROR((C$39-B$39)/ABS(B$39),"n/a")</f>
+        <f>IFERROR((C$52-B$52)/ABS(B$52),"n/a")</f>
         <v/>
       </c>
       <c r="D4" s="8">
-        <f>IFERROR((D$39-C$39)/ABS(C$39),"n/a")</f>
+        <f>IFERROR((D$52-C$52)/ABS(C$52),"n/a")</f>
         <v/>
       </c>
       <c r="E4" s="8">
-        <f>IFERROR((E$39-D$39)/ABS(D$39),"n/a")</f>
+        <f>IFERROR((E$52-D$52)/ABS(D$52),"n/a")</f>
         <v/>
       </c>
       <c r="F4" s="8">
-        <f>IFERROR((F$39-E$39)/ABS(E$39),"n/a")</f>
+        <f>IFERROR((F$52-E$52)/ABS(E$52),"n/a")</f>
         <v/>
       </c>
       <c r="G4" s="8">
-        <f>IFERROR((G$39-F$39)/ABS(F$39),"n/a")</f>
+        <f>IFERROR((G$52-F$52)/ABS(F$52),"n/a")</f>
         <v/>
       </c>
       <c r="H4" s="8">
-        <f>IFERROR((H$39-G$39)/ABS(G$39),"n/a")</f>
+        <f>IFERROR((H$52-G$52)/ABS(G$52),"n/a")</f>
         <v/>
       </c>
       <c r="I4" s="8">
-        <f>IFERROR((I$39-H$39)/ABS(H$39),"n/a")</f>
+        <f>IFERROR((I$52-H$52)/ABS(H$52),"n/a")</f>
+        <v/>
+      </c>
+      <c r="J4" s="8">
+        <f>IFERROR((J$52-I$52)/ABS(I$52),"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6785,31 +6842,35 @@
         </is>
       </c>
       <c r="C5" s="8">
-        <f>IFERROR((C$31-B$31)/ABS(B$31),"n/a")</f>
+        <f>IFERROR((C$43-B$43)/ABS(B$43),"n/a")</f>
         <v/>
       </c>
       <c r="D5" s="8">
-        <f>IFERROR((D$31-C$31)/ABS(C$31),"n/a")</f>
+        <f>IFERROR((D$43-C$43)/ABS(C$43),"n/a")</f>
         <v/>
       </c>
       <c r="E5" s="8">
-        <f>IFERROR((E$31-D$31)/ABS(D$31),"n/a")</f>
+        <f>IFERROR((E$43-D$43)/ABS(D$43),"n/a")</f>
         <v/>
       </c>
       <c r="F5" s="8">
-        <f>IFERROR((F$31-E$31)/ABS(E$31),"n/a")</f>
+        <f>IFERROR((F$43-E$43)/ABS(E$43),"n/a")</f>
         <v/>
       </c>
       <c r="G5" s="8">
-        <f>IFERROR((G$31-F$31)/ABS(F$31),"n/a")</f>
+        <f>IFERROR((G$43-F$43)/ABS(F$43),"n/a")</f>
         <v/>
       </c>
       <c r="H5" s="8">
-        <f>IFERROR((H$31-G$31)/ABS(G$31),"n/a")</f>
+        <f>IFERROR((H$43-G$43)/ABS(G$43),"n/a")</f>
         <v/>
       </c>
       <c r="I5" s="8">
-        <f>IFERROR((I$31-H$31)/ABS(H$31),"n/a")</f>
+        <f>IFERROR((I$43-H$43)/ABS(H$43),"n/a")</f>
+        <v/>
+      </c>
+      <c r="J5" s="8">
+        <f>IFERROR((J$43-I$43)/ABS(I$43),"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6820,35 +6881,35 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <f>IFERROR(B$33/B$31,"n/a")</f>
+        <f>IFERROR(B$45/B$43,"n/a")</f>
         <v/>
       </c>
       <c r="C6" s="8">
-        <f>IFERROR(C$33/C$31,"n/a")</f>
+        <f>IFERROR(C$45/C$43,"n/a")</f>
         <v/>
       </c>
       <c r="D6" s="8">
-        <f>IFERROR(D$33/D$31,"n/a")</f>
+        <f>IFERROR(D$45/D$43,"n/a")</f>
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>IFERROR(E$33/E$31,"n/a")</f>
+        <f>IFERROR(E$45/E$43,"n/a")</f>
         <v/>
       </c>
       <c r="F6" s="8">
-        <f>IFERROR(F$33/F$31,"n/a")</f>
+        <f>IFERROR(F$45/F$43,"n/a")</f>
         <v/>
       </c>
       <c r="G6" s="8">
-        <f>IFERROR(G$33/G$31,"n/a")</f>
+        <f>IFERROR(G$45/G$43,"n/a")</f>
         <v/>
       </c>
       <c r="H6" s="8">
-        <f>IFERROR(H$33/H$31,"n/a")</f>
+        <f>IFERROR(H$45/H$43,"n/a")</f>
         <v/>
       </c>
       <c r="I6" s="8">
-        <f>IFERROR(I$33/I$31,"n/a")</f>
+        <f>IFERROR(I$45/I$43,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6859,35 +6920,39 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>IFERROR(B$38/B$31,"n/a")</f>
+        <f>IFERROR(B$52/B$43,"n/a")</f>
         <v/>
       </c>
       <c r="C7" s="8">
-        <f>IFERROR(C$38/C$31,"n/a")</f>
+        <f>IFERROR(C$52/C$43,"n/a")</f>
         <v/>
       </c>
       <c r="D7" s="8">
-        <f>IFERROR(D$38/D$31,"n/a")</f>
+        <f>IFERROR(D$52/D$43,"n/a")</f>
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>IFERROR(E$38/E$31,"n/a")</f>
+        <f>IFERROR(E$52/E$43,"n/a")</f>
         <v/>
       </c>
       <c r="F7" s="8">
-        <f>IFERROR(F$38/F$31,"n/a")</f>
+        <f>IFERROR(F$52/F$43,"n/a")</f>
         <v/>
       </c>
       <c r="G7" s="8">
-        <f>IFERROR(G$38/G$31,"n/a")</f>
+        <f>IFERROR(G$52/G$43,"n/a")</f>
         <v/>
       </c>
       <c r="H7" s="8">
-        <f>IFERROR(H$38/H$31,"n/a")</f>
+        <f>IFERROR(H$52/H$43,"n/a")</f>
         <v/>
       </c>
       <c r="I7" s="8">
-        <f>IFERROR(I$38/I$31,"n/a")</f>
+        <f>IFERROR(I$52/I$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J7" s="8">
+        <f>IFERROR(J$52/J$43,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6898,35 +6963,35 @@
         </is>
       </c>
       <c r="B8" s="9">
-        <f>IFERROR((B$29+B$30)/B$24,"n/a")</f>
+        <f>IFERROR((B$34+B$36)/B$39,"n/a")</f>
         <v/>
       </c>
       <c r="C8" s="9">
-        <f>IFERROR((C$29+C$30)/C$24,"n/a")</f>
+        <f>IFERROR((C$34+C$36)/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D8" s="9">
-        <f>IFERROR((D$29+D$30)/D$24,"n/a")</f>
+        <f>IFERROR((D$34+D$36)/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E8" s="9">
-        <f>IFERROR((E$29+E$30)/E$24,"n/a")</f>
+        <f>IFERROR((E$34+E$36)/E$39,"n/a")</f>
         <v/>
       </c>
       <c r="F8" s="9">
-        <f>IFERROR((F$29+F$30)/F$24,"n/a")</f>
+        <f>IFERROR((F$34+F$36)/F$39,"n/a")</f>
         <v/>
       </c>
       <c r="G8" s="9">
-        <f>IFERROR((G$29+G$30)/G$24,"n/a")</f>
+        <f>IFERROR((G$34+G$36)/G$39,"n/a")</f>
         <v/>
       </c>
       <c r="H8" s="9">
-        <f>IFERROR((H$29+H$30)/H$24,"n/a")</f>
+        <f>IFERROR((H$34+H$36)/H$39,"n/a")</f>
         <v/>
       </c>
       <c r="I8" s="9">
-        <f>IFERROR((I$29+I$30)/I$24,"n/a")</f>
+        <f>IFERROR((I$34+I$36)/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6937,35 +7002,35 @@
         </is>
       </c>
       <c r="B9" s="9">
-        <f>IFERROR(B$30/B$24,"n/a")</f>
+        <f>IFERROR(B$36/B$39,"n/a")</f>
         <v/>
       </c>
       <c r="C9" s="9">
-        <f>IFERROR(C$30/C$24,"n/a")</f>
+        <f>IFERROR(C$36/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D9" s="9">
-        <f>IFERROR(D$30/D$24,"n/a")</f>
+        <f>IFERROR(D$36/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E9" s="9">
-        <f>IFERROR(E$30/E$24,"n/a")</f>
+        <f>IFERROR(E$36/E$39,"n/a")</f>
         <v/>
       </c>
       <c r="F9" s="9">
-        <f>IFERROR(F$30/F$24,"n/a")</f>
+        <f>IFERROR(F$36/F$39,"n/a")</f>
         <v/>
       </c>
       <c r="G9" s="9">
-        <f>IFERROR(G$30/G$24,"n/a")</f>
+        <f>IFERROR(G$36/G$39,"n/a")</f>
         <v/>
       </c>
       <c r="H9" s="9">
-        <f>IFERROR(H$30/H$24,"n/a")</f>
+        <f>IFERROR(H$36/H$39,"n/a")</f>
         <v/>
       </c>
       <c r="I9" s="9">
-        <f>IFERROR(I$30/I$24,"n/a")</f>
+        <f>IFERROR(I$36/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6976,35 +7041,35 @@
         </is>
       </c>
       <c r="B10" s="9">
-        <f>IFERROR(B$29/B$24,"n/a")</f>
+        <f>IFERROR(B$34/B$39,"n/a")</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(C$29/C$24,"n/a")</f>
+        <f>IFERROR(C$34/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>IFERROR(D$29/D$24,"n/a")</f>
+        <f>IFERROR(D$34/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E10" s="9">
-        <f>IFERROR(E$29/E$24,"n/a")</f>
+        <f>IFERROR(E$34/E$39,"n/a")</f>
         <v/>
       </c>
       <c r="F10" s="9">
-        <f>IFERROR(F$29/F$24,"n/a")</f>
+        <f>IFERROR(F$34/F$39,"n/a")</f>
         <v/>
       </c>
       <c r="G10" s="9">
-        <f>IFERROR(G$29/G$24,"n/a")</f>
+        <f>IFERROR(G$34/G$39,"n/a")</f>
         <v/>
       </c>
       <c r="H10" s="9">
-        <f>IFERROR(H$29/H$24,"n/a")</f>
+        <f>IFERROR(H$34/H$39,"n/a")</f>
         <v/>
       </c>
       <c r="I10" s="9">
-        <f>IFERROR(I$29/I$24,"n/a")</f>
+        <f>IFERROR(I$34/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7015,35 +7080,35 @@
         </is>
       </c>
       <c r="B11" s="9">
-        <f>IFERROR(B$26/B$24,"n/a")</f>
+        <f>IFERROR(B$38/B$39,"n/a")</f>
         <v/>
       </c>
       <c r="C11" s="9">
-        <f>IFERROR(C$26/C$24,"n/a")</f>
+        <f>IFERROR(C$38/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D11" s="9">
-        <f>IFERROR(D$26/D$24,"n/a")</f>
+        <f>IFERROR(D$38/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E11" s="9">
-        <f>IFERROR(E$26/E$24,"n/a")</f>
+        <f>IFERROR(E$38/E$39,"n/a")</f>
         <v/>
       </c>
       <c r="F11" s="9">
-        <f>IFERROR(F$26/F$24,"n/a")</f>
+        <f>IFERROR(F$38/F$39,"n/a")</f>
         <v/>
       </c>
       <c r="G11" s="9">
-        <f>IFERROR(G$26/G$24,"n/a")</f>
+        <f>IFERROR(G$38/G$39,"n/a")</f>
         <v/>
       </c>
       <c r="H11" s="9">
-        <f>IFERROR(H$26/H$24,"n/a")</f>
+        <f>IFERROR(H$38/H$39,"n/a")</f>
         <v/>
       </c>
       <c r="I11" s="9">
-        <f>IFERROR(I$26/I$24,"n/a")</f>
+        <f>IFERROR(I$38/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7054,35 +7119,35 @@
         </is>
       </c>
       <c r="B12" s="9">
-        <f>IFERROR(B$28/B$24,"n/a")</f>
+        <f>IFERROR(B$37/B$39,"n/a")</f>
         <v/>
       </c>
       <c r="C12" s="9">
-        <f>IFERROR(C$28/C$24,"n/a")</f>
+        <f>IFERROR(C$37/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D12" s="9">
-        <f>IFERROR(D$28/D$24,"n/a")</f>
+        <f>IFERROR(D$37/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E12" s="9">
-        <f>IFERROR(E$28/E$24,"n/a")</f>
+        <f>IFERROR(E$37/E$39,"n/a")</f>
         <v/>
       </c>
       <c r="F12" s="9">
-        <f>IFERROR(F$28/F$24,"n/a")</f>
+        <f>IFERROR(F$37/F$39,"n/a")</f>
         <v/>
       </c>
       <c r="G12" s="9">
-        <f>IFERROR(G$28/G$24,"n/a")</f>
+        <f>IFERROR(G$37/G$39,"n/a")</f>
         <v/>
       </c>
       <c r="H12" s="9">
-        <f>IFERROR(H$28/H$24,"n/a")</f>
+        <f>IFERROR(H$37/H$39,"n/a")</f>
         <v/>
       </c>
       <c r="I12" s="9">
-        <f>IFERROR(I$28/I$24,"n/a")</f>
+        <f>IFERROR(I$37/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7093,35 +7158,35 @@
         </is>
       </c>
       <c r="B13" s="9">
-        <f>IFERROR(B$27/B$24,"n/a")</f>
+        <f>IFERROR(B$35/B$39,"n/a")</f>
         <v/>
       </c>
       <c r="C13" s="9">
-        <f>IFERROR(C$27/C$24,"n/a")</f>
+        <f>IFERROR(C$35/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D13" s="9">
-        <f>IFERROR(D$27/D$24,"n/a")</f>
+        <f>IFERROR(D$35/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E13" s="9">
-        <f>IFERROR(E$27/E$24,"n/a")</f>
+        <f>IFERROR(E$35/E$39,"n/a")</f>
         <v/>
       </c>
       <c r="F13" s="9">
-        <f>IFERROR(F$27/F$24,"n/a")</f>
+        <f>IFERROR(F$35/F$39,"n/a")</f>
         <v/>
       </c>
       <c r="G13" s="9">
-        <f>IFERROR(G$27/G$24,"n/a")</f>
+        <f>IFERROR(G$35/G$39,"n/a")</f>
         <v/>
       </c>
       <c r="H13" s="9">
-        <f>IFERROR(H$27/H$24,"n/a")</f>
+        <f>IFERROR(H$35/H$39,"n/a")</f>
         <v/>
       </c>
       <c r="I13" s="9">
-        <f>IFERROR(I$27/I$24,"n/a")</f>
+        <f>IFERROR(I$35/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7132,35 +7197,35 @@
         </is>
       </c>
       <c r="B14" s="8">
-        <f>IFERROR((ABS(B$34)+ABS(B$35))/B$33,"n/a")</f>
+        <f>IFERROR((ABS(B$46)+ABS(B$47))/B$45,"n/a")</f>
         <v/>
       </c>
       <c r="C14" s="8">
-        <f>IFERROR((ABS(C$34)+ABS(C$35))/C$33,"n/a")</f>
+        <f>IFERROR((ABS(C$46)+ABS(C$47))/C$45,"n/a")</f>
         <v/>
       </c>
       <c r="D14" s="8">
-        <f>IFERROR((ABS(D$34)+ABS(D$35))/D$33,"n/a")</f>
+        <f>IFERROR((ABS(D$46)+ABS(D$47))/D$45,"n/a")</f>
         <v/>
       </c>
       <c r="E14" s="8">
-        <f>IFERROR((ABS(E$34)+ABS(E$35))/E$33,"n/a")</f>
+        <f>IFERROR((ABS(E$46)+ABS(E$47))/E$45,"n/a")</f>
         <v/>
       </c>
       <c r="F14" s="8">
-        <f>IFERROR((ABS(F$34)+ABS(F$35))/F$33,"n/a")</f>
+        <f>IFERROR((ABS(F$46)+ABS(F$47))/F$45,"n/a")</f>
         <v/>
       </c>
       <c r="G14" s="8">
-        <f>IFERROR((ABS(G$34)+ABS(G$35))/G$33,"n/a")</f>
+        <f>IFERROR((ABS(G$46)+ABS(G$47))/G$45,"n/a")</f>
         <v/>
       </c>
       <c r="H14" s="8">
-        <f>IFERROR((ABS(H$34)+ABS(H$35))/H$33,"n/a")</f>
+        <f>IFERROR((ABS(H$46)+ABS(H$47))/H$45,"n/a")</f>
         <v/>
       </c>
       <c r="I14" s="8">
-        <f>IFERROR((ABS(I$34)+ABS(I$35))/I$33,"n/a")</f>
+        <f>IFERROR((ABS(I$46)+ABS(I$47))/I$45,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7171,35 +7236,35 @@
         </is>
       </c>
       <c r="B15" s="8">
-        <f>IFERROR(ABS(B$37)/B$36,"n/a")</f>
+        <f>IFERROR(ABS(B$49)/B$48,"n/a")</f>
         <v/>
       </c>
       <c r="C15" s="8">
-        <f>IFERROR(ABS(C$37)/C$36,"n/a")</f>
+        <f>IFERROR(ABS(C$49)/C$48,"n/a")</f>
         <v/>
       </c>
       <c r="D15" s="8">
-        <f>IFERROR(ABS(D$37)/D$36,"n/a")</f>
+        <f>IFERROR(ABS(D$49)/D$48,"n/a")</f>
         <v/>
       </c>
       <c r="E15" s="8">
-        <f>IFERROR(ABS(E$37)/E$36,"n/a")</f>
+        <f>IFERROR(ABS(E$49)/E$48,"n/a")</f>
         <v/>
       </c>
       <c r="F15" s="8">
-        <f>IFERROR(ABS(F$37)/F$36,"n/a")</f>
+        <f>IFERROR(ABS(F$49)/F$48,"n/a")</f>
         <v/>
       </c>
       <c r="G15" s="8">
-        <f>IFERROR(ABS(G$37)/G$36,"n/a")</f>
+        <f>IFERROR(ABS(G$49)/G$48,"n/a")</f>
         <v/>
       </c>
       <c r="H15" s="8">
-        <f>IFERROR(ABS(H$37)/H$36,"n/a")</f>
+        <f>IFERROR(ABS(H$49)/H$48,"n/a")</f>
         <v/>
       </c>
       <c r="I15" s="8">
-        <f>IFERROR(ABS(I$37)/I$36,"n/a")</f>
+        <f>IFERROR(ABS(I$49)/I$48,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7215,31 +7280,31 @@
         </is>
       </c>
       <c r="C16" s="12">
-        <f>IFERROR(((C$41+B$41)/2)/ABS(C$32)*365,"n/a")</f>
+        <f>IFERROR(((C$33+B$33)/2)/ABS(C$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="D16" s="12">
-        <f>IFERROR(((D$41+C$41)/2)/ABS(D$32)*365,"n/a")</f>
+        <f>IFERROR(((D$33+C$33)/2)/ABS(D$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="E16" s="12">
-        <f>IFERROR(((E$41+D$41)/2)/ABS(E$32)*365,"n/a")</f>
+        <f>IFERROR(((E$33+D$33)/2)/ABS(E$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="F16" s="12">
-        <f>IFERROR(((F$41+E$41)/2)/ABS(F$32)*365,"n/a")</f>
+        <f>IFERROR(((F$33+E$33)/2)/ABS(F$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="G16" s="12">
-        <f>IFERROR(((G$41+F$41)/2)/ABS(G$32)*365,"n/a")</f>
+        <f>IFERROR(((G$33+F$33)/2)/ABS(G$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="H16" s="12">
-        <f>IFERROR(((H$41+G$41)/2)/ABS(H$32)*365,"n/a")</f>
+        <f>IFERROR(((H$33+G$33)/2)/ABS(H$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="I16" s="12">
-        <f>IFERROR(((I$41+H$41)/2)/ABS(I$32)*365,"n/a")</f>
+        <f>IFERROR(((I$33+H$33)/2)/ABS(I$44)*365,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7255,31 +7320,31 @@
         </is>
       </c>
       <c r="C17" s="12">
-        <f>IFERROR(((C$40+B$40)/2)/C$31*365,"n/a")</f>
+        <f>IFERROR(((C$27+B$27)/2)/C$43*365,"n/a")</f>
         <v/>
       </c>
       <c r="D17" s="12">
-        <f>IFERROR(((D$40+C$40)/2)/D$31*365,"n/a")</f>
+        <f>IFERROR(((D$27+C$27)/2)/D$43*365,"n/a")</f>
         <v/>
       </c>
       <c r="E17" s="12">
-        <f>IFERROR(((E$40+D$40)/2)/E$31*365,"n/a")</f>
+        <f>IFERROR(((E$27+D$27)/2)/E$43*365,"n/a")</f>
         <v/>
       </c>
       <c r="F17" s="12">
-        <f>IFERROR(((F$40+E$40)/2)/F$31*365,"n/a")</f>
+        <f>IFERROR(((F$27+E$27)/2)/F$43*365,"n/a")</f>
         <v/>
       </c>
       <c r="G17" s="12">
-        <f>IFERROR(((G$40+F$40)/2)/G$31*365,"n/a")</f>
+        <f>IFERROR(((G$27+F$27)/2)/G$43*365,"n/a")</f>
         <v/>
       </c>
       <c r="H17" s="12">
-        <f>IFERROR(((H$40+G$40)/2)/H$31*365,"n/a")</f>
+        <f>IFERROR(((H$27+G$27)/2)/H$43*365,"n/a")</f>
         <v/>
       </c>
       <c r="I17" s="12">
-        <f>IFERROR(((I$40+H$40)/2)/I$31*365,"n/a")</f>
+        <f>IFERROR(((I$27+H$27)/2)/I$43*365,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7295,31 +7360,31 @@
         </is>
       </c>
       <c r="C18" s="12">
-        <f>IFERROR(((C$42+B$42)/2)/ABS(C$32)*365,"n/a")</f>
+        <f>IFERROR(((C$28+B$28)/2)/ABS(C$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="D18" s="12">
-        <f>IFERROR(((D$42+C$42)/2)/ABS(D$32)*365,"n/a")</f>
+        <f>IFERROR(((D$28+C$28)/2)/ABS(D$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="E18" s="12">
-        <f>IFERROR(((E$42+D$42)/2)/ABS(E$32)*365,"n/a")</f>
+        <f>IFERROR(((E$28+D$28)/2)/ABS(E$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="F18" s="12">
-        <f>IFERROR(((F$42+E$42)/2)/ABS(F$32)*365,"n/a")</f>
+        <f>IFERROR(((F$28+E$28)/2)/ABS(F$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="G18" s="12">
-        <f>IFERROR(((G$42+F$42)/2)/ABS(G$32)*365,"n/a")</f>
+        <f>IFERROR(((G$28+F$28)/2)/ABS(G$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="H18" s="12">
-        <f>IFERROR(((H$42+G$42)/2)/ABS(H$32)*365,"n/a")</f>
+        <f>IFERROR(((H$28+G$28)/2)/ABS(H$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="I18" s="12">
-        <f>IFERROR(((I$42+H$42)/2)/ABS(I$32)*365,"n/a")</f>
+        <f>IFERROR(((I$28+H$28)/2)/ABS(I$44)*365,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7330,35 +7395,35 @@
         </is>
       </c>
       <c r="B19" s="8">
-        <f>IFERROR(B$43/B$25,"n/a")</f>
+        <f>IFERROR(B$26/B$31,"n/a")</f>
         <v/>
       </c>
       <c r="C19" s="8">
-        <f>IFERROR(C$43/C$25,"n/a")</f>
+        <f>IFERROR(C$26/C$31,"n/a")</f>
         <v/>
       </c>
       <c r="D19" s="8">
-        <f>IFERROR(D$43/D$25,"n/a")</f>
+        <f>IFERROR(D$26/D$31,"n/a")</f>
         <v/>
       </c>
       <c r="E19" s="8">
-        <f>IFERROR(E$43/E$25,"n/a")</f>
+        <f>IFERROR(E$26/E$31,"n/a")</f>
         <v/>
       </c>
       <c r="F19" s="8">
-        <f>IFERROR(F$43/F$25,"n/a")</f>
+        <f>IFERROR(F$26/F$31,"n/a")</f>
         <v/>
       </c>
       <c r="G19" s="8">
-        <f>IFERROR(G$43/G$25,"n/a")</f>
+        <f>IFERROR(G$26/G$31,"n/a")</f>
         <v/>
       </c>
       <c r="H19" s="8">
-        <f>IFERROR(H$43/H$25,"n/a")</f>
+        <f>IFERROR(H$26/H$31,"n/a")</f>
         <v/>
       </c>
       <c r="I19" s="8">
-        <f>IFERROR(I$43/I$25,"n/a")</f>
+        <f>IFERROR(I$26/I$31,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7369,35 +7434,35 @@
         </is>
       </c>
       <c r="B20" s="8">
-        <f>IFERROR(B$42/B$25,"n/a")</f>
+        <f>IFERROR(B$28/B$31,"n/a")</f>
         <v/>
       </c>
       <c r="C20" s="8">
-        <f>IFERROR(C$42/C$25,"n/a")</f>
+        <f>IFERROR(C$28/C$31,"n/a")</f>
         <v/>
       </c>
       <c r="D20" s="8">
-        <f>IFERROR(D$42/D$25,"n/a")</f>
+        <f>IFERROR(D$28/D$31,"n/a")</f>
         <v/>
       </c>
       <c r="E20" s="8">
-        <f>IFERROR(E$42/E$25,"n/a")</f>
+        <f>IFERROR(E$28/E$31,"n/a")</f>
         <v/>
       </c>
       <c r="F20" s="8">
-        <f>IFERROR(F$42/F$25,"n/a")</f>
+        <f>IFERROR(F$28/F$31,"n/a")</f>
         <v/>
       </c>
       <c r="G20" s="8">
-        <f>IFERROR(G$42/G$25,"n/a")</f>
+        <f>IFERROR(G$28/G$31,"n/a")</f>
         <v/>
       </c>
       <c r="H20" s="8">
-        <f>IFERROR(H$42/H$25,"n/a")</f>
+        <f>IFERROR(H$28/H$31,"n/a")</f>
         <v/>
       </c>
       <c r="I20" s="8">
-        <f>IFERROR(I$42/I$25,"n/a")</f>
+        <f>IFERROR(I$28/I$31,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7459,1903 +7524,2147 @@
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
+          <t>CĐKT</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="16" t="n"/>
+      <c r="G24" s="16" t="n"/>
+      <c r="H24" s="16" t="n"/>
+      <c r="I24" s="16" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="17" t="inlineStr">
         <is>
+          <t>Tài sản</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="16" t="n"/>
+      <c r="G25" s="16" t="n"/>
+      <c r="H25" s="16" t="n"/>
+      <c r="I25" s="16" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>Tiền và tương đương tiền</t>
+        </is>
+      </c>
+      <c r="B26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>Phải thu khách hàng</t>
+        </is>
+      </c>
+      <c r="B27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>Hàng tồn kho, ròng</t>
+        </is>
+      </c>
+      <c r="B28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>TÀI SẢN NGẮN HẠN</t>
+        </is>
+      </c>
+      <c r="B29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>GTCL tài sản cố định vô hình</t>
+        </is>
+      </c>
+      <c r="B30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
           <t>TỔNG CỘNG TÀI SẢN</t>
         </is>
       </c>
-      <c r="B25" s="18">
+      <c r="B31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C25" s="18">
+      <c r="C31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D25" s="18">
+      <c r="D31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E25" s="18">
+      <c r="E31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F25" s="18">
+      <c r="F31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G25" s="18">
+      <c r="G31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H25" s="18">
+      <c r="H31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I25" s="18">
+      <c r="I31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>Nguồn vốn</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="n"/>
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="19" t="n"/>
+      <c r="E32" s="19" t="n"/>
+      <c r="F32" s="19" t="n"/>
+      <c r="G32" s="19" t="n"/>
+      <c r="H32" s="19" t="n"/>
+      <c r="I32" s="19" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>Phải trả người bán</t>
+        </is>
+      </c>
+      <c r="B33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>Vay ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>Nợ ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>Vay dài hạn</t>
+        </is>
+      </c>
+      <c r="B36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>Nợ dài hạn</t>
+        </is>
+      </c>
+      <c r="B37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>NỢ PHẢI TRẢ</t>
         </is>
       </c>
-      <c r="B26" s="18">
+      <c r="B38" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C26" s="18">
+      <c r="C38" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D26" s="18">
+      <c r="D38" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E26" s="18">
+      <c r="E38" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F26" s="18">
+      <c r="F38" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G26" s="18">
+      <c r="G38" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H26" s="18">
+      <c r="H38" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I26" s="18">
+      <c r="I38" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>Nợ ngắn hạn</t>
-        </is>
-      </c>
-      <c r="B27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>Nợ dài hạn</t>
-        </is>
-      </c>
-      <c r="B28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>Vay ngắn hạn</t>
-        </is>
-      </c>
-      <c r="B29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>Vay dài hạn</t>
-        </is>
-      </c>
-      <c r="B30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="20" t="n">
+        <v>6096125000000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>Tăng VCSH/LN cổ đông cty mẹ</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="n"/>
+      <c r="C40" s="23">
+        <f>(C39-B39)/C52</f>
+        <v/>
+      </c>
+      <c r="D40" s="23">
+        <f>(D39-C39)/D52</f>
+        <v/>
+      </c>
+      <c r="E40" s="23">
+        <f>(E39-D39)/E52</f>
+        <v/>
+      </c>
+      <c r="F40" s="23">
+        <f>(F39-E39)/F52</f>
+        <v/>
+      </c>
+      <c r="G40" s="23">
+        <f>(G39-F39)/G52</f>
+        <v/>
+      </c>
+      <c r="H40" s="23">
+        <f>(H39-G39)/H52</f>
+        <v/>
+      </c>
+      <c r="I40" s="23">
+        <f>(I39-H39)/I52</f>
+        <v/>
+      </c>
+      <c r="J40" s="24" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>Lợi ích của cổ đông thiểu số</t>
+        </is>
+      </c>
+      <c r="B41" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C41" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I41" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J41" s="24" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>Kết quả hoạt động kinh doanh</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="n"/>
+      <c r="C42" s="19" t="n"/>
+      <c r="D42" s="19" t="n"/>
+      <c r="E42" s="19" t="n"/>
+      <c r="F42" s="19" t="n"/>
+      <c r="G42" s="19" t="n"/>
+      <c r="H42" s="19" t="n"/>
+      <c r="I42" s="19" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>Doanh thu thuần</t>
         </is>
       </c>
-      <c r="B31" s="18">
+      <c r="B43" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C31" s="18">
+      <c r="C43" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D31" s="18">
+      <c r="D43" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E31" s="18">
+      <c r="E43" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F31" s="18">
+      <c r="F43" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G31" s="18">
+      <c r="G43" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H31" s="18">
+      <c r="H43" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I31" s="18">
+      <c r="I43" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="J43" s="20" t="n">
+        <v>59500000000000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>Giá vốn hàng bán</t>
         </is>
       </c>
-      <c r="B32" s="18">
+      <c r="B44" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C32" s="18">
+      <c r="C44" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D32" s="18">
+      <c r="D44" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E32" s="18">
+      <c r="E44" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F32" s="18">
+      <c r="F44" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G32" s="18">
+      <c r="G44" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H32" s="18">
+      <c r="H44" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I32" s="18">
+      <c r="I44" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>Lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B33" s="18">
+      <c r="B45" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C33" s="18">
+      <c r="C45" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D33" s="18">
+      <c r="D45" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E33" s="18">
+      <c r="E45" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F33" s="18">
+      <c r="F45" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G33" s="18">
+      <c r="G45" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H33" s="18">
+      <c r="H45" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I33" s="18">
+      <c r="I45" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="18" t="inlineStr">
         <is>
           <t>Chi phí bán hàng</t>
         </is>
       </c>
-      <c r="B34" s="18">
+      <c r="B46" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C34" s="18">
+      <c r="C46" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D34" s="18">
+      <c r="D46" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E34" s="18">
+      <c r="E46" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F34" s="18">
+      <c r="F46" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G34" s="18">
+      <c r="G46" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H34" s="18">
+      <c r="H46" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I34" s="18">
+      <c r="I46" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>Chi phí quản lý doanh nghiệp</t>
         </is>
       </c>
-      <c r="B35" s="18">
+      <c r="B47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C35" s="18">
+      <c r="C47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D35" s="18">
+      <c r="D47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E35" s="18">
+      <c r="E47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F35" s="18">
+      <c r="F47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G35" s="18">
+      <c r="G47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H35" s="18">
+      <c r="H47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I35" s="18">
+      <c r="I47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="18" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) từ hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B36" s="18">
+      <c r="B48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C36" s="18">
+      <c r="C48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D36" s="18">
+      <c r="D48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E36" s="18">
+      <c r="E48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F36" s="18">
+      <c r="F48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G36" s="18">
+      <c r="G48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H36" s="18">
+      <c r="H48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I36" s="18">
+      <c r="I48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="18" t="inlineStr">
         <is>
           <t>Chi phí lãi vay</t>
         </is>
       </c>
-      <c r="B37" s="18">
+      <c r="B49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C37" s="18">
+      <c r="C49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D37" s="18">
+      <c r="D49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E37" s="18">
+      <c r="E49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F37" s="18">
+      <c r="F49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G37" s="18">
+      <c r="G49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H37" s="18">
+      <c r="H49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I37" s="18">
+      <c r="I49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="25" t="inlineStr">
+        <is>
+          <t>Lãi/(lỗ) trước thuế</t>
+        </is>
+      </c>
+      <c r="B50" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C50" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D50" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E50" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F50" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I50" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J50" s="20" t="n">
+        <v>1550000000000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="18" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) thuần sau thuế</t>
         </is>
       </c>
-      <c r="B38" s="18">
+      <c r="B51" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C38" s="18">
+      <c r="C51" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D38" s="18">
+      <c r="D51" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E38" s="18">
+      <c r="E51" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F38" s="18">
+      <c r="F51" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G38" s="18">
+      <c r="G51" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H38" s="18">
+      <c r="H51" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I38" s="18">
+      <c r="I51" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t>Lợi nhuận của Cổ đông của Công ty mẹ</t>
         </is>
       </c>
-      <c r="B39" s="18">
+      <c r="B52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C39" s="18">
+      <c r="C52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D39" s="18">
+      <c r="D52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E39" s="18">
+      <c r="E52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F39" s="18">
+      <c r="F52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G39" s="18">
+      <c r="G52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H39" s="18">
+      <c r="H52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I39" s="18">
+      <c r="I52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>Phải thu khách hàng</t>
-        </is>
-      </c>
-      <c r="B40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="17" t="inlineStr">
-        <is>
-          <t>Phải trả người bán</t>
-        </is>
-      </c>
-      <c r="B41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>Hàng tồn kho, ròng</t>
-        </is>
-      </c>
-      <c r="B42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>Tiền và tương đương tiền</t>
-        </is>
-      </c>
-      <c r="B43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="17" t="inlineStr">
-        <is>
-          <t>TÀI SẢN NGẮN HẠN</t>
-        </is>
-      </c>
-      <c r="B44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="17" t="inlineStr">
-        <is>
-          <t>GTCL tài sản cố định vô hình</t>
-        </is>
-      </c>
-      <c r="B45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="17" t="inlineStr">
+      <c r="J52" s="20">
+        <f>J50*0.65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="18" t="inlineStr">
+        <is>
+          <t>LN cổ đông cty mẹ/ LN trước thuế</t>
+        </is>
+      </c>
+      <c r="B53" s="26">
+        <f>B52/B50</f>
+        <v/>
+      </c>
+      <c r="C53" s="26">
+        <f>C52/C50</f>
+        <v/>
+      </c>
+      <c r="D53" s="26">
+        <f>D52/D50</f>
+        <v/>
+      </c>
+      <c r="E53" s="26">
+        <f>E52/E50</f>
+        <v/>
+      </c>
+      <c r="F53" s="26">
+        <f>F52/F50</f>
+        <v/>
+      </c>
+      <c r="G53" s="26">
+        <f>G52/G50</f>
+        <v/>
+      </c>
+      <c r="H53" s="26">
+        <f>H52/H50</f>
+        <v/>
+      </c>
+      <c r="I53" s="26">
+        <f>I52/I50</f>
+        <v/>
+      </c>
+      <c r="J53" s="27" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>Lưu chuyển tiền tệ</t>
+        </is>
+      </c>
+      <c r="B54" s="19" t="n"/>
+      <c r="C54" s="19" t="n"/>
+      <c r="D54" s="19" t="n"/>
+      <c r="E54" s="19" t="n"/>
+      <c r="F54" s="19" t="n"/>
+      <c r="G54" s="19" t="n"/>
+      <c r="H54" s="19" t="n"/>
+      <c r="I54" s="19" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="18" t="inlineStr">
         <is>
           <t>Khấu hao TSCĐ và BĐSĐT</t>
         </is>
       </c>
-      <c r="B46" s="18">
+      <c r="B55" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(B$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C46" s="18">
+      <c r="C55" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(C$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D46" s="18">
+      <c r="D55" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(D$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E46" s="18">
+      <c r="E55" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(E$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F46" s="18">
+      <c r="F55" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(F$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G46" s="18">
+      <c r="G55" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(G$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H46" s="18">
+      <c r="H55" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(H$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I46" s="18">
+      <c r="I55" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(I$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="17" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="18" t="inlineStr">
         <is>
           <t>Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác</t>
         </is>
       </c>
-      <c r="B47" s="18">
+      <c r="B56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(B$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C47" s="18">
+      <c r="C56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(C$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D47" s="18">
+      <c r="D56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(D$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E47" s="18">
+      <c r="E56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(E$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F47" s="18">
+      <c r="F56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(F$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G47" s="18">
+      <c r="G56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(G$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H47" s="18">
+      <c r="H56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(H$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I47" s="18">
+      <c r="I56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(I$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="17" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="18" t="inlineStr">
         <is>
           <t>Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh</t>
         </is>
       </c>
-      <c r="B48" s="18">
+      <c r="B57" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(B$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C48" s="18">
+      <c r="C57" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(C$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D48" s="18">
+      <c r="D57" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(D$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E48" s="18">
+      <c r="E57" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(E$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F48" s="18">
+      <c r="F57" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(F$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G48" s="18">
+      <c r="G57" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(G$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H48" s="18">
+      <c r="H57" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(H$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I48" s="18">
+      <c r="I57" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(I$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" s="19" t="inlineStr">
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61">
+      <c r="A61" s="28" t="inlineStr">
         <is>
           <t>CHỈ SỐ THÊM</t>
         </is>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B61" s="16" t="n">
         <v>2018</v>
       </c>
-      <c r="C52" s="6" t="n">
+      <c r="C61" s="16" t="n">
         <v>2019</v>
       </c>
-      <c r="D52" s="6" t="n">
+      <c r="D61" s="16" t="n">
         <v>2020</v>
       </c>
-      <c r="E52" s="6" t="n">
+      <c r="E61" s="16" t="n">
         <v>2021</v>
       </c>
-      <c r="F52" s="6" t="n">
+      <c r="F61" s="16" t="n">
         <v>2022</v>
       </c>
-      <c r="G52" s="6" t="n">
+      <c r="G61" s="16" t="n">
         <v>2023</v>
       </c>
-      <c r="H52" s="6" t="n">
+      <c r="H61" s="16" t="n">
         <v>2024</v>
       </c>
-      <c r="I52" s="6" t="n">
+      <c r="I61" s="16" t="n">
         <v>2025</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="19" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="28" t="inlineStr">
         <is>
           <t>Khả năng sinh lời &amp; hiệu quả sử dụng vốn</t>
         </is>
       </c>
-      <c r="B53" s="20" t="n"/>
-      <c r="C53" s="20" t="n"/>
-      <c r="D53" s="20" t="n"/>
-      <c r="E53" s="20" t="n"/>
-      <c r="F53" s="20" t="n"/>
-      <c r="G53" s="20" t="n"/>
-      <c r="H53" s="20" t="n"/>
-      <c r="I53" s="20" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="20" t="inlineStr">
+      <c r="B62" s="29" t="n"/>
+      <c r="C62" s="29" t="n"/>
+      <c r="D62" s="29" t="n"/>
+      <c r="E62" s="29" t="n"/>
+      <c r="F62" s="29" t="n"/>
+      <c r="G62" s="29" t="n"/>
+      <c r="H62" s="29" t="n"/>
+      <c r="I62" s="29" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="29" t="inlineStr">
         <is>
           <t>ROCE</t>
         </is>
       </c>
-      <c r="B54" s="21">
-        <f>IFERROR(B$56/(B$25-B$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C54" s="21">
-        <f>IFERROR(C$56/(C$25-C$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D54" s="21">
-        <f>IFERROR(D$56/(D$25-D$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E54" s="21">
-        <f>IFERROR(E$56/(E$25-E$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F54" s="21">
-        <f>IFERROR(F$56/(F$25-F$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G54" s="21">
-        <f>IFERROR(G$56/(G$25-G$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H54" s="21">
-        <f>IFERROR(H$56/(H$25-H$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I54" s="21">
-        <f>IFERROR(I$56/(I$25-I$27),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="20" t="inlineStr">
+      <c r="B63" s="30">
+        <f>IFERROR(B$65/(B$31-B$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C63" s="30">
+        <f>IFERROR(C$65/(C$31-C$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D63" s="30">
+        <f>IFERROR(D$65/(D$31-D$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E63" s="30">
+        <f>IFERROR(E$65/(E$31-E$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F63" s="30">
+        <f>IFERROR(F$65/(F$31-F$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G63" s="30">
+        <f>IFERROR(G$65/(G$31-G$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H63" s="30">
+        <f>IFERROR(H$65/(H$31-H$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I63" s="30">
+        <f>IFERROR(I$65/(I$31-I$35),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="29" t="inlineStr">
         <is>
           <t>CROIC</t>
         </is>
       </c>
-      <c r="B55" s="21">
-        <f>IFERROR(B$60/(B$25-B$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C55" s="21">
-        <f>IFERROR(C$60/(C$25-C$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D55" s="21">
-        <f>IFERROR(D$60/(D$25-D$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E55" s="21">
-        <f>IFERROR(E$60/(E$25-E$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F55" s="21">
-        <f>IFERROR(F$60/(F$25-F$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G55" s="21">
-        <f>IFERROR(G$60/(G$25-G$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H55" s="21">
-        <f>IFERROR(H$60/(H$25-H$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I55" s="21">
-        <f>IFERROR(I$60/(I$25-I$27),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="20" t="inlineStr">
+      <c r="B64" s="30">
+        <f>IFERROR(B$69/(B$31-B$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C64" s="30">
+        <f>IFERROR(C$69/(C$31-C$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D64" s="30">
+        <f>IFERROR(D$69/(D$31-D$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E64" s="30">
+        <f>IFERROR(E$69/(E$31-E$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F64" s="30">
+        <f>IFERROR(F$69/(F$31-F$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G64" s="30">
+        <f>IFERROR(G$69/(G$31-G$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H64" s="30">
+        <f>IFERROR(H$69/(H$31-H$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I64" s="30">
+        <f>IFERROR(I$69/(I$31-I$35),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="29" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B56" s="22">
-        <f>IFERROR(B$36+ABS(B$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C56" s="22">
-        <f>IFERROR(C$36+ABS(C$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D56" s="22">
-        <f>IFERROR(D$36+ABS(D$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E56" s="22">
-        <f>IFERROR(E$36+ABS(E$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F56" s="22">
-        <f>IFERROR(F$36+ABS(F$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G56" s="22">
-        <f>IFERROR(G$36+ABS(G$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H56" s="22">
-        <f>IFERROR(H$36+ABS(H$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I56" s="22">
-        <f>IFERROR(I$36+ABS(I$37),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="20" t="inlineStr">
+      <c r="B65" s="31">
+        <f>IFERROR(B$48+ABS(B$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C65" s="31">
+        <f>IFERROR(C$48+ABS(C$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D65" s="31">
+        <f>IFERROR(D$48+ABS(D$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E65" s="31">
+        <f>IFERROR(E$48+ABS(E$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F65" s="31">
+        <f>IFERROR(F$48+ABS(F$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G65" s="31">
+        <f>IFERROR(G$48+ABS(G$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H65" s="31">
+        <f>IFERROR(H$48+ABS(H$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I65" s="31">
+        <f>IFERROR(I$48+ABS(I$49),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
         <is>
           <t>EBIT/DT</t>
         </is>
       </c>
-      <c r="B57" s="21">
-        <f>IFERROR(B$56/B$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C57" s="21">
-        <f>IFERROR(C$56/C$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D57" s="21">
-        <f>IFERROR(D$56/D$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E57" s="21">
-        <f>IFERROR(E$56/E$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F57" s="21">
-        <f>IFERROR(F$56/F$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G57" s="21">
-        <f>IFERROR(G$56/G$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H57" s="21">
-        <f>IFERROR(H$56/H$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I57" s="21">
-        <f>IFERROR(I$56/I$31,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="20" t="inlineStr">
+      <c r="B66" s="30">
+        <f>IFERROR(B$65/B$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C66" s="30">
+        <f>IFERROR(C$65/C$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D66" s="30">
+        <f>IFERROR(D$65/D$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E66" s="30">
+        <f>IFERROR(E$65/E$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F66" s="30">
+        <f>IFERROR(F$65/F$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G66" s="30">
+        <f>IFERROR(G$65/G$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H66" s="30">
+        <f>IFERROR(H$65/H$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I66" s="30">
+        <f>IFERROR(I$65/I$43,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
         <is>
           <t>DT/TS</t>
         </is>
       </c>
-      <c r="B58" s="21">
-        <f>IFERROR(B$31/B$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C58" s="21">
-        <f>IFERROR(C$31/C$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D58" s="21">
-        <f>IFERROR(D$31/D$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E58" s="21">
-        <f>IFERROR(E$31/E$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F58" s="21">
-        <f>IFERROR(F$31/F$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G58" s="21">
-        <f>IFERROR(G$31/G$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H58" s="21">
-        <f>IFERROR(H$31/H$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I58" s="21">
-        <f>IFERROR(I$31/I$25,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="19" t="inlineStr">
+      <c r="B67" s="30">
+        <f>IFERROR(B$43/B$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C67" s="30">
+        <f>IFERROR(C$43/C$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D67" s="30">
+        <f>IFERROR(D$43/D$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E67" s="30">
+        <f>IFERROR(E$43/E$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F67" s="30">
+        <f>IFERROR(F$43/F$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G67" s="30">
+        <f>IFERROR(G$43/G$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H67" s="30">
+        <f>IFERROR(H$43/H$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I67" s="30">
+        <f>IFERROR(I$43/I$31,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="28" t="inlineStr">
         <is>
           <t>Dòng tiền &amp; tái đầu tư</t>
         </is>
       </c>
-      <c r="B59" s="20" t="n"/>
-      <c r="C59" s="20" t="n"/>
-      <c r="D59" s="20" t="n"/>
-      <c r="E59" s="20" t="n"/>
-      <c r="F59" s="20" t="n"/>
-      <c r="G59" s="20" t="n"/>
-      <c r="H59" s="20" t="n"/>
-      <c r="I59" s="20" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="20" t="inlineStr">
+      <c r="B68" s="29" t="n"/>
+      <c r="C68" s="29" t="n"/>
+      <c r="D68" s="29" t="n"/>
+      <c r="E68" s="29" t="n"/>
+      <c r="F68" s="29" t="n"/>
+      <c r="G68" s="29" t="n"/>
+      <c r="H68" s="29" t="n"/>
+      <c r="I68" s="29" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>FCF</t>
         </is>
       </c>
-      <c r="B60" s="22">
-        <f>IFERROR(B$48-ABS(B$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C60" s="22">
-        <f>IFERROR(C$48-ABS(C$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D60" s="22">
-        <f>IFERROR(D$48-ABS(D$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E60" s="22">
-        <f>IFERROR(E$48-ABS(E$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F60" s="22">
-        <f>IFERROR(F$48-ABS(F$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G60" s="22">
-        <f>IFERROR(G$48-ABS(G$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H60" s="22">
-        <f>IFERROR(H$48-ABS(H$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I60" s="22">
-        <f>IFERROR(I$48-ABS(I$47),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="20" t="inlineStr">
+      <c r="B69" s="31">
+        <f>IFERROR(B$57-ABS(B$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C69" s="31">
+        <f>IFERROR(C$57-ABS(C$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D69" s="31">
+        <f>IFERROR(D$57-ABS(D$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E69" s="31">
+        <f>IFERROR(E$57-ABS(E$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F69" s="31">
+        <f>IFERROR(F$57-ABS(F$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G69" s="31">
+        <f>IFERROR(G$57-ABS(G$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H69" s="31">
+        <f>IFERROR(H$57-ABS(H$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I69" s="31">
+        <f>IFERROR(I$57-ABS(I$56),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="29" t="inlineStr">
         <is>
           <t>FCF/DT</t>
         </is>
       </c>
-      <c r="B61" s="21">
-        <f>IFERROR(B$60/B$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C61" s="21">
-        <f>IFERROR(C$60/C$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D61" s="21">
-        <f>IFERROR(D$60/D$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E61" s="21">
-        <f>IFERROR(E$60/E$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F61" s="21">
-        <f>IFERROR(F$60/F$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G61" s="21">
-        <f>IFERROR(G$60/G$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H61" s="21">
-        <f>IFERROR(H$60/H$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I61" s="21">
-        <f>IFERROR(I$60/I$31,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="20" t="inlineStr">
+      <c r="B70" s="30">
+        <f>IFERROR(B$69/B$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C70" s="30">
+        <f>IFERROR(C$69/C$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D70" s="30">
+        <f>IFERROR(D$69/D$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E70" s="30">
+        <f>IFERROR(E$69/E$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F70" s="30">
+        <f>IFERROR(F$69/F$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G70" s="30">
+        <f>IFERROR(G$69/G$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H70" s="30">
+        <f>IFERROR(H$69/H$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I70" s="30">
+        <f>IFERROR(I$69/I$43,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="29" t="inlineStr">
         <is>
           <t>FCF/Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B62" s="21">
-        <f>IFERROR(B$60/B$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C62" s="21">
-        <f>IFERROR(C$60/C$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D62" s="21">
-        <f>IFERROR(D$60/D$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E62" s="21">
-        <f>IFERROR(E$60/E$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F62" s="21">
-        <f>IFERROR(F$60/F$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G62" s="21">
-        <f>IFERROR(G$60/G$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H62" s="21">
-        <f>IFERROR(H$60/H$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I62" s="21">
-        <f>IFERROR(I$60/I$27,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="20" t="inlineStr">
+      <c r="B71" s="30">
+        <f>IFERROR(B$69/B$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C71" s="30">
+        <f>IFERROR(C$69/C$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D71" s="30">
+        <f>IFERROR(D$69/D$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E71" s="30">
+        <f>IFERROR(E$69/E$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F71" s="30">
+        <f>IFERROR(F$69/F$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G71" s="30">
+        <f>IFERROR(G$69/G$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H71" s="30">
+        <f>IFERROR(H$69/H$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I71" s="30">
+        <f>IFERROR(I$69/I$35,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="29" t="inlineStr">
         <is>
           <t>Capex</t>
         </is>
       </c>
-      <c r="B63" s="22">
-        <f>IFERROR(ABS(B$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C63" s="22">
-        <f>IFERROR(ABS(C$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D63" s="22">
-        <f>IFERROR(ABS(D$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E63" s="22">
-        <f>IFERROR(ABS(E$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F63" s="22">
-        <f>IFERROR(ABS(F$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G63" s="22">
-        <f>IFERROR(ABS(G$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H63" s="22">
-        <f>IFERROR(ABS(H$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I63" s="22">
-        <f>IFERROR(ABS(I$47),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="20" t="inlineStr">
+      <c r="B72" s="31">
+        <f>IFERROR(ABS(B$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C72" s="31">
+        <f>IFERROR(ABS(C$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D72" s="31">
+        <f>IFERROR(ABS(D$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E72" s="31">
+        <f>IFERROR(ABS(E$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F72" s="31">
+        <f>IFERROR(ABS(F$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G72" s="31">
+        <f>IFERROR(ABS(G$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H72" s="31">
+        <f>IFERROR(ABS(H$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I72" s="31">
+        <f>IFERROR(ABS(I$56),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="29" t="inlineStr">
         <is>
           <t>Capex/TS</t>
         </is>
       </c>
-      <c r="B64" s="21">
-        <f>IFERROR(B$63/B$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C64" s="21">
-        <f>IFERROR(C$63/C$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D64" s="21">
-        <f>IFERROR(D$63/D$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E64" s="21">
-        <f>IFERROR(E$63/E$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F64" s="21">
-        <f>IFERROR(F$63/F$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G64" s="21">
-        <f>IFERROR(G$63/G$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H64" s="21">
-        <f>IFERROR(H$63/H$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I64" s="21">
-        <f>IFERROR(I$63/I$25,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="20" t="inlineStr">
+      <c r="B73" s="30">
+        <f>IFERROR(B$72/B$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C73" s="30">
+        <f>IFERROR(C$72/C$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D73" s="30">
+        <f>IFERROR(D$72/D$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E73" s="30">
+        <f>IFERROR(E$72/E$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F73" s="30">
+        <f>IFERROR(F$72/F$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G73" s="30">
+        <f>IFERROR(G$72/G$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H73" s="30">
+        <f>IFERROR(H$72/H$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I73" s="30">
+        <f>IFERROR(I$72/I$31,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="29" t="inlineStr">
         <is>
           <t>Capex/LNST</t>
         </is>
       </c>
-      <c r="B65" s="21">
-        <f>IFERROR(B$63/ABS(B$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C65" s="21">
-        <f>IFERROR(C$63/ABS(C$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D65" s="21">
-        <f>IFERROR(D$63/ABS(D$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E65" s="21">
-        <f>IFERROR(E$63/ABS(E$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F65" s="21">
-        <f>IFERROR(F$63/ABS(F$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G65" s="21">
-        <f>IFERROR(G$63/ABS(G$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H65" s="21">
-        <f>IFERROR(H$63/ABS(H$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I65" s="21">
-        <f>IFERROR(I$63/ABS(I$38),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="20" t="inlineStr">
+      <c r="B74" s="30">
+        <f>IFERROR(B$72/ABS(B$51),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C74" s="30">
+        <f>IFERROR(C$72/ABS(C$51),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D74" s="30">
+        <f>IFERROR(D$72/ABS(D$51),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E74" s="30">
+        <f>IFERROR(E$72/ABS(E$51),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F74" s="30">
+        <f>IFERROR(F$72/ABS(F$51),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G74" s="30">
+        <f>IFERROR(G$72/ABS(G$51),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H74" s="30">
+        <f>IFERROR(H$72/ABS(H$51),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I74" s="30">
+        <f>IFERROR(I$72/ABS(I$51),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
         <is>
           <t>Chi phí khấu hao/Lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B66" s="21">
-        <f>IFERROR(ABS(B$46)/B$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C66" s="21">
-        <f>IFERROR(ABS(C$46)/C$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D66" s="21">
-        <f>IFERROR(ABS(D$46)/D$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E66" s="21">
-        <f>IFERROR(ABS(E$46)/E$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F66" s="21">
-        <f>IFERROR(ABS(F$46)/F$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G66" s="21">
-        <f>IFERROR(ABS(G$46)/G$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H66" s="21">
-        <f>IFERROR(ABS(H$46)/H$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I66" s="21">
-        <f>IFERROR(ABS(I$46)/I$33,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="20" t="inlineStr">
+      <c r="B75" s="30">
+        <f>IFERROR(ABS(B$55)/B$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C75" s="30">
+        <f>IFERROR(ABS(C$55)/C$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D75" s="30">
+        <f>IFERROR(ABS(D$55)/D$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E75" s="30">
+        <f>IFERROR(ABS(E$55)/E$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F75" s="30">
+        <f>IFERROR(ABS(F$55)/F$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G75" s="30">
+        <f>IFERROR(ABS(G$55)/G$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H75" s="30">
+        <f>IFERROR(ABS(H$55)/H$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I75" s="30">
+        <f>IFERROR(ABS(I$55)/I$45,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>EBIT/Chi phí lãi vay</t>
         </is>
       </c>
-      <c r="B67" s="23">
-        <f>IFERROR(B$56/ABS(B$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C67" s="23">
-        <f>IFERROR(C$56/ABS(C$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D67" s="23">
-        <f>IFERROR(D$56/ABS(D$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E67" s="23">
-        <f>IFERROR(E$56/ABS(E$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F67" s="23">
-        <f>IFERROR(F$56/ABS(F$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G67" s="23">
-        <f>IFERROR(G$56/ABS(G$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H67" s="23">
-        <f>IFERROR(H$56/ABS(H$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I67" s="23">
-        <f>IFERROR(I$56/ABS(I$37),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="19" t="inlineStr">
+      <c r="B76" s="32">
+        <f>IFERROR(B$65/ABS(B$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C76" s="32">
+        <f>IFERROR(C$65/ABS(C$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D76" s="32">
+        <f>IFERROR(D$65/ABS(D$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E76" s="32">
+        <f>IFERROR(E$65/ABS(E$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F76" s="32">
+        <f>IFERROR(F$65/ABS(F$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G76" s="32">
+        <f>IFERROR(G$65/ABS(G$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H76" s="32">
+        <f>IFERROR(H$65/ABS(H$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I76" s="32">
+        <f>IFERROR(I$65/ABS(I$49),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
         <is>
           <t>Vốn lưu động &amp; hiệu quả hoạt động</t>
         </is>
       </c>
-      <c r="B68" s="20" t="n"/>
-      <c r="C68" s="20" t="n"/>
-      <c r="D68" s="20" t="n"/>
-      <c r="E68" s="20" t="n"/>
-      <c r="F68" s="20" t="n"/>
-      <c r="G68" s="20" t="n"/>
-      <c r="H68" s="20" t="n"/>
-      <c r="I68" s="20" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="20" t="inlineStr">
+      <c r="B77" s="29" t="n"/>
+      <c r="C77" s="29" t="n"/>
+      <c r="D77" s="29" t="n"/>
+      <c r="E77" s="29" t="n"/>
+      <c r="F77" s="29" t="n"/>
+      <c r="G77" s="29" t="n"/>
+      <c r="H77" s="29" t="n"/>
+      <c r="I77" s="29" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="29" t="inlineStr">
         <is>
           <t>Vòng quay tiền mặt</t>
         </is>
       </c>
-      <c r="B69" s="24">
+      <c r="B78" s="33">
         <f>IFERROR(B$17+B$18-B$16,"n/a")</f>
         <v/>
       </c>
-      <c r="C69" s="24">
+      <c r="C78" s="33">
         <f>IFERROR(C$17+C$18-C$16,"n/a")</f>
         <v/>
       </c>
-      <c r="D69" s="24">
+      <c r="D78" s="33">
         <f>IFERROR(D$17+D$18-D$16,"n/a")</f>
         <v/>
       </c>
-      <c r="E69" s="24">
+      <c r="E78" s="33">
         <f>IFERROR(E$17+E$18-E$16,"n/a")</f>
         <v/>
       </c>
-      <c r="F69" s="24">
+      <c r="F78" s="33">
         <f>IFERROR(F$17+F$18-F$16,"n/a")</f>
         <v/>
       </c>
-      <c r="G69" s="24">
+      <c r="G78" s="33">
         <f>IFERROR(G$17+G$18-G$16,"n/a")</f>
         <v/>
       </c>
-      <c r="H69" s="24">
+      <c r="H78" s="33">
         <f>IFERROR(H$17+H$18-H$16,"n/a")</f>
         <v/>
       </c>
-      <c r="I69" s="24">
+      <c r="I78" s="33">
         <f>IFERROR(I$17+I$18-I$16,"n/a")</f>
         <v/>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="20" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="29" t="inlineStr">
         <is>
           <t>HTK/DT</t>
         </is>
       </c>
-      <c r="B70" s="21">
-        <f>IFERROR(B$42/B$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C70" s="21">
-        <f>IFERROR(C$42/C$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D70" s="21">
-        <f>IFERROR(D$42/D$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E70" s="21">
-        <f>IFERROR(E$42/E$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F70" s="21">
-        <f>IFERROR(F$42/F$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G70" s="21">
-        <f>IFERROR(G$42/G$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H70" s="21">
-        <f>IFERROR(H$42/H$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I70" s="21">
-        <f>IFERROR(I$42/I$31,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="20" t="inlineStr">
+      <c r="B79" s="30">
+        <f>IFERROR(B$28/B$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C79" s="30">
+        <f>IFERROR(C$28/C$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D79" s="30">
+        <f>IFERROR(D$28/D$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E79" s="30">
+        <f>IFERROR(E$28/E$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F79" s="30">
+        <f>IFERROR(F$28/F$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G79" s="30">
+        <f>IFERROR(G$28/G$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H79" s="30">
+        <f>IFERROR(H$28/H$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I79" s="30">
+        <f>IFERROR(I$28/I$43,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="29" t="inlineStr">
         <is>
           <t>HTK/TS</t>
         </is>
       </c>
-      <c r="B71" s="21">
-        <f>IFERROR(B$42/B$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C71" s="21">
-        <f>IFERROR(C$42/C$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D71" s="21">
-        <f>IFERROR(D$42/D$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E71" s="21">
-        <f>IFERROR(E$42/E$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F71" s="21">
-        <f>IFERROR(F$42/F$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G71" s="21">
-        <f>IFERROR(G$42/G$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H71" s="21">
-        <f>IFERROR(H$42/H$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I71" s="21">
-        <f>IFERROR(I$42/I$25,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="20" t="inlineStr">
+      <c r="B80" s="30">
+        <f>IFERROR(B$28/B$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C80" s="30">
+        <f>IFERROR(C$28/C$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D80" s="30">
+        <f>IFERROR(D$28/D$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E80" s="30">
+        <f>IFERROR(E$28/E$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F80" s="30">
+        <f>IFERROR(F$28/F$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G80" s="30">
+        <f>IFERROR(G$28/G$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H80" s="30">
+        <f>IFERROR(H$28/H$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I80" s="30">
+        <f>IFERROR(I$28/I$31,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="29" t="inlineStr">
         <is>
           <t>DT/TS</t>
         </is>
       </c>
-      <c r="B72" s="21">
-        <f>IFERROR(B$31/B$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C72" s="21">
-        <f>IFERROR(C$31/C$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D72" s="21">
-        <f>IFERROR(D$31/D$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E72" s="21">
-        <f>IFERROR(E$31/E$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F72" s="21">
-        <f>IFERROR(F$31/F$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G72" s="21">
-        <f>IFERROR(G$31/G$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H72" s="21">
-        <f>IFERROR(H$31/H$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I72" s="21">
-        <f>IFERROR(I$31/I$25,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="19" t="inlineStr">
+      <c r="B81" s="30">
+        <f>IFERROR(B$43/B$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C81" s="30">
+        <f>IFERROR(C$43/C$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D81" s="30">
+        <f>IFERROR(D$43/D$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E81" s="30">
+        <f>IFERROR(E$43/E$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F81" s="30">
+        <f>IFERROR(F$43/F$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G81" s="30">
+        <f>IFERROR(G$43/G$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H81" s="30">
+        <f>IFERROR(H$43/H$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I81" s="30">
+        <f>IFERROR(I$43/I$31,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="28" t="inlineStr">
         <is>
           <t>Khả năng thanh toán</t>
         </is>
       </c>
-      <c r="B73" s="20" t="n"/>
-      <c r="C73" s="20" t="n"/>
-      <c r="D73" s="20" t="n"/>
-      <c r="E73" s="20" t="n"/>
-      <c r="F73" s="20" t="n"/>
-      <c r="G73" s="20" t="n"/>
-      <c r="H73" s="20" t="n"/>
-      <c r="I73" s="20" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="20" t="inlineStr">
+      <c r="B82" s="29" t="n"/>
+      <c r="C82" s="29" t="n"/>
+      <c r="D82" s="29" t="n"/>
+      <c r="E82" s="29" t="n"/>
+      <c r="F82" s="29" t="n"/>
+      <c r="G82" s="29" t="n"/>
+      <c r="H82" s="29" t="n"/>
+      <c r="I82" s="29" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="29" t="inlineStr">
         <is>
           <t>(TS ngắn hạn − HTK)/Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B74" s="23">
-        <f>IFERROR((B$44-B$42)/B$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C74" s="23">
-        <f>IFERROR((C$44-C$42)/C$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D74" s="23">
-        <f>IFERROR((D$44-D$42)/D$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E74" s="23">
-        <f>IFERROR((E$44-E$42)/E$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F74" s="23">
-        <f>IFERROR((F$44-F$42)/F$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G74" s="23">
-        <f>IFERROR((G$44-G$42)/G$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H74" s="23">
-        <f>IFERROR((H$44-H$42)/H$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I74" s="23">
-        <f>IFERROR((I$44-I$42)/I$27,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="20" t="inlineStr">
+      <c r="B83" s="32">
+        <f>IFERROR((B$29-B$28)/B$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C83" s="32">
+        <f>IFERROR((C$29-C$28)/C$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D83" s="32">
+        <f>IFERROR((D$29-D$28)/D$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E83" s="32">
+        <f>IFERROR((E$29-E$28)/E$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F83" s="32">
+        <f>IFERROR((F$29-F$28)/F$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G83" s="32">
+        <f>IFERROR((G$29-G$28)/G$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H83" s="32">
+        <f>IFERROR((H$29-H$28)/H$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I83" s="32">
+        <f>IFERROR((I$29-I$28)/I$35,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="29" t="inlineStr">
         <is>
           <t>TS ngắn hạn/Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B75" s="23">
-        <f>IFERROR(B$44/B$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C75" s="23">
-        <f>IFERROR(C$44/C$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D75" s="23">
-        <f>IFERROR(D$44/D$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E75" s="23">
-        <f>IFERROR(E$44/E$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F75" s="23">
-        <f>IFERROR(F$44/F$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G75" s="23">
-        <f>IFERROR(G$44/G$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H75" s="23">
-        <f>IFERROR(H$44/H$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I75" s="23">
-        <f>IFERROR(I$44/I$27,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="19" t="inlineStr">
+      <c r="B84" s="32">
+        <f>IFERROR(B$29/B$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C84" s="32">
+        <f>IFERROR(C$29/C$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D84" s="32">
+        <f>IFERROR(D$29/D$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E84" s="32">
+        <f>IFERROR(E$29/E$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F84" s="32">
+        <f>IFERROR(F$29/F$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G84" s="32">
+        <f>IFERROR(G$29/G$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H84" s="32">
+        <f>IFERROR(H$29/H$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I84" s="32">
+        <f>IFERROR(I$29/I$35,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="28" t="inlineStr">
         <is>
           <t>Tài sản &amp; cơ cấu tài sản</t>
         </is>
       </c>
-      <c r="B76" s="20" t="n"/>
-      <c r="C76" s="20" t="n"/>
-      <c r="D76" s="20" t="n"/>
-      <c r="E76" s="20" t="n"/>
-      <c r="F76" s="20" t="n"/>
-      <c r="G76" s="20" t="n"/>
-      <c r="H76" s="20" t="n"/>
-      <c r="I76" s="20" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="20" t="inlineStr">
+      <c r="B85" s="29" t="n"/>
+      <c r="C85" s="29" t="n"/>
+      <c r="D85" s="29" t="n"/>
+      <c r="E85" s="29" t="n"/>
+      <c r="F85" s="29" t="n"/>
+      <c r="G85" s="29" t="n"/>
+      <c r="H85" s="29" t="n"/>
+      <c r="I85" s="29" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="29" t="inlineStr">
         <is>
           <t>TSCĐ vô hình</t>
         </is>
       </c>
-      <c r="B77" s="22">
-        <f>IFERROR(B$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C77" s="22">
-        <f>IFERROR(C$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D77" s="22">
-        <f>IFERROR(D$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E77" s="22">
-        <f>IFERROR(E$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F77" s="22">
-        <f>IFERROR(F$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G77" s="22">
-        <f>IFERROR(G$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H77" s="22">
-        <f>IFERROR(H$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I77" s="22">
-        <f>IFERROR(I$45,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="20" t="inlineStr">
+      <c r="B86" s="31">
+        <f>IFERROR(B$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C86" s="31">
+        <f>IFERROR(C$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D86" s="31">
+        <f>IFERROR(D$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E86" s="31">
+        <f>IFERROR(E$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F86" s="31">
+        <f>IFERROR(F$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G86" s="31">
+        <f>IFERROR(G$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H86" s="31">
+        <f>IFERROR(H$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I86" s="31">
+        <f>IFERROR(I$30,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="29" t="inlineStr">
         <is>
           <t>Tài sản vô hình/Giá trị sổ sách</t>
         </is>
       </c>
-      <c r="B78" s="21">
-        <f>IFERROR(B$45/B$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C78" s="21">
-        <f>IFERROR(C$45/C$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D78" s="21">
-        <f>IFERROR(D$45/D$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E78" s="21">
-        <f>IFERROR(E$45/E$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F78" s="21">
-        <f>IFERROR(F$45/F$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G78" s="21">
-        <f>IFERROR(G$45/G$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H78" s="21">
-        <f>IFERROR(H$45/H$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I78" s="21">
-        <f>IFERROR(I$45/I$24,"n/a")</f>
+      <c r="B87" s="30">
+        <f>IFERROR(B$30/B$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C87" s="30">
+        <f>IFERROR(C$30/C$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D87" s="30">
+        <f>IFERROR(D$30/D$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E87" s="30">
+        <f>IFERROR(E$30/E$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F87" s="30">
+        <f>IFERROR(F$30/F$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G87" s="30">
+        <f>IFERROR(G$30/G$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H87" s="30">
+        <f>IFERROR(H$30/H$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I87" s="30">
+        <f>IFERROR(I$30/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -9365,18 +9674,6 @@
       <formula>0.15</formula>
     </cfRule>
     <cfRule type="cellIs" priority="15" operator="lessThan" dxfId="1">
-      <formula>0.15</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4:I5">
-    <cfRule type="cellIs" priority="11" operator="lessThan" dxfId="1">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="12" operator="greaterThanOrEqual" dxfId="0">
-      <formula>0.15</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="13" operator="between" dxfId="2">
-      <formula>0.1</formula>
       <formula>0.15</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9390,11 +9687,6 @@
     <cfRule type="cellIs" priority="10" operator="between" dxfId="2">
       <formula>0.1</formula>
       <formula>0.3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7:I7">
-    <cfRule type="cellIs" priority="7" operator="greaterThanOrEqual" dxfId="0">
-      <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:I8 B11:I11">
@@ -9420,6 +9712,23 @@
       <formula>0.3</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B4:J5">
+    <cfRule type="cellIs" priority="11" operator="lessThan" dxfId="1">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0.15</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="13" operator="between" dxfId="2">
+      <formula>0.1</formula>
+      <formula>0.15</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:J7">
+    <cfRule type="cellIs" priority="7" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9430,22 +9739,1635 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11.77734375" customWidth="1" min="1" max="1"/>
+    <col width="17.44140625" customWidth="1" min="2" max="2"/>
+    <col width="11.77734375" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1">
-        <f>A1+B1</f>
-        <v/>
-      </c>
-    </row>
+    <row r="1" ht="13.5" customHeight="1">
+      <c r="A1" s="29" t="n"/>
+      <c r="B1" s="29" t="inlineStr">
+        <is>
+          <t>Q4/2025</t>
+        </is>
+      </c>
+      <c r="C1" s="29" t="inlineStr">
+        <is>
+          <t>Q1/2026</t>
+        </is>
+      </c>
+      <c r="D1" s="29" t="inlineStr">
+        <is>
+          <t>Q2/2026</t>
+        </is>
+      </c>
+      <c r="E1" s="29" t="inlineStr">
+        <is>
+          <t>Q3/2026</t>
+        </is>
+      </c>
+      <c r="F1" s="29" t="inlineStr">
+        <is>
+          <t>Q4/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="13.5" customHeight="1">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Số CP</t>
+        </is>
+      </c>
+      <c r="B2" s="34" t="n">
+        <v>178815054</v>
+      </c>
+      <c r="C2" s="34" t="n">
+        <v>178815054</v>
+      </c>
+      <c r="D2" s="34" t="n">
+        <v>178815054</v>
+      </c>
+      <c r="E2" s="34" t="n">
+        <v>178815054</v>
+      </c>
+      <c r="F2" s="34" t="n">
+        <v>178815054</v>
+      </c>
+    </row>
+    <row r="3" ht="13.5" customHeight="1">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>Thị giá</t>
+        </is>
+      </c>
+      <c r="B3" s="34">
+        <f>[1]Sheet1!$F$2</f>
+        <v/>
+      </c>
+      <c r="C3" s="34">
+        <f>[1]Sheet1!$F$2</f>
+        <v/>
+      </c>
+      <c r="D3" s="34">
+        <f>[1]Sheet1!$F$2</f>
+        <v/>
+      </c>
+      <c r="E3" s="34">
+        <f>[1]Sheet1!$F$2</f>
+        <v/>
+      </c>
+      <c r="F3" s="34">
+        <f>[1]Sheet1!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="13.5" customHeight="1">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>Vốn hoá</t>
+        </is>
+      </c>
+      <c r="B4" s="34">
+        <f>B2*B3</f>
+        <v/>
+      </c>
+      <c r="C4" s="34">
+        <f>C2*C3</f>
+        <v/>
+      </c>
+      <c r="D4" s="34">
+        <f>D2*D3</f>
+        <v/>
+      </c>
+      <c r="E4" s="34">
+        <f>E2*E3</f>
+        <v/>
+      </c>
+      <c r="F4" s="34">
+        <f>F2*F3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="13.5" customHeight="1"/>
+    <row r="6" ht="13.5" customHeight="1">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>VCSH</t>
+        </is>
+      </c>
+      <c r="B6" s="34">
+        <f>chi_so_tai_chinh!I39</f>
+        <v/>
+      </c>
+      <c r="C6" s="34" t="n">
+        <v>5514000000000</v>
+      </c>
+      <c r="D6" s="34">
+        <f>$C$6*(($F$6/$C$6)^(1/3))</f>
+        <v/>
+      </c>
+      <c r="E6" s="34">
+        <f>$C$6*(($F$6/$C$6)^(2/3))</f>
+        <v/>
+      </c>
+      <c r="F6" s="34">
+        <f>chi_so_tai_chinh!J39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="13.5" customHeight="1">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>LICĐKKS</t>
+        </is>
+      </c>
+      <c r="B7" s="34">
+        <f>chi_so_tai_chinh!I41</f>
+        <v/>
+      </c>
+      <c r="C7" s="34">
+        <f>chi_so_tai_chinh!J41</f>
+        <v/>
+      </c>
+      <c r="D7" s="34">
+        <f>chi_so_tai_chinh!K41</f>
+        <v/>
+      </c>
+      <c r="E7" s="34">
+        <f>chi_so_tai_chinh!L41</f>
+        <v/>
+      </c>
+      <c r="F7" s="34">
+        <f>chi_so_tai_chinh!M41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="13.5" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>BV</t>
+        </is>
+      </c>
+      <c r="B8" s="34">
+        <f>B6-B7</f>
+        <v/>
+      </c>
+      <c r="C8" s="34">
+        <f>C6-C7</f>
+        <v/>
+      </c>
+      <c r="D8" s="34">
+        <f>D6-D7</f>
+        <v/>
+      </c>
+      <c r="E8" s="34">
+        <f>E6-E7</f>
+        <v/>
+      </c>
+      <c r="F8" s="34">
+        <f>F6-F7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="13.5" customHeight="1">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>BVPS</t>
+        </is>
+      </c>
+      <c r="B9" s="35">
+        <f>B8/B2</f>
+        <v/>
+      </c>
+      <c r="C9" s="35">
+        <f>C8/C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="35">
+        <f>D8/D2</f>
+        <v/>
+      </c>
+      <c r="E9" s="35">
+        <f>E8/E2</f>
+        <v/>
+      </c>
+      <c r="F9" s="35">
+        <f>F8/F2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="13.5" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="B10" s="36">
+        <f>B3/B9</f>
+        <v/>
+      </c>
+      <c r="C10" s="36">
+        <f>C3/C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="36">
+        <f>D3/D9</f>
+        <v/>
+      </c>
+      <c r="E10" s="36">
+        <f>E3/E9</f>
+        <v/>
+      </c>
+      <c r="F10" s="36">
+        <f>F3/F9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="13.5" customHeight="1">
+      <c r="H11" s="37" t="n"/>
+      <c r="I11" s="37" t="n"/>
+      <c r="J11" s="37" t="n"/>
+    </row>
+    <row r="12" ht="13.5" customHeight="1">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="B12" s="34">
+        <f>chi_so_tai_chinh!I43</f>
+        <v/>
+      </c>
+      <c r="C12" s="34">
+        <f>$B$12*(($F$12/$B$12)^(1/4))</f>
+        <v/>
+      </c>
+      <c r="D12" s="34">
+        <f>$B$12*(($F$12/$B$12)^(2/4))</f>
+        <v/>
+      </c>
+      <c r="E12" s="34">
+        <f>$B$12*(($F$12/$B$12)^(3/4))</f>
+        <v/>
+      </c>
+      <c r="F12" s="34">
+        <f>chi_so_tai_chinh!J43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="13.5" customHeight="1">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>DT per share</t>
+        </is>
+      </c>
+      <c r="B13" s="35">
+        <f>B12/C2</f>
+        <v/>
+      </c>
+      <c r="C13" s="35">
+        <f>C12/C2</f>
+        <v/>
+      </c>
+      <c r="D13" s="35">
+        <f>D12/D2</f>
+        <v/>
+      </c>
+      <c r="E13" s="35">
+        <f>E12/E2</f>
+        <v/>
+      </c>
+      <c r="F13" s="35">
+        <f>F12/F2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="13.5" customHeight="1">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+      <c r="B14" s="36">
+        <f>C3/B13</f>
+        <v/>
+      </c>
+      <c r="C14" s="36">
+        <f>C4/C12</f>
+        <v/>
+      </c>
+      <c r="D14" s="36">
+        <f>D4/D12</f>
+        <v/>
+      </c>
+      <c r="E14" s="36">
+        <f>E4/E12</f>
+        <v/>
+      </c>
+      <c r="F14" s="36">
+        <f>F4/F12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="13.5" customHeight="1"/>
+    <row r="16" ht="13.5" customHeight="1">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>Earning</t>
+        </is>
+      </c>
+      <c r="B16" s="34">
+        <f>chi_so_tai_chinh!I52</f>
+        <v/>
+      </c>
+      <c r="C16" s="34">
+        <f>$B$16*(($F$16/$B$16)^(1/4))</f>
+        <v/>
+      </c>
+      <c r="D16" s="34">
+        <f>$B$16*(($F$16/$B$16)^(2/4))</f>
+        <v/>
+      </c>
+      <c r="E16" s="34">
+        <f>$B$16*(($F$16/$B$16)^(3/4))</f>
+        <v/>
+      </c>
+      <c r="F16" s="34">
+        <f>chi_so_tai_chinh!J52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="13.5" customHeight="1">
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B17" s="35">
+        <f>B16/$F$2</f>
+        <v/>
+      </c>
+      <c r="C17" s="35">
+        <f>C16/$F$2</f>
+        <v/>
+      </c>
+      <c r="D17" s="35">
+        <f>D16/$F$2</f>
+        <v/>
+      </c>
+      <c r="E17" s="35">
+        <f>E16/$F$2</f>
+        <v/>
+      </c>
+      <c r="F17" s="35">
+        <f>F16/$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="13.5" customHeight="1">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="B18" s="36">
+        <f>$F$3/B17</f>
+        <v/>
+      </c>
+      <c r="C18" s="36">
+        <f>$F$3/C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="36">
+        <f>$F$3/D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="36">
+        <f>$F$3/E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="36">
+        <f>$F$3/F17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="13.5" customHeight="1"/>
+    <row r="20" ht="13.5" customHeight="1"/>
+    <row r="21" ht="13.5" customHeight="1"/>
+    <row r="22" ht="13.5" customHeight="1"/>
+    <row r="23" ht="13.5" customHeight="1"/>
+    <row r="24" ht="13.5" customHeight="1"/>
+    <row r="25" ht="13.5" customHeight="1"/>
+    <row r="26" ht="13.5" customHeight="1"/>
+    <row r="27" ht="13.5" customHeight="1"/>
+    <row r="28" ht="13.5" customHeight="1"/>
+    <row r="29" ht="13.5" customHeight="1"/>
+    <row r="30" ht="13.5" customHeight="1"/>
+    <row r="31" ht="13.5" customHeight="1"/>
+    <row r="32" ht="13.5" customHeight="1"/>
+    <row r="33" ht="13.5" customHeight="1"/>
+    <row r="34" ht="13.5" customHeight="1"/>
+    <row r="35" ht="13.5" customHeight="1"/>
+    <row r="36" ht="13.5" customHeight="1"/>
+    <row r="37" ht="13.5" customHeight="1"/>
+    <row r="38" ht="13.5" customHeight="1"/>
+    <row r="39" ht="13.5" customHeight="1"/>
+    <row r="40" ht="13.5" customHeight="1"/>
+    <row r="41" ht="13.5" customHeight="1"/>
+    <row r="42" ht="13.5" customHeight="1"/>
+    <row r="43" ht="13.5" customHeight="1"/>
+    <row r="44" ht="13.5" customHeight="1"/>
+    <row r="45" ht="13.5" customHeight="1"/>
+    <row r="46" ht="13.5" customHeight="1"/>
+    <row r="47" ht="13.5" customHeight="1"/>
+    <row r="48" ht="13.5" customHeight="1"/>
+    <row r="49" ht="13.5" customHeight="1"/>
+    <row r="50" ht="13.5" customHeight="1"/>
+    <row r="51" ht="13.5" customHeight="1"/>
+    <row r="52" ht="13.5" customHeight="1"/>
+    <row r="53" ht="13.5" customHeight="1"/>
+    <row r="54" ht="13.5" customHeight="1"/>
+    <row r="55" ht="13.5" customHeight="1"/>
+    <row r="56" ht="13.5" customHeight="1"/>
+    <row r="57" ht="13.5" customHeight="1"/>
+    <row r="58" ht="13.5" customHeight="1"/>
+    <row r="59" ht="13.5" customHeight="1"/>
+    <row r="60" ht="13.5" customHeight="1"/>
+    <row r="61" ht="13.5" customHeight="1"/>
+    <row r="62" ht="13.5" customHeight="1"/>
+    <row r="63" ht="13.5" customHeight="1"/>
+    <row r="64" ht="13.5" customHeight="1"/>
+    <row r="65" ht="13.5" customHeight="1"/>
+    <row r="66" ht="13.5" customHeight="1"/>
+    <row r="67" ht="13.5" customHeight="1"/>
+    <row r="68" ht="13.5" customHeight="1"/>
+    <row r="69" ht="13.5" customHeight="1"/>
+    <row r="70" ht="13.5" customHeight="1"/>
+    <row r="71" ht="13.5" customHeight="1"/>
+    <row r="72" ht="13.5" customHeight="1"/>
+    <row r="73" ht="13.5" customHeight="1"/>
+    <row r="74" ht="13.5" customHeight="1"/>
+    <row r="75" ht="13.5" customHeight="1"/>
+    <row r="76" ht="13.5" customHeight="1"/>
+    <row r="77" ht="13.5" customHeight="1"/>
+    <row r="78" ht="13.5" customHeight="1"/>
+    <row r="79" ht="13.5" customHeight="1"/>
+    <row r="80" ht="13.5" customHeight="1"/>
+    <row r="81" ht="13.5" customHeight="1"/>
+    <row r="82" ht="13.5" customHeight="1"/>
+    <row r="83" ht="13.5" customHeight="1"/>
+    <row r="84" ht="13.5" customHeight="1"/>
+    <row r="85" ht="13.5" customHeight="1"/>
+    <row r="86" ht="13.5" customHeight="1"/>
+    <row r="87" ht="13.5" customHeight="1"/>
+    <row r="88" ht="13.5" customHeight="1"/>
+    <row r="89" ht="13.5" customHeight="1"/>
+    <row r="90" ht="13.5" customHeight="1"/>
+    <row r="91" ht="13.5" customHeight="1"/>
+    <row r="92" ht="13.5" customHeight="1"/>
+    <row r="93" ht="13.5" customHeight="1"/>
+    <row r="94" ht="13.5" customHeight="1"/>
+    <row r="95" ht="13.5" customHeight="1"/>
+    <row r="96" ht="13.5" customHeight="1"/>
+    <row r="97" ht="13.5" customHeight="1"/>
+    <row r="98" ht="13.5" customHeight="1"/>
+    <row r="99" ht="13.5" customHeight="1"/>
+    <row r="100" ht="13.5" customHeight="1"/>
+    <row r="101" ht="13.5" customHeight="1"/>
+    <row r="102" ht="13.5" customHeight="1"/>
+    <row r="103" ht="13.5" customHeight="1"/>
+    <row r="104" ht="13.5" customHeight="1"/>
+    <row r="105" ht="13.5" customHeight="1"/>
+    <row r="106" ht="13.5" customHeight="1"/>
+    <row r="107" ht="13.5" customHeight="1"/>
+    <row r="108" ht="13.5" customHeight="1"/>
+    <row r="109" ht="13.5" customHeight="1"/>
+    <row r="110" ht="13.5" customHeight="1"/>
+    <row r="111" ht="13.5" customHeight="1"/>
+    <row r="112" ht="13.5" customHeight="1"/>
+    <row r="113" ht="13.5" customHeight="1"/>
+    <row r="114" ht="13.5" customHeight="1"/>
+    <row r="115" ht="13.5" customHeight="1"/>
+    <row r="116" ht="13.5" customHeight="1"/>
+    <row r="117" ht="13.5" customHeight="1"/>
+    <row r="118" ht="13.5" customHeight="1"/>
+    <row r="119" ht="13.5" customHeight="1"/>
+    <row r="120" ht="13.5" customHeight="1"/>
+    <row r="121" ht="13.5" customHeight="1"/>
+    <row r="122" ht="13.5" customHeight="1"/>
+    <row r="123" ht="13.5" customHeight="1"/>
+    <row r="124" ht="13.5" customHeight="1"/>
+    <row r="125" ht="13.5" customHeight="1"/>
+    <row r="126" ht="13.5" customHeight="1"/>
+    <row r="127" ht="13.5" customHeight="1"/>
+    <row r="128" ht="13.5" customHeight="1"/>
+    <row r="129" ht="13.5" customHeight="1"/>
+    <row r="130" ht="13.5" customHeight="1"/>
+    <row r="131" ht="13.5" customHeight="1"/>
+    <row r="132" ht="13.5" customHeight="1"/>
+    <row r="133" ht="13.5" customHeight="1"/>
+    <row r="134" ht="13.5" customHeight="1"/>
+    <row r="135" ht="13.5" customHeight="1"/>
+    <row r="136" ht="13.5" customHeight="1"/>
+    <row r="137" ht="13.5" customHeight="1"/>
+    <row r="138" ht="13.5" customHeight="1"/>
+    <row r="139" ht="13.5" customHeight="1"/>
+    <row r="140" ht="13.5" customHeight="1"/>
+    <row r="141" ht="13.5" customHeight="1"/>
+    <row r="142" ht="13.5" customHeight="1"/>
+    <row r="143" ht="13.5" customHeight="1"/>
+    <row r="144" ht="13.5" customHeight="1"/>
+    <row r="145" ht="13.5" customHeight="1"/>
+    <row r="146" ht="13.5" customHeight="1"/>
+    <row r="147" ht="13.5" customHeight="1"/>
+    <row r="148" ht="13.5" customHeight="1"/>
+    <row r="149" ht="13.5" customHeight="1"/>
+    <row r="150" ht="13.5" customHeight="1"/>
+    <row r="151" ht="13.5" customHeight="1"/>
+    <row r="152" ht="13.5" customHeight="1"/>
+    <row r="153" ht="13.5" customHeight="1"/>
+    <row r="154" ht="13.5" customHeight="1"/>
+    <row r="155" ht="13.5" customHeight="1"/>
+    <row r="156" ht="13.5" customHeight="1"/>
+    <row r="157" ht="13.5" customHeight="1"/>
+    <row r="158" ht="13.5" customHeight="1"/>
+    <row r="159" ht="13.5" customHeight="1"/>
+    <row r="160" ht="13.5" customHeight="1"/>
+    <row r="161" ht="13.5" customHeight="1"/>
+    <row r="162" ht="13.5" customHeight="1"/>
+    <row r="163" ht="13.5" customHeight="1"/>
+    <row r="164" ht="13.5" customHeight="1"/>
+    <row r="165" ht="13.5" customHeight="1"/>
+    <row r="166" ht="13.5" customHeight="1"/>
+    <row r="167" ht="13.5" customHeight="1"/>
+    <row r="168" ht="13.5" customHeight="1"/>
+    <row r="169" ht="13.5" customHeight="1"/>
+    <row r="170" ht="13.5" customHeight="1"/>
+    <row r="171" ht="13.5" customHeight="1"/>
+    <row r="172" ht="13.5" customHeight="1"/>
+    <row r="173" ht="13.5" customHeight="1"/>
+    <row r="174" ht="13.5" customHeight="1"/>
+    <row r="175" ht="13.5" customHeight="1"/>
+    <row r="176" ht="13.5" customHeight="1"/>
+    <row r="177" ht="13.5" customHeight="1"/>
+    <row r="178" ht="13.5" customHeight="1"/>
+    <row r="179" ht="13.5" customHeight="1"/>
+    <row r="180" ht="13.5" customHeight="1"/>
+    <row r="181" ht="13.5" customHeight="1"/>
+    <row r="182" ht="13.5" customHeight="1"/>
+    <row r="183" ht="13.5" customHeight="1"/>
+    <row r="184" ht="13.5" customHeight="1"/>
+    <row r="185" ht="13.5" customHeight="1"/>
+    <row r="186" ht="13.5" customHeight="1"/>
+    <row r="187" ht="13.5" customHeight="1"/>
+    <row r="188" ht="13.5" customHeight="1"/>
+    <row r="189" ht="13.5" customHeight="1"/>
+    <row r="190" ht="13.5" customHeight="1"/>
+    <row r="191" ht="13.5" customHeight="1"/>
+    <row r="192" ht="13.5" customHeight="1"/>
+    <row r="193" ht="13.5" customHeight="1"/>
+    <row r="194" ht="13.5" customHeight="1"/>
+    <row r="195" ht="13.5" customHeight="1"/>
+    <row r="196" ht="13.5" customHeight="1"/>
+    <row r="197" ht="13.5" customHeight="1"/>
+    <row r="198" ht="13.5" customHeight="1"/>
+    <row r="199" ht="13.5" customHeight="1"/>
+    <row r="200" ht="13.5" customHeight="1"/>
+    <row r="201" ht="13.5" customHeight="1"/>
+    <row r="202" ht="13.5" customHeight="1"/>
+    <row r="203" ht="13.5" customHeight="1"/>
+    <row r="204" ht="13.5" customHeight="1"/>
+    <row r="205" ht="13.5" customHeight="1"/>
+    <row r="206" ht="13.5" customHeight="1"/>
+    <row r="207" ht="13.5" customHeight="1"/>
+    <row r="208" ht="13.5" customHeight="1"/>
+    <row r="209" ht="13.5" customHeight="1"/>
+    <row r="210" ht="13.5" customHeight="1"/>
+    <row r="211" ht="13.5" customHeight="1"/>
+    <row r="212" ht="13.5" customHeight="1"/>
+    <row r="213" ht="13.5" customHeight="1"/>
+    <row r="214" ht="13.5" customHeight="1"/>
+    <row r="215" ht="13.5" customHeight="1"/>
+    <row r="216" ht="13.5" customHeight="1"/>
+    <row r="217" ht="13.5" customHeight="1"/>
+    <row r="218" ht="13.5" customHeight="1"/>
+    <row r="219" ht="13.5" customHeight="1"/>
+    <row r="220" ht="13.5" customHeight="1"/>
+    <row r="221" ht="13.5" customHeight="1"/>
+    <row r="222" ht="13.5" customHeight="1"/>
+    <row r="223" ht="13.5" customHeight="1"/>
+    <row r="224" ht="13.5" customHeight="1"/>
+    <row r="225" ht="13.5" customHeight="1"/>
+    <row r="226" ht="13.5" customHeight="1"/>
+    <row r="227" ht="13.5" customHeight="1"/>
+    <row r="228" ht="13.5" customHeight="1"/>
+    <row r="229" ht="13.5" customHeight="1"/>
+    <row r="230" ht="13.5" customHeight="1"/>
+    <row r="231" ht="13.5" customHeight="1"/>
+    <row r="232" ht="13.5" customHeight="1"/>
+    <row r="233" ht="13.5" customHeight="1"/>
+    <row r="234" ht="13.5" customHeight="1"/>
+    <row r="235" ht="13.5" customHeight="1"/>
+    <row r="236" ht="13.5" customHeight="1"/>
+    <row r="237" ht="13.5" customHeight="1"/>
+    <row r="238" ht="13.5" customHeight="1"/>
+    <row r="239" ht="13.5" customHeight="1"/>
+    <row r="240" ht="13.5" customHeight="1"/>
+    <row r="241" ht="13.5" customHeight="1"/>
+    <row r="242" ht="13.5" customHeight="1"/>
+    <row r="243" ht="13.5" customHeight="1"/>
+    <row r="244" ht="13.5" customHeight="1"/>
+    <row r="245" ht="13.5" customHeight="1"/>
+    <row r="246" ht="13.5" customHeight="1"/>
+    <row r="247" ht="13.5" customHeight="1"/>
+    <row r="248" ht="13.5" customHeight="1"/>
+    <row r="249" ht="13.5" customHeight="1"/>
+    <row r="250" ht="13.5" customHeight="1"/>
+    <row r="251" ht="13.5" customHeight="1"/>
+    <row r="252" ht="13.5" customHeight="1"/>
+    <row r="253" ht="13.5" customHeight="1"/>
+    <row r="254" ht="13.5" customHeight="1"/>
+    <row r="255" ht="13.5" customHeight="1"/>
+    <row r="256" ht="13.5" customHeight="1"/>
+    <row r="257" ht="13.5" customHeight="1"/>
+    <row r="258" ht="13.5" customHeight="1"/>
+    <row r="259" ht="13.5" customHeight="1"/>
+    <row r="260" ht="13.5" customHeight="1"/>
+    <row r="261" ht="13.5" customHeight="1"/>
+    <row r="262" ht="13.5" customHeight="1"/>
+    <row r="263" ht="13.5" customHeight="1"/>
+    <row r="264" ht="13.5" customHeight="1"/>
+    <row r="265" ht="13.5" customHeight="1"/>
+    <row r="266" ht="13.5" customHeight="1"/>
+    <row r="267" ht="13.5" customHeight="1"/>
+    <row r="268" ht="13.5" customHeight="1"/>
+    <row r="269" ht="13.5" customHeight="1"/>
+    <row r="270" ht="13.5" customHeight="1"/>
+    <row r="271" ht="13.5" customHeight="1"/>
+    <row r="272" ht="13.5" customHeight="1"/>
+    <row r="273" ht="13.5" customHeight="1"/>
+    <row r="274" ht="13.5" customHeight="1"/>
+    <row r="275" ht="13.5" customHeight="1"/>
+    <row r="276" ht="13.5" customHeight="1"/>
+    <row r="277" ht="13.5" customHeight="1"/>
+    <row r="278" ht="13.5" customHeight="1"/>
+    <row r="279" ht="13.5" customHeight="1"/>
+    <row r="280" ht="13.5" customHeight="1"/>
+    <row r="281" ht="13.5" customHeight="1"/>
+    <row r="282" ht="13.5" customHeight="1"/>
+    <row r="283" ht="13.5" customHeight="1"/>
+    <row r="284" ht="13.5" customHeight="1"/>
+    <row r="285" ht="13.5" customHeight="1"/>
+    <row r="286" ht="13.5" customHeight="1"/>
+    <row r="287" ht="13.5" customHeight="1"/>
+    <row r="288" ht="13.5" customHeight="1"/>
+    <row r="289" ht="13.5" customHeight="1"/>
+    <row r="290" ht="13.5" customHeight="1"/>
+    <row r="291" ht="13.5" customHeight="1"/>
+    <row r="292" ht="13.5" customHeight="1"/>
+    <row r="293" ht="13.5" customHeight="1"/>
+    <row r="294" ht="13.5" customHeight="1"/>
+    <row r="295" ht="13.5" customHeight="1"/>
+    <row r="296" ht="13.5" customHeight="1"/>
+    <row r="297" ht="13.5" customHeight="1"/>
+    <row r="298" ht="13.5" customHeight="1"/>
+    <row r="299" ht="13.5" customHeight="1"/>
+    <row r="300" ht="13.5" customHeight="1"/>
+    <row r="301" ht="13.5" customHeight="1"/>
+    <row r="302" ht="13.5" customHeight="1"/>
+    <row r="303" ht="13.5" customHeight="1"/>
+    <row r="304" ht="13.5" customHeight="1"/>
+    <row r="305" ht="13.5" customHeight="1"/>
+    <row r="306" ht="13.5" customHeight="1"/>
+    <row r="307" ht="13.5" customHeight="1"/>
+    <row r="308" ht="13.5" customHeight="1"/>
+    <row r="309" ht="13.5" customHeight="1"/>
+    <row r="310" ht="13.5" customHeight="1"/>
+    <row r="311" ht="13.5" customHeight="1"/>
+    <row r="312" ht="13.5" customHeight="1"/>
+    <row r="313" ht="13.5" customHeight="1"/>
+    <row r="314" ht="13.5" customHeight="1"/>
+    <row r="315" ht="13.5" customHeight="1"/>
+    <row r="316" ht="13.5" customHeight="1"/>
+    <row r="317" ht="13.5" customHeight="1"/>
+    <row r="318" ht="13.5" customHeight="1"/>
+    <row r="319" ht="13.5" customHeight="1"/>
+    <row r="320" ht="13.5" customHeight="1"/>
+    <row r="321" ht="13.5" customHeight="1"/>
+    <row r="322" ht="13.5" customHeight="1"/>
+    <row r="323" ht="13.5" customHeight="1"/>
+    <row r="324" ht="13.5" customHeight="1"/>
+    <row r="325" ht="13.5" customHeight="1"/>
+    <row r="326" ht="13.5" customHeight="1"/>
+    <row r="327" ht="13.5" customHeight="1"/>
+    <row r="328" ht="13.5" customHeight="1"/>
+    <row r="329" ht="13.5" customHeight="1"/>
+    <row r="330" ht="13.5" customHeight="1"/>
+    <row r="331" ht="13.5" customHeight="1"/>
+    <row r="332" ht="13.5" customHeight="1"/>
+    <row r="333" ht="13.5" customHeight="1"/>
+    <row r="334" ht="13.5" customHeight="1"/>
+    <row r="335" ht="13.5" customHeight="1"/>
+    <row r="336" ht="13.5" customHeight="1"/>
+    <row r="337" ht="13.5" customHeight="1"/>
+    <row r="338" ht="13.5" customHeight="1"/>
+    <row r="339" ht="13.5" customHeight="1"/>
+    <row r="340" ht="13.5" customHeight="1"/>
+    <row r="341" ht="13.5" customHeight="1"/>
+    <row r="342" ht="13.5" customHeight="1"/>
+    <row r="343" ht="13.5" customHeight="1"/>
+    <row r="344" ht="13.5" customHeight="1"/>
+    <row r="345" ht="13.5" customHeight="1"/>
+    <row r="346" ht="13.5" customHeight="1"/>
+    <row r="347" ht="13.5" customHeight="1"/>
+    <row r="348" ht="13.5" customHeight="1"/>
+    <row r="349" ht="13.5" customHeight="1"/>
+    <row r="350" ht="13.5" customHeight="1"/>
+    <row r="351" ht="13.5" customHeight="1"/>
+    <row r="352" ht="13.5" customHeight="1"/>
+    <row r="353" ht="13.5" customHeight="1"/>
+    <row r="354" ht="13.5" customHeight="1"/>
+    <row r="355" ht="13.5" customHeight="1"/>
+    <row r="356" ht="13.5" customHeight="1"/>
+    <row r="357" ht="13.5" customHeight="1"/>
+    <row r="358" ht="13.5" customHeight="1"/>
+    <row r="359" ht="13.5" customHeight="1"/>
+    <row r="360" ht="13.5" customHeight="1"/>
+    <row r="361" ht="13.5" customHeight="1"/>
+    <row r="362" ht="13.5" customHeight="1"/>
+    <row r="363" ht="13.5" customHeight="1"/>
+    <row r="364" ht="13.5" customHeight="1"/>
+    <row r="365" ht="13.5" customHeight="1"/>
+    <row r="366" ht="13.5" customHeight="1"/>
+    <row r="367" ht="13.5" customHeight="1"/>
+    <row r="368" ht="13.5" customHeight="1"/>
+    <row r="369" ht="13.5" customHeight="1"/>
+    <row r="370" ht="13.5" customHeight="1"/>
+    <row r="371" ht="13.5" customHeight="1"/>
+    <row r="372" ht="13.5" customHeight="1"/>
+    <row r="373" ht="13.5" customHeight="1"/>
+    <row r="374" ht="13.5" customHeight="1"/>
+    <row r="375" ht="13.5" customHeight="1"/>
+    <row r="376" ht="13.5" customHeight="1"/>
+    <row r="377" ht="13.5" customHeight="1"/>
+    <row r="378" ht="13.5" customHeight="1"/>
+    <row r="379" ht="13.5" customHeight="1"/>
+    <row r="380" ht="13.5" customHeight="1"/>
+    <row r="381" ht="13.5" customHeight="1"/>
+    <row r="382" ht="13.5" customHeight="1"/>
+    <row r="383" ht="13.5" customHeight="1"/>
+    <row r="384" ht="13.5" customHeight="1"/>
+    <row r="385" ht="13.5" customHeight="1"/>
+    <row r="386" ht="13.5" customHeight="1"/>
+    <row r="387" ht="13.5" customHeight="1"/>
+    <row r="388" ht="13.5" customHeight="1"/>
+    <row r="389" ht="13.5" customHeight="1"/>
+    <row r="390" ht="13.5" customHeight="1"/>
+    <row r="391" ht="13.5" customHeight="1"/>
+    <row r="392" ht="13.5" customHeight="1"/>
+    <row r="393" ht="13.5" customHeight="1"/>
+    <row r="394" ht="13.5" customHeight="1"/>
+    <row r="395" ht="13.5" customHeight="1"/>
+    <row r="396" ht="13.5" customHeight="1"/>
+    <row r="397" ht="13.5" customHeight="1"/>
+    <row r="398" ht="13.5" customHeight="1"/>
+    <row r="399" ht="13.5" customHeight="1"/>
+    <row r="400" ht="13.5" customHeight="1"/>
+    <row r="401" ht="13.5" customHeight="1"/>
+    <row r="402" ht="13.5" customHeight="1"/>
+    <row r="403" ht="13.5" customHeight="1"/>
+    <row r="404" ht="13.5" customHeight="1"/>
+    <row r="405" ht="13.5" customHeight="1"/>
+    <row r="406" ht="13.5" customHeight="1"/>
+    <row r="407" ht="13.5" customHeight="1"/>
+    <row r="408" ht="13.5" customHeight="1"/>
+    <row r="409" ht="13.5" customHeight="1"/>
+    <row r="410" ht="13.5" customHeight="1"/>
+    <row r="411" ht="13.5" customHeight="1"/>
+    <row r="412" ht="13.5" customHeight="1"/>
+    <row r="413" ht="13.5" customHeight="1"/>
+    <row r="414" ht="13.5" customHeight="1"/>
+    <row r="415" ht="13.5" customHeight="1"/>
+    <row r="416" ht="13.5" customHeight="1"/>
+    <row r="417" ht="13.5" customHeight="1"/>
+    <row r="418" ht="13.5" customHeight="1"/>
+    <row r="419" ht="13.5" customHeight="1"/>
+    <row r="420" ht="13.5" customHeight="1"/>
+    <row r="421" ht="13.5" customHeight="1"/>
+    <row r="422" ht="13.5" customHeight="1"/>
+    <row r="423" ht="13.5" customHeight="1"/>
+    <row r="424" ht="13.5" customHeight="1"/>
+    <row r="425" ht="13.5" customHeight="1"/>
+    <row r="426" ht="13.5" customHeight="1"/>
+    <row r="427" ht="13.5" customHeight="1"/>
+    <row r="428" ht="13.5" customHeight="1"/>
+    <row r="429" ht="13.5" customHeight="1"/>
+    <row r="430" ht="13.5" customHeight="1"/>
+    <row r="431" ht="13.5" customHeight="1"/>
+    <row r="432" ht="13.5" customHeight="1"/>
+    <row r="433" ht="13.5" customHeight="1"/>
+    <row r="434" ht="13.5" customHeight="1"/>
+    <row r="435" ht="13.5" customHeight="1"/>
+    <row r="436" ht="13.5" customHeight="1"/>
+    <row r="437" ht="13.5" customHeight="1"/>
+    <row r="438" ht="13.5" customHeight="1"/>
+    <row r="439" ht="13.5" customHeight="1"/>
+    <row r="440" ht="13.5" customHeight="1"/>
+    <row r="441" ht="13.5" customHeight="1"/>
+    <row r="442" ht="13.5" customHeight="1"/>
+    <row r="443" ht="13.5" customHeight="1"/>
+    <row r="444" ht="13.5" customHeight="1"/>
+    <row r="445" ht="13.5" customHeight="1"/>
+    <row r="446" ht="13.5" customHeight="1"/>
+    <row r="447" ht="13.5" customHeight="1"/>
+    <row r="448" ht="13.5" customHeight="1"/>
+    <row r="449" ht="13.5" customHeight="1"/>
+    <row r="450" ht="13.5" customHeight="1"/>
+    <row r="451" ht="13.5" customHeight="1"/>
+    <row r="452" ht="13.5" customHeight="1"/>
+    <row r="453" ht="13.5" customHeight="1"/>
+    <row r="454" ht="13.5" customHeight="1"/>
+    <row r="455" ht="13.5" customHeight="1"/>
+    <row r="456" ht="13.5" customHeight="1"/>
+    <row r="457" ht="13.5" customHeight="1"/>
+    <row r="458" ht="13.5" customHeight="1"/>
+    <row r="459" ht="13.5" customHeight="1"/>
+    <row r="460" ht="13.5" customHeight="1"/>
+    <row r="461" ht="13.5" customHeight="1"/>
+    <row r="462" ht="13.5" customHeight="1"/>
+    <row r="463" ht="13.5" customHeight="1"/>
+    <row r="464" ht="13.5" customHeight="1"/>
+    <row r="465" ht="13.5" customHeight="1"/>
+    <row r="466" ht="13.5" customHeight="1"/>
+    <row r="467" ht="13.5" customHeight="1"/>
+    <row r="468" ht="13.5" customHeight="1"/>
+    <row r="469" ht="13.5" customHeight="1"/>
+    <row r="470" ht="13.5" customHeight="1"/>
+    <row r="471" ht="13.5" customHeight="1"/>
+    <row r="472" ht="13.5" customHeight="1"/>
+    <row r="473" ht="13.5" customHeight="1"/>
+    <row r="474" ht="13.5" customHeight="1"/>
+    <row r="475" ht="13.5" customHeight="1"/>
+    <row r="476" ht="13.5" customHeight="1"/>
+    <row r="477" ht="13.5" customHeight="1"/>
+    <row r="478" ht="13.5" customHeight="1"/>
+    <row r="479" ht="13.5" customHeight="1"/>
+    <row r="480" ht="13.5" customHeight="1"/>
+    <row r="481" ht="13.5" customHeight="1"/>
+    <row r="482" ht="13.5" customHeight="1"/>
+    <row r="483" ht="13.5" customHeight="1"/>
+    <row r="484" ht="13.5" customHeight="1"/>
+    <row r="485" ht="13.5" customHeight="1"/>
+    <row r="486" ht="13.5" customHeight="1"/>
+    <row r="487" ht="13.5" customHeight="1"/>
+    <row r="488" ht="13.5" customHeight="1"/>
+    <row r="489" ht="13.5" customHeight="1"/>
+    <row r="490" ht="13.5" customHeight="1"/>
+    <row r="491" ht="13.5" customHeight="1"/>
+    <row r="492" ht="13.5" customHeight="1"/>
+    <row r="493" ht="13.5" customHeight="1"/>
+    <row r="494" ht="13.5" customHeight="1"/>
+    <row r="495" ht="13.5" customHeight="1"/>
+    <row r="496" ht="13.5" customHeight="1"/>
+    <row r="497" ht="13.5" customHeight="1"/>
+    <row r="498" ht="13.5" customHeight="1"/>
+    <row r="499" ht="13.5" customHeight="1"/>
+    <row r="500" ht="13.5" customHeight="1"/>
+    <row r="501" ht="13.5" customHeight="1"/>
+    <row r="502" ht="13.5" customHeight="1"/>
+    <row r="503" ht="13.5" customHeight="1"/>
+    <row r="504" ht="13.5" customHeight="1"/>
+    <row r="505" ht="13.5" customHeight="1"/>
+    <row r="506" ht="13.5" customHeight="1"/>
+    <row r="507" ht="13.5" customHeight="1"/>
+    <row r="508" ht="13.5" customHeight="1"/>
+    <row r="509" ht="13.5" customHeight="1"/>
+    <row r="510" ht="13.5" customHeight="1"/>
+    <row r="511" ht="13.5" customHeight="1"/>
+    <row r="512" ht="13.5" customHeight="1"/>
+    <row r="513" ht="13.5" customHeight="1"/>
+    <row r="514" ht="13.5" customHeight="1"/>
+    <row r="515" ht="13.5" customHeight="1"/>
+    <row r="516" ht="13.5" customHeight="1"/>
+    <row r="517" ht="13.5" customHeight="1"/>
+    <row r="518" ht="13.5" customHeight="1"/>
+    <row r="519" ht="13.5" customHeight="1"/>
+    <row r="520" ht="13.5" customHeight="1"/>
+    <row r="521" ht="13.5" customHeight="1"/>
+    <row r="522" ht="13.5" customHeight="1"/>
+    <row r="523" ht="13.5" customHeight="1"/>
+    <row r="524" ht="13.5" customHeight="1"/>
+    <row r="525" ht="13.5" customHeight="1"/>
+    <row r="526" ht="13.5" customHeight="1"/>
+    <row r="527" ht="13.5" customHeight="1"/>
+    <row r="528" ht="13.5" customHeight="1"/>
+    <row r="529" ht="13.5" customHeight="1"/>
+    <row r="530" ht="13.5" customHeight="1"/>
+    <row r="531" ht="13.5" customHeight="1"/>
+    <row r="532" ht="13.5" customHeight="1"/>
+    <row r="533" ht="13.5" customHeight="1"/>
+    <row r="534" ht="13.5" customHeight="1"/>
+    <row r="535" ht="13.5" customHeight="1"/>
+    <row r="536" ht="13.5" customHeight="1"/>
+    <row r="537" ht="13.5" customHeight="1"/>
+    <row r="538" ht="13.5" customHeight="1"/>
+    <row r="539" ht="13.5" customHeight="1"/>
+    <row r="540" ht="13.5" customHeight="1"/>
+    <row r="541" ht="13.5" customHeight="1"/>
+    <row r="542" ht="13.5" customHeight="1"/>
+    <row r="543" ht="13.5" customHeight="1"/>
+    <row r="544" ht="13.5" customHeight="1"/>
+    <row r="545" ht="13.5" customHeight="1"/>
+    <row r="546" ht="13.5" customHeight="1"/>
+    <row r="547" ht="13.5" customHeight="1"/>
+    <row r="548" ht="13.5" customHeight="1"/>
+    <row r="549" ht="13.5" customHeight="1"/>
+    <row r="550" ht="13.5" customHeight="1"/>
+    <row r="551" ht="13.5" customHeight="1"/>
+    <row r="552" ht="13.5" customHeight="1"/>
+    <row r="553" ht="13.5" customHeight="1"/>
+    <row r="554" ht="13.5" customHeight="1"/>
+    <row r="555" ht="13.5" customHeight="1"/>
+    <row r="556" ht="13.5" customHeight="1"/>
+    <row r="557" ht="13.5" customHeight="1"/>
+    <row r="558" ht="13.5" customHeight="1"/>
+    <row r="559" ht="13.5" customHeight="1"/>
+    <row r="560" ht="13.5" customHeight="1"/>
+    <row r="561" ht="13.5" customHeight="1"/>
+    <row r="562" ht="13.5" customHeight="1"/>
+    <row r="563" ht="13.5" customHeight="1"/>
+    <row r="564" ht="13.5" customHeight="1"/>
+    <row r="565" ht="13.5" customHeight="1"/>
+    <row r="566" ht="13.5" customHeight="1"/>
+    <row r="567" ht="13.5" customHeight="1"/>
+    <row r="568" ht="13.5" customHeight="1"/>
+    <row r="569" ht="13.5" customHeight="1"/>
+    <row r="570" ht="13.5" customHeight="1"/>
+    <row r="571" ht="13.5" customHeight="1"/>
+    <row r="572" ht="13.5" customHeight="1"/>
+    <row r="573" ht="13.5" customHeight="1"/>
+    <row r="574" ht="13.5" customHeight="1"/>
+    <row r="575" ht="13.5" customHeight="1"/>
+    <row r="576" ht="13.5" customHeight="1"/>
+    <row r="577" ht="13.5" customHeight="1"/>
+    <row r="578" ht="13.5" customHeight="1"/>
+    <row r="579" ht="13.5" customHeight="1"/>
+    <row r="580" ht="13.5" customHeight="1"/>
+    <row r="581" ht="13.5" customHeight="1"/>
+    <row r="582" ht="13.5" customHeight="1"/>
+    <row r="583" ht="13.5" customHeight="1"/>
+    <row r="584" ht="13.5" customHeight="1"/>
+    <row r="585" ht="13.5" customHeight="1"/>
+    <row r="586" ht="13.5" customHeight="1"/>
+    <row r="587" ht="13.5" customHeight="1"/>
+    <row r="588" ht="13.5" customHeight="1"/>
+    <row r="589" ht="13.5" customHeight="1"/>
+    <row r="590" ht="13.5" customHeight="1"/>
+    <row r="591" ht="13.5" customHeight="1"/>
+    <row r="592" ht="13.5" customHeight="1"/>
+    <row r="593" ht="13.5" customHeight="1"/>
+    <row r="594" ht="13.5" customHeight="1"/>
+    <row r="595" ht="13.5" customHeight="1"/>
+    <row r="596" ht="13.5" customHeight="1"/>
+    <row r="597" ht="13.5" customHeight="1"/>
+    <row r="598" ht="13.5" customHeight="1"/>
+    <row r="599" ht="13.5" customHeight="1"/>
+    <row r="600" ht="13.5" customHeight="1"/>
+    <row r="601" ht="13.5" customHeight="1"/>
+    <row r="602" ht="13.5" customHeight="1"/>
+    <row r="603" ht="13.5" customHeight="1"/>
+    <row r="604" ht="13.5" customHeight="1"/>
+    <row r="605" ht="13.5" customHeight="1"/>
+    <row r="606" ht="13.5" customHeight="1"/>
+    <row r="607" ht="13.5" customHeight="1"/>
+    <row r="608" ht="13.5" customHeight="1"/>
+    <row r="609" ht="13.5" customHeight="1"/>
+    <row r="610" ht="13.5" customHeight="1"/>
+    <row r="611" ht="13.5" customHeight="1"/>
+    <row r="612" ht="13.5" customHeight="1"/>
+    <row r="613" ht="13.5" customHeight="1"/>
+    <row r="614" ht="13.5" customHeight="1"/>
+    <row r="615" ht="13.5" customHeight="1"/>
+    <row r="616" ht="13.5" customHeight="1"/>
+    <row r="617" ht="13.5" customHeight="1"/>
+    <row r="618" ht="13.5" customHeight="1"/>
+    <row r="619" ht="13.5" customHeight="1"/>
+    <row r="620" ht="13.5" customHeight="1"/>
+    <row r="621" ht="13.5" customHeight="1"/>
+    <row r="622" ht="13.5" customHeight="1"/>
+    <row r="623" ht="13.5" customHeight="1"/>
+    <row r="624" ht="13.5" customHeight="1"/>
+    <row r="625" ht="13.5" customHeight="1"/>
+    <row r="626" ht="13.5" customHeight="1"/>
+    <row r="627" ht="13.5" customHeight="1"/>
+    <row r="628" ht="13.5" customHeight="1"/>
+    <row r="629" ht="13.5" customHeight="1"/>
+    <row r="630" ht="13.5" customHeight="1"/>
+    <row r="631" ht="13.5" customHeight="1"/>
+    <row r="632" ht="13.5" customHeight="1"/>
+    <row r="633" ht="13.5" customHeight="1"/>
+    <row r="634" ht="13.5" customHeight="1"/>
+    <row r="635" ht="13.5" customHeight="1"/>
+    <row r="636" ht="13.5" customHeight="1"/>
+    <row r="637" ht="13.5" customHeight="1"/>
+    <row r="638" ht="13.5" customHeight="1"/>
+    <row r="639" ht="13.5" customHeight="1"/>
+    <row r="640" ht="13.5" customHeight="1"/>
+    <row r="641" ht="13.5" customHeight="1"/>
+    <row r="642" ht="13.5" customHeight="1"/>
+    <row r="643" ht="13.5" customHeight="1"/>
+    <row r="644" ht="13.5" customHeight="1"/>
+    <row r="645" ht="13.5" customHeight="1"/>
+    <row r="646" ht="13.5" customHeight="1"/>
+    <row r="647" ht="13.5" customHeight="1"/>
+    <row r="648" ht="13.5" customHeight="1"/>
+    <row r="649" ht="13.5" customHeight="1"/>
+    <row r="650" ht="13.5" customHeight="1"/>
+    <row r="651" ht="13.5" customHeight="1"/>
+    <row r="652" ht="13.5" customHeight="1"/>
+    <row r="653" ht="13.5" customHeight="1"/>
+    <row r="654" ht="13.5" customHeight="1"/>
+    <row r="655" ht="13.5" customHeight="1"/>
+    <row r="656" ht="13.5" customHeight="1"/>
+    <row r="657" ht="13.5" customHeight="1"/>
+    <row r="658" ht="13.5" customHeight="1"/>
+    <row r="659" ht="13.5" customHeight="1"/>
+    <row r="660" ht="13.5" customHeight="1"/>
+    <row r="661" ht="13.5" customHeight="1"/>
+    <row r="662" ht="13.5" customHeight="1"/>
+    <row r="663" ht="13.5" customHeight="1"/>
+    <row r="664" ht="13.5" customHeight="1"/>
+    <row r="665" ht="13.5" customHeight="1"/>
+    <row r="666" ht="13.5" customHeight="1"/>
+    <row r="667" ht="13.5" customHeight="1"/>
+    <row r="668" ht="13.5" customHeight="1"/>
+    <row r="669" ht="13.5" customHeight="1"/>
+    <row r="670" ht="13.5" customHeight="1"/>
+    <row r="671" ht="13.5" customHeight="1"/>
+    <row r="672" ht="13.5" customHeight="1"/>
+    <row r="673" ht="13.5" customHeight="1"/>
+    <row r="674" ht="13.5" customHeight="1"/>
+    <row r="675" ht="13.5" customHeight="1"/>
+    <row r="676" ht="13.5" customHeight="1"/>
+    <row r="677" ht="13.5" customHeight="1"/>
+    <row r="678" ht="13.5" customHeight="1"/>
+    <row r="679" ht="13.5" customHeight="1"/>
+    <row r="680" ht="13.5" customHeight="1"/>
+    <row r="681" ht="13.5" customHeight="1"/>
+    <row r="682" ht="13.5" customHeight="1"/>
+    <row r="683" ht="13.5" customHeight="1"/>
+    <row r="684" ht="13.5" customHeight="1"/>
+    <row r="685" ht="13.5" customHeight="1"/>
+    <row r="686" ht="13.5" customHeight="1"/>
+    <row r="687" ht="13.5" customHeight="1"/>
+    <row r="688" ht="13.5" customHeight="1"/>
+    <row r="689" ht="13.5" customHeight="1"/>
+    <row r="690" ht="13.5" customHeight="1"/>
+    <row r="691" ht="13.5" customHeight="1"/>
+    <row r="692" ht="13.5" customHeight="1"/>
+    <row r="693" ht="13.5" customHeight="1"/>
+    <row r="694" ht="13.5" customHeight="1"/>
+    <row r="695" ht="13.5" customHeight="1"/>
+    <row r="696" ht="13.5" customHeight="1"/>
+    <row r="697" ht="13.5" customHeight="1"/>
+    <row r="698" ht="13.5" customHeight="1"/>
+    <row r="699" ht="13.5" customHeight="1"/>
+    <row r="700" ht="13.5" customHeight="1"/>
+    <row r="701" ht="13.5" customHeight="1"/>
+    <row r="702" ht="13.5" customHeight="1"/>
+    <row r="703" ht="13.5" customHeight="1"/>
+    <row r="704" ht="13.5" customHeight="1"/>
+    <row r="705" ht="13.5" customHeight="1"/>
+    <row r="706" ht="13.5" customHeight="1"/>
+    <row r="707" ht="13.5" customHeight="1"/>
+    <row r="708" ht="13.5" customHeight="1"/>
+    <row r="709" ht="13.5" customHeight="1"/>
+    <row r="710" ht="13.5" customHeight="1"/>
+    <row r="711" ht="13.5" customHeight="1"/>
+    <row r="712" ht="13.5" customHeight="1"/>
+    <row r="713" ht="13.5" customHeight="1"/>
+    <row r="714" ht="13.5" customHeight="1"/>
+    <row r="715" ht="13.5" customHeight="1"/>
+    <row r="716" ht="13.5" customHeight="1"/>
+    <row r="717" ht="13.5" customHeight="1"/>
+    <row r="718" ht="13.5" customHeight="1"/>
+    <row r="719" ht="13.5" customHeight="1"/>
+    <row r="720" ht="13.5" customHeight="1"/>
+    <row r="721" ht="13.5" customHeight="1"/>
+    <row r="722" ht="13.5" customHeight="1"/>
+    <row r="723" ht="13.5" customHeight="1"/>
+    <row r="724" ht="13.5" customHeight="1"/>
+    <row r="725" ht="13.5" customHeight="1"/>
+    <row r="726" ht="13.5" customHeight="1"/>
+    <row r="727" ht="13.5" customHeight="1"/>
+    <row r="728" ht="13.5" customHeight="1"/>
+    <row r="729" ht="13.5" customHeight="1"/>
+    <row r="730" ht="13.5" customHeight="1"/>
+    <row r="731" ht="13.5" customHeight="1"/>
+    <row r="732" ht="13.5" customHeight="1"/>
+    <row r="733" ht="13.5" customHeight="1"/>
+    <row r="734" ht="13.5" customHeight="1"/>
+    <row r="735" ht="13.5" customHeight="1"/>
+    <row r="736" ht="13.5" customHeight="1"/>
+    <row r="737" ht="13.5" customHeight="1"/>
+    <row r="738" ht="13.5" customHeight="1"/>
+    <row r="739" ht="13.5" customHeight="1"/>
+    <row r="740" ht="13.5" customHeight="1"/>
+    <row r="741" ht="13.5" customHeight="1"/>
+    <row r="742" ht="13.5" customHeight="1"/>
+    <row r="743" ht="13.5" customHeight="1"/>
+    <row r="744" ht="13.5" customHeight="1"/>
+    <row r="745" ht="13.5" customHeight="1"/>
+    <row r="746" ht="13.5" customHeight="1"/>
+    <row r="747" ht="13.5" customHeight="1"/>
+    <row r="748" ht="13.5" customHeight="1"/>
+    <row r="749" ht="13.5" customHeight="1"/>
+    <row r="750" ht="13.5" customHeight="1"/>
+    <row r="751" ht="13.5" customHeight="1"/>
+    <row r="752" ht="13.5" customHeight="1"/>
+    <row r="753" ht="13.5" customHeight="1"/>
+    <row r="754" ht="13.5" customHeight="1"/>
+    <row r="755" ht="13.5" customHeight="1"/>
+    <row r="756" ht="13.5" customHeight="1"/>
+    <row r="757" ht="13.5" customHeight="1"/>
+    <row r="758" ht="13.5" customHeight="1"/>
+    <row r="759" ht="13.5" customHeight="1"/>
+    <row r="760" ht="13.5" customHeight="1"/>
+    <row r="761" ht="13.5" customHeight="1"/>
+    <row r="762" ht="13.5" customHeight="1"/>
+    <row r="763" ht="13.5" customHeight="1"/>
+    <row r="764" ht="13.5" customHeight="1"/>
+    <row r="765" ht="13.5" customHeight="1"/>
+    <row r="766" ht="13.5" customHeight="1"/>
+    <row r="767" ht="13.5" customHeight="1"/>
+    <row r="768" ht="13.5" customHeight="1"/>
+    <row r="769" ht="13.5" customHeight="1"/>
+    <row r="770" ht="13.5" customHeight="1"/>
+    <row r="771" ht="13.5" customHeight="1"/>
+    <row r="772" ht="13.5" customHeight="1"/>
+    <row r="773" ht="13.5" customHeight="1"/>
+    <row r="774" ht="13.5" customHeight="1"/>
+    <row r="775" ht="13.5" customHeight="1"/>
+    <row r="776" ht="13.5" customHeight="1"/>
+    <row r="777" ht="13.5" customHeight="1"/>
+    <row r="778" ht="13.5" customHeight="1"/>
+    <row r="779" ht="13.5" customHeight="1"/>
+    <row r="780" ht="13.5" customHeight="1"/>
+    <row r="781" ht="13.5" customHeight="1"/>
+    <row r="782" ht="13.5" customHeight="1"/>
+    <row r="783" ht="13.5" customHeight="1"/>
+    <row r="784" ht="13.5" customHeight="1"/>
+    <row r="785" ht="13.5" customHeight="1"/>
+    <row r="786" ht="13.5" customHeight="1"/>
+    <row r="787" ht="13.5" customHeight="1"/>
+    <row r="788" ht="13.5" customHeight="1"/>
+    <row r="789" ht="13.5" customHeight="1"/>
+    <row r="790" ht="13.5" customHeight="1"/>
+    <row r="791" ht="13.5" customHeight="1"/>
+    <row r="792" ht="13.5" customHeight="1"/>
+    <row r="793" ht="13.5" customHeight="1"/>
+    <row r="794" ht="13.5" customHeight="1"/>
+    <row r="795" ht="13.5" customHeight="1"/>
+    <row r="796" ht="13.5" customHeight="1"/>
+    <row r="797" ht="13.5" customHeight="1"/>
+    <row r="798" ht="13.5" customHeight="1"/>
+    <row r="799" ht="13.5" customHeight="1"/>
+    <row r="800" ht="13.5" customHeight="1"/>
+    <row r="801" ht="13.5" customHeight="1"/>
+    <row r="802" ht="13.5" customHeight="1"/>
+    <row r="803" ht="13.5" customHeight="1"/>
+    <row r="804" ht="13.5" customHeight="1"/>
+    <row r="805" ht="13.5" customHeight="1"/>
+    <row r="806" ht="13.5" customHeight="1"/>
+    <row r="807" ht="13.5" customHeight="1"/>
+    <row r="808" ht="13.5" customHeight="1"/>
+    <row r="809" ht="13.5" customHeight="1"/>
+    <row r="810" ht="13.5" customHeight="1"/>
+    <row r="811" ht="13.5" customHeight="1"/>
+    <row r="812" ht="13.5" customHeight="1"/>
+    <row r="813" ht="13.5" customHeight="1"/>
+    <row r="814" ht="13.5" customHeight="1"/>
+    <row r="815" ht="13.5" customHeight="1"/>
+    <row r="816" ht="13.5" customHeight="1"/>
+    <row r="817" ht="13.5" customHeight="1"/>
+    <row r="818" ht="13.5" customHeight="1"/>
+    <row r="819" ht="13.5" customHeight="1"/>
+    <row r="820" ht="13.5" customHeight="1"/>
+    <row r="821" ht="13.5" customHeight="1"/>
+    <row r="822" ht="13.5" customHeight="1"/>
+    <row r="823" ht="13.5" customHeight="1"/>
+    <row r="824" ht="13.5" customHeight="1"/>
+    <row r="825" ht="13.5" customHeight="1"/>
+    <row r="826" ht="13.5" customHeight="1"/>
+    <row r="827" ht="13.5" customHeight="1"/>
+    <row r="828" ht="13.5" customHeight="1"/>
+    <row r="829" ht="13.5" customHeight="1"/>
+    <row r="830" ht="13.5" customHeight="1"/>
+    <row r="831" ht="13.5" customHeight="1"/>
+    <row r="832" ht="13.5" customHeight="1"/>
+    <row r="833" ht="13.5" customHeight="1"/>
+    <row r="834" ht="13.5" customHeight="1"/>
+    <row r="835" ht="13.5" customHeight="1"/>
+    <row r="836" ht="13.5" customHeight="1"/>
+    <row r="837" ht="13.5" customHeight="1"/>
+    <row r="838" ht="13.5" customHeight="1"/>
+    <row r="839" ht="13.5" customHeight="1"/>
+    <row r="840" ht="13.5" customHeight="1"/>
+    <row r="841" ht="13.5" customHeight="1"/>
+    <row r="842" ht="13.5" customHeight="1"/>
+    <row r="843" ht="13.5" customHeight="1"/>
+    <row r="844" ht="13.5" customHeight="1"/>
+    <row r="845" ht="13.5" customHeight="1"/>
+    <row r="846" ht="13.5" customHeight="1"/>
+    <row r="847" ht="13.5" customHeight="1"/>
+    <row r="848" ht="13.5" customHeight="1"/>
+    <row r="849" ht="13.5" customHeight="1"/>
+    <row r="850" ht="13.5" customHeight="1"/>
+    <row r="851" ht="13.5" customHeight="1"/>
+    <row r="852" ht="13.5" customHeight="1"/>
+    <row r="853" ht="13.5" customHeight="1"/>
+    <row r="854" ht="13.5" customHeight="1"/>
+    <row r="855" ht="13.5" customHeight="1"/>
+    <row r="856" ht="13.5" customHeight="1"/>
+    <row r="857" ht="13.5" customHeight="1"/>
+    <row r="858" ht="13.5" customHeight="1"/>
+    <row r="859" ht="13.5" customHeight="1"/>
+    <row r="860" ht="13.5" customHeight="1"/>
+    <row r="861" ht="13.5" customHeight="1"/>
+    <row r="862" ht="13.5" customHeight="1"/>
+    <row r="863" ht="13.5" customHeight="1"/>
+    <row r="864" ht="13.5" customHeight="1"/>
+    <row r="865" ht="13.5" customHeight="1"/>
+    <row r="866" ht="13.5" customHeight="1"/>
+    <row r="867" ht="13.5" customHeight="1"/>
+    <row r="868" ht="13.5" customHeight="1"/>
+    <row r="869" ht="13.5" customHeight="1"/>
+    <row r="870" ht="13.5" customHeight="1"/>
+    <row r="871" ht="13.5" customHeight="1"/>
+    <row r="872" ht="13.5" customHeight="1"/>
+    <row r="873" ht="13.5" customHeight="1"/>
+    <row r="874" ht="13.5" customHeight="1"/>
+    <row r="875" ht="13.5" customHeight="1"/>
+    <row r="876" ht="13.5" customHeight="1"/>
+    <row r="877" ht="13.5" customHeight="1"/>
+    <row r="878" ht="13.5" customHeight="1"/>
+    <row r="879" ht="13.5" customHeight="1"/>
+    <row r="880" ht="13.5" customHeight="1"/>
+    <row r="881" ht="13.5" customHeight="1"/>
+    <row r="882" ht="13.5" customHeight="1"/>
+    <row r="883" ht="13.5" customHeight="1"/>
+    <row r="884" ht="13.5" customHeight="1"/>
+    <row r="885" ht="13.5" customHeight="1"/>
+    <row r="886" ht="13.5" customHeight="1"/>
+    <row r="887" ht="13.5" customHeight="1"/>
+    <row r="888" ht="13.5" customHeight="1"/>
+    <row r="889" ht="13.5" customHeight="1"/>
+    <row r="890" ht="13.5" customHeight="1"/>
+    <row r="891" ht="13.5" customHeight="1"/>
+    <row r="892" ht="13.5" customHeight="1"/>
+    <row r="893" ht="13.5" customHeight="1"/>
+    <row r="894" ht="13.5" customHeight="1"/>
+    <row r="895" ht="13.5" customHeight="1"/>
+    <row r="896" ht="13.5" customHeight="1"/>
+    <row r="897" ht="13.5" customHeight="1"/>
+    <row r="898" ht="13.5" customHeight="1"/>
+    <row r="899" ht="13.5" customHeight="1"/>
+    <row r="900" ht="13.5" customHeight="1"/>
+    <row r="901" ht="13.5" customHeight="1"/>
+    <row r="902" ht="13.5" customHeight="1"/>
+    <row r="903" ht="13.5" customHeight="1"/>
+    <row r="904" ht="13.5" customHeight="1"/>
+    <row r="905" ht="13.5" customHeight="1"/>
+    <row r="906" ht="13.5" customHeight="1"/>
+    <row r="907" ht="13.5" customHeight="1"/>
+    <row r="908" ht="13.5" customHeight="1"/>
+    <row r="909" ht="13.5" customHeight="1"/>
+    <row r="910" ht="13.5" customHeight="1"/>
+    <row r="911" ht="13.5" customHeight="1"/>
+    <row r="912" ht="13.5" customHeight="1"/>
+    <row r="913" ht="13.5" customHeight="1"/>
+    <row r="914" ht="13.5" customHeight="1"/>
+    <row r="915" ht="13.5" customHeight="1"/>
+    <row r="916" ht="13.5" customHeight="1"/>
+    <row r="917" ht="13.5" customHeight="1"/>
+    <row r="918" ht="13.5" customHeight="1"/>
+    <row r="919" ht="13.5" customHeight="1"/>
+    <row r="920" ht="13.5" customHeight="1"/>
+    <row r="921" ht="13.5" customHeight="1"/>
+    <row r="922" ht="13.5" customHeight="1"/>
+    <row r="923" ht="13.5" customHeight="1"/>
+    <row r="924" ht="13.5" customHeight="1"/>
+    <row r="925" ht="13.5" customHeight="1"/>
+    <row r="926" ht="13.5" customHeight="1"/>
+    <row r="927" ht="13.5" customHeight="1"/>
+    <row r="928" ht="13.5" customHeight="1"/>
+    <row r="929" ht="13.5" customHeight="1"/>
+    <row r="930" ht="13.5" customHeight="1"/>
+    <row r="931" ht="13.5" customHeight="1"/>
+    <row r="932" ht="13.5" customHeight="1"/>
+    <row r="933" ht="13.5" customHeight="1"/>
+    <row r="934" ht="13.5" customHeight="1"/>
+    <row r="935" ht="13.5" customHeight="1"/>
+    <row r="936" ht="13.5" customHeight="1"/>
+    <row r="937" ht="13.5" customHeight="1"/>
+    <row r="938" ht="13.5" customHeight="1"/>
+    <row r="939" ht="13.5" customHeight="1"/>
+    <row r="940" ht="13.5" customHeight="1"/>
+    <row r="941" ht="13.5" customHeight="1"/>
+    <row r="942" ht="13.5" customHeight="1"/>
+    <row r="943" ht="13.5" customHeight="1"/>
+    <row r="944" ht="13.5" customHeight="1"/>
+    <row r="945" ht="13.5" customHeight="1"/>
+    <row r="946" ht="13.5" customHeight="1"/>
+    <row r="947" ht="13.5" customHeight="1"/>
+    <row r="948" ht="13.5" customHeight="1"/>
+    <row r="949" ht="13.5" customHeight="1"/>
+    <row r="950" ht="13.5" customHeight="1"/>
+    <row r="951" ht="13.5" customHeight="1"/>
+    <row r="952" ht="13.5" customHeight="1"/>
+    <row r="953" ht="13.5" customHeight="1"/>
+    <row r="954" ht="13.5" customHeight="1"/>
+    <row r="955" ht="13.5" customHeight="1"/>
+    <row r="956" ht="13.5" customHeight="1"/>
+    <row r="957" ht="13.5" customHeight="1"/>
+    <row r="958" ht="13.5" customHeight="1"/>
+    <row r="959" ht="13.5" customHeight="1"/>
+    <row r="960" ht="13.5" customHeight="1"/>
+    <row r="961" ht="13.5" customHeight="1"/>
+    <row r="962" ht="13.5" customHeight="1"/>
+    <row r="963" ht="13.5" customHeight="1"/>
+    <row r="964" ht="13.5" customHeight="1"/>
+    <row r="965" ht="13.5" customHeight="1"/>
+    <row r="966" ht="13.5" customHeight="1"/>
+    <row r="967" ht="13.5" customHeight="1"/>
+    <row r="968" ht="13.5" customHeight="1"/>
+    <row r="969" ht="13.5" customHeight="1"/>
+    <row r="970" ht="13.5" customHeight="1"/>
+    <row r="971" ht="13.5" customHeight="1"/>
+    <row r="972" ht="13.5" customHeight="1"/>
+    <row r="973" ht="13.5" customHeight="1"/>
+    <row r="974" ht="13.5" customHeight="1"/>
+    <row r="975" ht="13.5" customHeight="1"/>
+    <row r="976" ht="13.5" customHeight="1"/>
+    <row r="977" ht="13.5" customHeight="1"/>
+    <row r="978" ht="13.5" customHeight="1"/>
+    <row r="979" ht="13.5" customHeight="1"/>
+    <row r="980" ht="13.5" customHeight="1"/>
+    <row r="981" ht="13.5" customHeight="1"/>
+    <row r="982" ht="13.5" customHeight="1"/>
+    <row r="983" ht="13.5" customHeight="1"/>
+    <row r="984" ht="13.5" customHeight="1"/>
+    <row r="985" ht="13.5" customHeight="1"/>
+    <row r="986" ht="13.5" customHeight="1"/>
+    <row r="987" ht="13.5" customHeight="1"/>
+    <row r="988" ht="13.5" customHeight="1"/>
+    <row r="989" ht="13.5" customHeight="1"/>
+    <row r="990" ht="13.5" customHeight="1"/>
+    <row r="991" ht="13.5" customHeight="1"/>
+    <row r="992" ht="13.5" customHeight="1"/>
+    <row r="993" ht="13.5" customHeight="1"/>
+    <row r="994" ht="13.5" customHeight="1"/>
+    <row r="995" ht="13.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48.44140625" customWidth="1" min="1" max="1"/>
+    <col width="12.6640625" customWidth="1" min="2" max="2"/>
+    <col width="11.33203125" customWidth="1" min="6" max="6"/>
+    <col width="8.88671875" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>Chỉ tiêu</t>
+        </is>
+      </c>
+      <c r="B1" s="29" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C1" s="29" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D1" s="29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E1" s="29" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F1" s="29" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Doanh thu kế hoạch</t>
+        </is>
+      </c>
+      <c r="B2" s="34" t="n">
+        <v>27000000</v>
+      </c>
+      <c r="C2" s="34" t="n">
+        <v>34000000</v>
+      </c>
+      <c r="D2" s="34" t="n">
+        <v>37300000</v>
+      </c>
+      <c r="E2" s="34" t="n">
+        <v>48100000</v>
+      </c>
+      <c r="F2" s="34" t="n">
+        <v>59500</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>Doanh thu thuần về bán hàng và cung cấp dịch vụ</t>
+        </is>
+      </c>
+      <c r="B3" s="34">
+        <f>[2]KQHĐKD!F4*1000</f>
+        <v/>
+      </c>
+      <c r="C3" s="34">
+        <f>[2]KQHĐKD!G4*1000</f>
+        <v/>
+      </c>
+      <c r="D3" s="34">
+        <f>[2]KQHĐKD!H4*1000</f>
+        <v/>
+      </c>
+      <c r="E3" s="34" t="n">
+        <v>59500000</v>
+      </c>
+      <c r="F3" s="29" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>%thực hiện</t>
+        </is>
+      </c>
+      <c r="B4" s="38">
+        <f>B3/B2</f>
+        <v/>
+      </c>
+      <c r="C4" s="38">
+        <f>C3/C2</f>
+        <v/>
+      </c>
+      <c r="D4" s="38">
+        <f>D3/D2</f>
+        <v/>
+      </c>
+      <c r="E4" s="38">
+        <f>E3/E2</f>
+        <v/>
+      </c>
+      <c r="F4" s="29" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>Lợi nhuận trước thuế kế hoạch</t>
+        </is>
+      </c>
+      <c r="B5" s="34" t="n">
+        <v>720000</v>
+      </c>
+      <c r="C5" s="34" t="n">
+        <v>240000</v>
+      </c>
+      <c r="D5" s="34" t="n">
+        <v>125000</v>
+      </c>
+      <c r="E5" s="34" t="n">
+        <v>900000</v>
+      </c>
+      <c r="F5" s="34" t="n">
+        <v>1550000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>Lợi nhuận trước thuế thu nhập doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="B6" s="34">
+        <f>[2]KQHĐKD!F18*1000</f>
+        <v/>
+      </c>
+      <c r="C6" s="34">
+        <f>[2]KQHĐKD!G18*1000</f>
+        <v/>
+      </c>
+      <c r="D6" s="34">
+        <f>[2]KQHĐKD!H18*1000</f>
+        <v/>
+      </c>
+      <c r="E6" s="34" t="n">
+        <v>1219117.502673</v>
+      </c>
+      <c r="F6" s="29" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>%thực hiện</t>
+        </is>
+      </c>
+      <c r="B7" s="38">
+        <f>B6/B5</f>
+        <v/>
+      </c>
+      <c r="C7" s="38">
+        <f>C6/C5</f>
+        <v/>
+      </c>
+      <c r="D7" s="38">
+        <f>D6/D5</f>
+        <v/>
+      </c>
+      <c r="E7" s="38">
+        <f>E6/E5</f>
+        <v/>
+      </c>
+      <c r="F7" s="29" t="n"/>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>Trung vị %thực hiện DT</t>
+        </is>
+      </c>
+      <c r="B9" s="38">
+        <f>MEDIAN(B4:D4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Trung vị %thực hiện LNST</t>
+        </is>
+      </c>
+      <c r="B10" s="38">
+        <f>MEDIAN(B7:D7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành DT trên 95%</t>
+        </is>
+      </c>
+      <c r="B12" s="38">
+        <f>COUNTIF(B4:E4,"&gt;=95%")/COUNT(B4:E4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành LNST trên 95%</t>
+        </is>
+      </c>
+      <c r="B13" s="38">
+        <f>COUNTIF(B7:F7,"&gt;=95%")/COUNT(B7:F7)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B9:B10">
+    <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="3">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:E4 B7:E7">
+    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" dxfId="3">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/financials/FRT/FRT.xlsx
+++ b/financials/FRT/FRT.xlsx
@@ -12,6 +12,7 @@
     <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Dự báo tăng trưởng" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Hiệu quả thực hiện kế hoạch" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,16 +27,13 @@
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="167" formatCode="0.00\x"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Tahoma"/>
@@ -48,14 +46,12 @@
     </font>
     <font>
       <name val="Tahoma"/>
-      <charset val="1"/>
       <family val="2"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Tahoma"/>
-      <charset val="1"/>
       <family val="2"/>
       <i val="1"/>
       <color rgb="FF808080"/>
@@ -63,20 +59,17 @@
     </font>
     <font>
       <name val="Tahoma"/>
-      <charset val="1"/>
       <family val="2"/>
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Tahoma"/>
-      <charset val="1"/>
       <family val="2"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Tahoma"/>
-      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="10"/>
@@ -85,19 +78,44 @@
       <name val="Tahoma"/>
       <charset val="1"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <family val="2"/>
       <color rgb="FF008000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF7030A0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
       <family val="2"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <color rgb="FF7030A0"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -111,24 +129,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.7999816888943144"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
         <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -178,45 +196,59 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="41" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
@@ -235,6 +267,14 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6604,14 +6644,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40.77734375" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="3" customWidth="1" min="10" max="10"/>
+    <col width="40.75" customWidth="1" min="1" max="1"/>
+    <col width="17.25" customWidth="1" min="2" max="2"/>
+    <col width="18.25" customWidth="1" min="9" max="9"/>
+    <col width="20.5" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="8.875" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6652,6 +6693,9 @@
         <f>balance_sheet!I1</f>
         <v/>
       </c>
+      <c r="J1" s="6" t="n">
+        <v>2026</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -6665,31 +6709,31 @@
         </is>
       </c>
       <c r="C2" s="8">
-        <f>IFERROR(C$39/((C$24+B$24)/2),"n/a")</f>
+        <f>IFERROR(C$52/((C$39+B$39)/2),"n/a")</f>
         <v/>
       </c>
       <c r="D2" s="8">
-        <f>IFERROR(D$39/((D$24+C$24)/2),"n/a")</f>
+        <f>IFERROR(D$52/((D$39+C$39)/2),"n/a")</f>
         <v/>
       </c>
       <c r="E2" s="8">
-        <f>IFERROR(E$39/((E$24+D$24)/2),"n/a")</f>
+        <f>IFERROR(E$52/((E$39+D$39)/2),"n/a")</f>
         <v/>
       </c>
       <c r="F2" s="8">
-        <f>IFERROR(F$39/((F$24+E$24)/2),"n/a")</f>
+        <f>IFERROR(F$52/((F$39+E$39)/2),"n/a")</f>
         <v/>
       </c>
       <c r="G2" s="8">
-        <f>IFERROR(G$39/((G$24+F$24)/2),"n/a")</f>
+        <f>IFERROR(G$52/((G$39+F$39)/2),"n/a")</f>
         <v/>
       </c>
       <c r="H2" s="8">
-        <f>IFERROR(H$39/((H$24+G$24)/2),"n/a")</f>
+        <f>IFERROR(H$52/((H$39+G$39)/2),"n/a")</f>
         <v/>
       </c>
       <c r="I2" s="8">
-        <f>IFERROR(I$39/((I$24+H$24)/2),"n/a")</f>
+        <f>IFERROR(I$52/((I$39+H$39)/2),"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6705,31 +6749,31 @@
         </is>
       </c>
       <c r="C3" s="8">
-        <f>IFERROR(C$38/((C$25+B$25)/2),"n/a")</f>
+        <f>IFERROR(C$51/((C$31+B$31)/2),"n/a")</f>
         <v/>
       </c>
       <c r="D3" s="8">
-        <f>IFERROR(D$38/((D$25+C$25)/2),"n/a")</f>
+        <f>IFERROR(D$51/((D$31+C$31)/2),"n/a")</f>
         <v/>
       </c>
       <c r="E3" s="8">
-        <f>IFERROR(E$38/((E$25+D$25)/2),"n/a")</f>
+        <f>IFERROR(E$51/((E$31+D$31)/2),"n/a")</f>
         <v/>
       </c>
       <c r="F3" s="8">
-        <f>IFERROR(F$38/((F$25+E$25)/2),"n/a")</f>
+        <f>IFERROR(F$51/((F$31+E$31)/2),"n/a")</f>
         <v/>
       </c>
       <c r="G3" s="8">
-        <f>IFERROR(G$38/((G$25+F$25)/2),"n/a")</f>
+        <f>IFERROR(G$51/((G$31+F$31)/2),"n/a")</f>
         <v/>
       </c>
       <c r="H3" s="8">
-        <f>IFERROR(H$38/((H$25+G$25)/2),"n/a")</f>
+        <f>IFERROR(H$51/((H$31+G$31)/2),"n/a")</f>
         <v/>
       </c>
       <c r="I3" s="8">
-        <f>IFERROR(I$38/((I$25+H$25)/2),"n/a")</f>
+        <f>IFERROR(I$51/((I$31+H$31)/2),"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6745,31 +6789,35 @@
         </is>
       </c>
       <c r="C4" s="8">
-        <f>IFERROR((C$39-B$39)/ABS(B$39),"n/a")</f>
+        <f>IFERROR((C$52-B$52)/ABS(B$52),"n/a")</f>
         <v/>
       </c>
       <c r="D4" s="8">
-        <f>IFERROR((D$39-C$39)/ABS(C$39),"n/a")</f>
+        <f>IFERROR((D$52-C$52)/ABS(C$52),"n/a")</f>
         <v/>
       </c>
       <c r="E4" s="8">
-        <f>IFERROR((E$39-D$39)/ABS(D$39),"n/a")</f>
+        <f>IFERROR((E$52-D$52)/ABS(D$52),"n/a")</f>
         <v/>
       </c>
       <c r="F4" s="8">
-        <f>IFERROR((F$39-E$39)/ABS(E$39),"n/a")</f>
+        <f>IFERROR((F$52-E$52)/ABS(E$52),"n/a")</f>
         <v/>
       </c>
       <c r="G4" s="8">
-        <f>IFERROR((G$39-F$39)/ABS(F$39),"n/a")</f>
+        <f>IFERROR((G$52-F$52)/ABS(F$52),"n/a")</f>
         <v/>
       </c>
       <c r="H4" s="8">
-        <f>IFERROR((H$39-G$39)/ABS(G$39),"n/a")</f>
+        <f>IFERROR((H$52-G$52)/ABS(G$52),"n/a")</f>
         <v/>
       </c>
       <c r="I4" s="8">
-        <f>IFERROR((I$39-H$39)/ABS(H$39),"n/a")</f>
+        <f>IFERROR((I$52-H$52)/ABS(H$52),"n/a")</f>
+        <v/>
+      </c>
+      <c r="J4" s="8">
+        <f>IFERROR((J$52-I$52)/ABS(I$52),"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6785,31 +6833,35 @@
         </is>
       </c>
       <c r="C5" s="8">
-        <f>IFERROR((C$31-B$31)/ABS(B$31),"n/a")</f>
+        <f>IFERROR((C$43-B$43)/ABS(B$43),"n/a")</f>
         <v/>
       </c>
       <c r="D5" s="8">
-        <f>IFERROR((D$31-C$31)/ABS(C$31),"n/a")</f>
+        <f>IFERROR((D$43-C$43)/ABS(C$43),"n/a")</f>
         <v/>
       </c>
       <c r="E5" s="8">
-        <f>IFERROR((E$31-D$31)/ABS(D$31),"n/a")</f>
+        <f>IFERROR((E$43-D$43)/ABS(D$43),"n/a")</f>
         <v/>
       </c>
       <c r="F5" s="8">
-        <f>IFERROR((F$31-E$31)/ABS(E$31),"n/a")</f>
+        <f>IFERROR((F$43-E$43)/ABS(E$43),"n/a")</f>
         <v/>
       </c>
       <c r="G5" s="8">
-        <f>IFERROR((G$31-F$31)/ABS(F$31),"n/a")</f>
+        <f>IFERROR((G$43-F$43)/ABS(F$43),"n/a")</f>
         <v/>
       </c>
       <c r="H5" s="8">
-        <f>IFERROR((H$31-G$31)/ABS(G$31),"n/a")</f>
+        <f>IFERROR((H$43-G$43)/ABS(G$43),"n/a")</f>
         <v/>
       </c>
       <c r="I5" s="8">
-        <f>IFERROR((I$31-H$31)/ABS(H$31),"n/a")</f>
+        <f>IFERROR((I$43-H$43)/ABS(H$43),"n/a")</f>
+        <v/>
+      </c>
+      <c r="J5" s="8">
+        <f>IFERROR((J$43-I$43)/ABS(I$43),"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6820,35 +6872,35 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <f>IFERROR(B$33/B$31,"n/a")</f>
+        <f>IFERROR(B$45/B$43,"n/a")</f>
         <v/>
       </c>
       <c r="C6" s="8">
-        <f>IFERROR(C$33/C$31,"n/a")</f>
+        <f>IFERROR(C$45/C$43,"n/a")</f>
         <v/>
       </c>
       <c r="D6" s="8">
-        <f>IFERROR(D$33/D$31,"n/a")</f>
+        <f>IFERROR(D$45/D$43,"n/a")</f>
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>IFERROR(E$33/E$31,"n/a")</f>
+        <f>IFERROR(E$45/E$43,"n/a")</f>
         <v/>
       </c>
       <c r="F6" s="8">
-        <f>IFERROR(F$33/F$31,"n/a")</f>
+        <f>IFERROR(F$45/F$43,"n/a")</f>
         <v/>
       </c>
       <c r="G6" s="8">
-        <f>IFERROR(G$33/G$31,"n/a")</f>
+        <f>IFERROR(G$45/G$43,"n/a")</f>
         <v/>
       </c>
       <c r="H6" s="8">
-        <f>IFERROR(H$33/H$31,"n/a")</f>
+        <f>IFERROR(H$45/H$43,"n/a")</f>
         <v/>
       </c>
       <c r="I6" s="8">
-        <f>IFERROR(I$33/I$31,"n/a")</f>
+        <f>IFERROR(I$45/I$43,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6859,35 +6911,39 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>IFERROR(B$38/B$31,"n/a")</f>
+        <f>IFERROR(B$52/B$43,"n/a")</f>
         <v/>
       </c>
       <c r="C7" s="8">
-        <f>IFERROR(C$38/C$31,"n/a")</f>
+        <f>IFERROR(C$52/C$43,"n/a")</f>
         <v/>
       </c>
       <c r="D7" s="8">
-        <f>IFERROR(D$38/D$31,"n/a")</f>
+        <f>IFERROR(D$52/D$43,"n/a")</f>
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>IFERROR(E$38/E$31,"n/a")</f>
+        <f>IFERROR(E$52/E$43,"n/a")</f>
         <v/>
       </c>
       <c r="F7" s="8">
-        <f>IFERROR(F$38/F$31,"n/a")</f>
+        <f>IFERROR(F$52/F$43,"n/a")</f>
         <v/>
       </c>
       <c r="G7" s="8">
-        <f>IFERROR(G$38/G$31,"n/a")</f>
+        <f>IFERROR(G$52/G$43,"n/a")</f>
         <v/>
       </c>
       <c r="H7" s="8">
-        <f>IFERROR(H$38/H$31,"n/a")</f>
+        <f>IFERROR(H$52/H$43,"n/a")</f>
         <v/>
       </c>
       <c r="I7" s="8">
-        <f>IFERROR(I$38/I$31,"n/a")</f>
+        <f>IFERROR(I$52/I$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J7" s="8">
+        <f>IFERROR(J$52/J$43,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6898,35 +6954,35 @@
         </is>
       </c>
       <c r="B8" s="9">
-        <f>IFERROR((B$29+B$30)/B$24,"n/a")</f>
+        <f>IFERROR((B$34+B$36)/B$39,"n/a")</f>
         <v/>
       </c>
       <c r="C8" s="9">
-        <f>IFERROR((C$29+C$30)/C$24,"n/a")</f>
+        <f>IFERROR((C$34+C$36)/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D8" s="9">
-        <f>IFERROR((D$29+D$30)/D$24,"n/a")</f>
+        <f>IFERROR((D$34+D$36)/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E8" s="9">
-        <f>IFERROR((E$29+E$30)/E$24,"n/a")</f>
+        <f>IFERROR((E$34+E$36)/E$39,"n/a")</f>
         <v/>
       </c>
       <c r="F8" s="9">
-        <f>IFERROR((F$29+F$30)/F$24,"n/a")</f>
+        <f>IFERROR((F$34+F$36)/F$39,"n/a")</f>
         <v/>
       </c>
       <c r="G8" s="9">
-        <f>IFERROR((G$29+G$30)/G$24,"n/a")</f>
+        <f>IFERROR((G$34+G$36)/G$39,"n/a")</f>
         <v/>
       </c>
       <c r="H8" s="9">
-        <f>IFERROR((H$29+H$30)/H$24,"n/a")</f>
+        <f>IFERROR((H$34+H$36)/H$39,"n/a")</f>
         <v/>
       </c>
       <c r="I8" s="9">
-        <f>IFERROR((I$29+I$30)/I$24,"n/a")</f>
+        <f>IFERROR((I$34+I$36)/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6937,35 +6993,35 @@
         </is>
       </c>
       <c r="B9" s="9">
-        <f>IFERROR(B$30/B$24,"n/a")</f>
+        <f>IFERROR(B$36/B$39,"n/a")</f>
         <v/>
       </c>
       <c r="C9" s="9">
-        <f>IFERROR(C$30/C$24,"n/a")</f>
+        <f>IFERROR(C$36/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D9" s="9">
-        <f>IFERROR(D$30/D$24,"n/a")</f>
+        <f>IFERROR(D$36/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E9" s="9">
-        <f>IFERROR(E$30/E$24,"n/a")</f>
+        <f>IFERROR(E$36/E$39,"n/a")</f>
         <v/>
       </c>
       <c r="F9" s="9">
-        <f>IFERROR(F$30/F$24,"n/a")</f>
+        <f>IFERROR(F$36/F$39,"n/a")</f>
         <v/>
       </c>
       <c r="G9" s="9">
-        <f>IFERROR(G$30/G$24,"n/a")</f>
+        <f>IFERROR(G$36/G$39,"n/a")</f>
         <v/>
       </c>
       <c r="H9" s="9">
-        <f>IFERROR(H$30/H$24,"n/a")</f>
+        <f>IFERROR(H$36/H$39,"n/a")</f>
         <v/>
       </c>
       <c r="I9" s="9">
-        <f>IFERROR(I$30/I$24,"n/a")</f>
+        <f>IFERROR(I$36/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6976,35 +7032,35 @@
         </is>
       </c>
       <c r="B10" s="9">
-        <f>IFERROR(B$29/B$24,"n/a")</f>
+        <f>IFERROR(B$34/B$39,"n/a")</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(C$29/C$24,"n/a")</f>
+        <f>IFERROR(C$34/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>IFERROR(D$29/D$24,"n/a")</f>
+        <f>IFERROR(D$34/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E10" s="9">
-        <f>IFERROR(E$29/E$24,"n/a")</f>
+        <f>IFERROR(E$34/E$39,"n/a")</f>
         <v/>
       </c>
       <c r="F10" s="9">
-        <f>IFERROR(F$29/F$24,"n/a")</f>
+        <f>IFERROR(F$34/F$39,"n/a")</f>
         <v/>
       </c>
       <c r="G10" s="9">
-        <f>IFERROR(G$29/G$24,"n/a")</f>
+        <f>IFERROR(G$34/G$39,"n/a")</f>
         <v/>
       </c>
       <c r="H10" s="9">
-        <f>IFERROR(H$29/H$24,"n/a")</f>
+        <f>IFERROR(H$34/H$39,"n/a")</f>
         <v/>
       </c>
       <c r="I10" s="9">
-        <f>IFERROR(I$29/I$24,"n/a")</f>
+        <f>IFERROR(I$34/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7015,35 +7071,35 @@
         </is>
       </c>
       <c r="B11" s="9">
-        <f>IFERROR(B$26/B$24,"n/a")</f>
+        <f>IFERROR(B$38/B$39,"n/a")</f>
         <v/>
       </c>
       <c r="C11" s="9">
-        <f>IFERROR(C$26/C$24,"n/a")</f>
+        <f>IFERROR(C$38/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D11" s="9">
-        <f>IFERROR(D$26/D$24,"n/a")</f>
+        <f>IFERROR(D$38/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E11" s="9">
-        <f>IFERROR(E$26/E$24,"n/a")</f>
+        <f>IFERROR(E$38/E$39,"n/a")</f>
         <v/>
       </c>
       <c r="F11" s="9">
-        <f>IFERROR(F$26/F$24,"n/a")</f>
+        <f>IFERROR(F$38/F$39,"n/a")</f>
         <v/>
       </c>
       <c r="G11" s="9">
-        <f>IFERROR(G$26/G$24,"n/a")</f>
+        <f>IFERROR(G$38/G$39,"n/a")</f>
         <v/>
       </c>
       <c r="H11" s="9">
-        <f>IFERROR(H$26/H$24,"n/a")</f>
+        <f>IFERROR(H$38/H$39,"n/a")</f>
         <v/>
       </c>
       <c r="I11" s="9">
-        <f>IFERROR(I$26/I$24,"n/a")</f>
+        <f>IFERROR(I$38/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7054,35 +7110,35 @@
         </is>
       </c>
       <c r="B12" s="9">
-        <f>IFERROR(B$28/B$24,"n/a")</f>
+        <f>IFERROR(B$37/B$39,"n/a")</f>
         <v/>
       </c>
       <c r="C12" s="9">
-        <f>IFERROR(C$28/C$24,"n/a")</f>
+        <f>IFERROR(C$37/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D12" s="9">
-        <f>IFERROR(D$28/D$24,"n/a")</f>
+        <f>IFERROR(D$37/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E12" s="9">
-        <f>IFERROR(E$28/E$24,"n/a")</f>
+        <f>IFERROR(E$37/E$39,"n/a")</f>
         <v/>
       </c>
       <c r="F12" s="9">
-        <f>IFERROR(F$28/F$24,"n/a")</f>
+        <f>IFERROR(F$37/F$39,"n/a")</f>
         <v/>
       </c>
       <c r="G12" s="9">
-        <f>IFERROR(G$28/G$24,"n/a")</f>
+        <f>IFERROR(G$37/G$39,"n/a")</f>
         <v/>
       </c>
       <c r="H12" s="9">
-        <f>IFERROR(H$28/H$24,"n/a")</f>
+        <f>IFERROR(H$37/H$39,"n/a")</f>
         <v/>
       </c>
       <c r="I12" s="9">
-        <f>IFERROR(I$28/I$24,"n/a")</f>
+        <f>IFERROR(I$37/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7093,35 +7149,35 @@
         </is>
       </c>
       <c r="B13" s="9">
-        <f>IFERROR(B$27/B$24,"n/a")</f>
+        <f>IFERROR(B$35/B$39,"n/a")</f>
         <v/>
       </c>
       <c r="C13" s="9">
-        <f>IFERROR(C$27/C$24,"n/a")</f>
+        <f>IFERROR(C$35/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D13" s="9">
-        <f>IFERROR(D$27/D$24,"n/a")</f>
+        <f>IFERROR(D$35/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E13" s="9">
-        <f>IFERROR(E$27/E$24,"n/a")</f>
+        <f>IFERROR(E$35/E$39,"n/a")</f>
         <v/>
       </c>
       <c r="F13" s="9">
-        <f>IFERROR(F$27/F$24,"n/a")</f>
+        <f>IFERROR(F$35/F$39,"n/a")</f>
         <v/>
       </c>
       <c r="G13" s="9">
-        <f>IFERROR(G$27/G$24,"n/a")</f>
+        <f>IFERROR(G$35/G$39,"n/a")</f>
         <v/>
       </c>
       <c r="H13" s="9">
-        <f>IFERROR(H$27/H$24,"n/a")</f>
+        <f>IFERROR(H$35/H$39,"n/a")</f>
         <v/>
       </c>
       <c r="I13" s="9">
-        <f>IFERROR(I$27/I$24,"n/a")</f>
+        <f>IFERROR(I$35/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7132,35 +7188,35 @@
         </is>
       </c>
       <c r="B14" s="8">
-        <f>IFERROR((ABS(B$34)+ABS(B$35))/B$33,"n/a")</f>
+        <f>IFERROR((ABS(B$46)+ABS(B$47))/B$45,"n/a")</f>
         <v/>
       </c>
       <c r="C14" s="8">
-        <f>IFERROR((ABS(C$34)+ABS(C$35))/C$33,"n/a")</f>
+        <f>IFERROR((ABS(C$46)+ABS(C$47))/C$45,"n/a")</f>
         <v/>
       </c>
       <c r="D14" s="8">
-        <f>IFERROR((ABS(D$34)+ABS(D$35))/D$33,"n/a")</f>
+        <f>IFERROR((ABS(D$46)+ABS(D$47))/D$45,"n/a")</f>
         <v/>
       </c>
       <c r="E14" s="8">
-        <f>IFERROR((ABS(E$34)+ABS(E$35))/E$33,"n/a")</f>
+        <f>IFERROR((ABS(E$46)+ABS(E$47))/E$45,"n/a")</f>
         <v/>
       </c>
       <c r="F14" s="8">
-        <f>IFERROR((ABS(F$34)+ABS(F$35))/F$33,"n/a")</f>
+        <f>IFERROR((ABS(F$46)+ABS(F$47))/F$45,"n/a")</f>
         <v/>
       </c>
       <c r="G14" s="8">
-        <f>IFERROR((ABS(G$34)+ABS(G$35))/G$33,"n/a")</f>
+        <f>IFERROR((ABS(G$46)+ABS(G$47))/G$45,"n/a")</f>
         <v/>
       </c>
       <c r="H14" s="8">
-        <f>IFERROR((ABS(H$34)+ABS(H$35))/H$33,"n/a")</f>
+        <f>IFERROR((ABS(H$46)+ABS(H$47))/H$45,"n/a")</f>
         <v/>
       </c>
       <c r="I14" s="8">
-        <f>IFERROR((ABS(I$34)+ABS(I$35))/I$33,"n/a")</f>
+        <f>IFERROR((ABS(I$46)+ABS(I$47))/I$45,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7171,35 +7227,35 @@
         </is>
       </c>
       <c r="B15" s="8">
-        <f>IFERROR(ABS(B$37)/B$36,"n/a")</f>
+        <f>IFERROR(ABS(B$49)/B$48,"n/a")</f>
         <v/>
       </c>
       <c r="C15" s="8">
-        <f>IFERROR(ABS(C$37)/C$36,"n/a")</f>
+        <f>IFERROR(ABS(C$49)/C$48,"n/a")</f>
         <v/>
       </c>
       <c r="D15" s="8">
-        <f>IFERROR(ABS(D$37)/D$36,"n/a")</f>
+        <f>IFERROR(ABS(D$49)/D$48,"n/a")</f>
         <v/>
       </c>
       <c r="E15" s="8">
-        <f>IFERROR(ABS(E$37)/E$36,"n/a")</f>
+        <f>IFERROR(ABS(E$49)/E$48,"n/a")</f>
         <v/>
       </c>
       <c r="F15" s="8">
-        <f>IFERROR(ABS(F$37)/F$36,"n/a")</f>
+        <f>IFERROR(ABS(F$49)/F$48,"n/a")</f>
         <v/>
       </c>
       <c r="G15" s="8">
-        <f>IFERROR(ABS(G$37)/G$36,"n/a")</f>
+        <f>IFERROR(ABS(G$49)/G$48,"n/a")</f>
         <v/>
       </c>
       <c r="H15" s="8">
-        <f>IFERROR(ABS(H$37)/H$36,"n/a")</f>
+        <f>IFERROR(ABS(H$49)/H$48,"n/a")</f>
         <v/>
       </c>
       <c r="I15" s="8">
-        <f>IFERROR(ABS(I$37)/I$36,"n/a")</f>
+        <f>IFERROR(ABS(I$49)/I$48,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7215,31 +7271,31 @@
         </is>
       </c>
       <c r="C16" s="12">
-        <f>IFERROR(((C$41+B$41)/2)/ABS(C$32)*365,"n/a")</f>
+        <f>IFERROR(((C$33+B$33)/2)/ABS(C$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="D16" s="12">
-        <f>IFERROR(((D$41+C$41)/2)/ABS(D$32)*365,"n/a")</f>
+        <f>IFERROR(((D$33+C$33)/2)/ABS(D$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="E16" s="12">
-        <f>IFERROR(((E$41+D$41)/2)/ABS(E$32)*365,"n/a")</f>
+        <f>IFERROR(((E$33+D$33)/2)/ABS(E$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="F16" s="12">
-        <f>IFERROR(((F$41+E$41)/2)/ABS(F$32)*365,"n/a")</f>
+        <f>IFERROR(((F$33+E$33)/2)/ABS(F$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="G16" s="12">
-        <f>IFERROR(((G$41+F$41)/2)/ABS(G$32)*365,"n/a")</f>
+        <f>IFERROR(((G$33+F$33)/2)/ABS(G$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="H16" s="12">
-        <f>IFERROR(((H$41+G$41)/2)/ABS(H$32)*365,"n/a")</f>
+        <f>IFERROR(((H$33+G$33)/2)/ABS(H$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="I16" s="12">
-        <f>IFERROR(((I$41+H$41)/2)/ABS(I$32)*365,"n/a")</f>
+        <f>IFERROR(((I$33+H$33)/2)/ABS(I$44)*365,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7255,31 +7311,31 @@
         </is>
       </c>
       <c r="C17" s="12">
-        <f>IFERROR(((C$40+B$40)/2)/C$31*365,"n/a")</f>
+        <f>IFERROR(((C$27+B$27)/2)/C$43*365,"n/a")</f>
         <v/>
       </c>
       <c r="D17" s="12">
-        <f>IFERROR(((D$40+C$40)/2)/D$31*365,"n/a")</f>
+        <f>IFERROR(((D$27+C$27)/2)/D$43*365,"n/a")</f>
         <v/>
       </c>
       <c r="E17" s="12">
-        <f>IFERROR(((E$40+D$40)/2)/E$31*365,"n/a")</f>
+        <f>IFERROR(((E$27+D$27)/2)/E$43*365,"n/a")</f>
         <v/>
       </c>
       <c r="F17" s="12">
-        <f>IFERROR(((F$40+E$40)/2)/F$31*365,"n/a")</f>
+        <f>IFERROR(((F$27+E$27)/2)/F$43*365,"n/a")</f>
         <v/>
       </c>
       <c r="G17" s="12">
-        <f>IFERROR(((G$40+F$40)/2)/G$31*365,"n/a")</f>
+        <f>IFERROR(((G$27+F$27)/2)/G$43*365,"n/a")</f>
         <v/>
       </c>
       <c r="H17" s="12">
-        <f>IFERROR(((H$40+G$40)/2)/H$31*365,"n/a")</f>
+        <f>IFERROR(((H$27+G$27)/2)/H$43*365,"n/a")</f>
         <v/>
       </c>
       <c r="I17" s="12">
-        <f>IFERROR(((I$40+H$40)/2)/I$31*365,"n/a")</f>
+        <f>IFERROR(((I$27+H$27)/2)/I$43*365,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7295,31 +7351,31 @@
         </is>
       </c>
       <c r="C18" s="12">
-        <f>IFERROR(((C$42+B$42)/2)/ABS(C$32)*365,"n/a")</f>
+        <f>IFERROR(((C$28+B$28)/2)/ABS(C$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="D18" s="12">
-        <f>IFERROR(((D$42+C$42)/2)/ABS(D$32)*365,"n/a")</f>
+        <f>IFERROR(((D$28+C$28)/2)/ABS(D$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="E18" s="12">
-        <f>IFERROR(((E$42+D$42)/2)/ABS(E$32)*365,"n/a")</f>
+        <f>IFERROR(((E$28+D$28)/2)/ABS(E$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="F18" s="12">
-        <f>IFERROR(((F$42+E$42)/2)/ABS(F$32)*365,"n/a")</f>
+        <f>IFERROR(((F$28+E$28)/2)/ABS(F$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="G18" s="12">
-        <f>IFERROR(((G$42+F$42)/2)/ABS(G$32)*365,"n/a")</f>
+        <f>IFERROR(((G$28+F$28)/2)/ABS(G$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="H18" s="12">
-        <f>IFERROR(((H$42+G$42)/2)/ABS(H$32)*365,"n/a")</f>
+        <f>IFERROR(((H$28+G$28)/2)/ABS(H$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="I18" s="12">
-        <f>IFERROR(((I$42+H$42)/2)/ABS(I$32)*365,"n/a")</f>
+        <f>IFERROR(((I$28+H$28)/2)/ABS(I$44)*365,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7330,35 +7386,35 @@
         </is>
       </c>
       <c r="B19" s="8">
-        <f>IFERROR(B$43/B$25,"n/a")</f>
+        <f>IFERROR(B$26/B$31,"n/a")</f>
         <v/>
       </c>
       <c r="C19" s="8">
-        <f>IFERROR(C$43/C$25,"n/a")</f>
+        <f>IFERROR(C$26/C$31,"n/a")</f>
         <v/>
       </c>
       <c r="D19" s="8">
-        <f>IFERROR(D$43/D$25,"n/a")</f>
+        <f>IFERROR(D$26/D$31,"n/a")</f>
         <v/>
       </c>
       <c r="E19" s="8">
-        <f>IFERROR(E$43/E$25,"n/a")</f>
+        <f>IFERROR(E$26/E$31,"n/a")</f>
         <v/>
       </c>
       <c r="F19" s="8">
-        <f>IFERROR(F$43/F$25,"n/a")</f>
+        <f>IFERROR(F$26/F$31,"n/a")</f>
         <v/>
       </c>
       <c r="G19" s="8">
-        <f>IFERROR(G$43/G$25,"n/a")</f>
+        <f>IFERROR(G$26/G$31,"n/a")</f>
         <v/>
       </c>
       <c r="H19" s="8">
-        <f>IFERROR(H$43/H$25,"n/a")</f>
+        <f>IFERROR(H$26/H$31,"n/a")</f>
         <v/>
       </c>
       <c r="I19" s="8">
-        <f>IFERROR(I$43/I$25,"n/a")</f>
+        <f>IFERROR(I$26/I$31,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7369,35 +7425,35 @@
         </is>
       </c>
       <c r="B20" s="8">
-        <f>IFERROR(B$42/B$25,"n/a")</f>
+        <f>IFERROR(B$28/B$31,"n/a")</f>
         <v/>
       </c>
       <c r="C20" s="8">
-        <f>IFERROR(C$42/C$25,"n/a")</f>
+        <f>IFERROR(C$28/C$31,"n/a")</f>
         <v/>
       </c>
       <c r="D20" s="8">
-        <f>IFERROR(D$42/D$25,"n/a")</f>
+        <f>IFERROR(D$28/D$31,"n/a")</f>
         <v/>
       </c>
       <c r="E20" s="8">
-        <f>IFERROR(E$42/E$25,"n/a")</f>
+        <f>IFERROR(E$28/E$31,"n/a")</f>
         <v/>
       </c>
       <c r="F20" s="8">
-        <f>IFERROR(F$42/F$25,"n/a")</f>
+        <f>IFERROR(F$28/F$31,"n/a")</f>
         <v/>
       </c>
       <c r="G20" s="8">
-        <f>IFERROR(G$42/G$25,"n/a")</f>
+        <f>IFERROR(G$28/G$31,"n/a")</f>
         <v/>
       </c>
       <c r="H20" s="8">
-        <f>IFERROR(H$42/H$25,"n/a")</f>
+        <f>IFERROR(H$28/H$31,"n/a")</f>
         <v/>
       </c>
       <c r="I20" s="8">
-        <f>IFERROR(I$42/I$25,"n/a")</f>
+        <f>IFERROR(I$28/I$31,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7459,1903 +7515,2147 @@
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
+          <t>CĐKT</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="16" t="n"/>
+      <c r="G24" s="16" t="n"/>
+      <c r="H24" s="16" t="n"/>
+      <c r="I24" s="16" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="17" t="inlineStr">
         <is>
+          <t>Tài sản</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="16" t="n"/>
+      <c r="G25" s="16" t="n"/>
+      <c r="H25" s="16" t="n"/>
+      <c r="I25" s="16" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>Tiền và tương đương tiền</t>
+        </is>
+      </c>
+      <c r="B26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>Phải thu khách hàng</t>
+        </is>
+      </c>
+      <c r="B27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>Hàng tồn kho, ròng</t>
+        </is>
+      </c>
+      <c r="B28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>TÀI SẢN NGẮN HẠN</t>
+        </is>
+      </c>
+      <c r="B29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>GTCL tài sản cố định vô hình</t>
+        </is>
+      </c>
+      <c r="B30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
           <t>TỔNG CỘNG TÀI SẢN</t>
         </is>
       </c>
-      <c r="B25" s="18">
+      <c r="B31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C25" s="18">
+      <c r="C31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D25" s="18">
+      <c r="D31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E25" s="18">
+      <c r="E31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F25" s="18">
+      <c r="F31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G25" s="18">
+      <c r="G31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H25" s="18">
+      <c r="H31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I25" s="18">
+      <c r="I31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>Nguồn vốn</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="n"/>
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="19" t="n"/>
+      <c r="E32" s="19" t="n"/>
+      <c r="F32" s="19" t="n"/>
+      <c r="G32" s="19" t="n"/>
+      <c r="H32" s="19" t="n"/>
+      <c r="I32" s="19" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>Phải trả người bán</t>
+        </is>
+      </c>
+      <c r="B33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>Vay ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>Nợ ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>Vay dài hạn</t>
+        </is>
+      </c>
+      <c r="B36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>Nợ dài hạn</t>
+        </is>
+      </c>
+      <c r="B37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>NỢ PHẢI TRẢ</t>
         </is>
       </c>
-      <c r="B26" s="18">
+      <c r="B38" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C26" s="18">
+      <c r="C38" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D26" s="18">
+      <c r="D38" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E26" s="18">
+      <c r="E38" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F26" s="18">
+      <c r="F38" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G26" s="18">
+      <c r="G38" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H26" s="18">
+      <c r="H38" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I26" s="18">
+      <c r="I38" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>Nợ ngắn hạn</t>
-        </is>
-      </c>
-      <c r="B27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>Nợ dài hạn</t>
-        </is>
-      </c>
-      <c r="B28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>Vay ngắn hạn</t>
-        </is>
-      </c>
-      <c r="B29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>Vay dài hạn</t>
-        </is>
-      </c>
-      <c r="B30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="20" t="n">
+        <v>6096125000000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>Tăng VCSH/LN cổ đông cty mẹ</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="n"/>
+      <c r="C40" s="23">
+        <f>(C39-B39)/C52</f>
+        <v/>
+      </c>
+      <c r="D40" s="23">
+        <f>(D39-C39)/D52</f>
+        <v/>
+      </c>
+      <c r="E40" s="23">
+        <f>(E39-D39)/E52</f>
+        <v/>
+      </c>
+      <c r="F40" s="23">
+        <f>(F39-E39)/F52</f>
+        <v/>
+      </c>
+      <c r="G40" s="23">
+        <f>(G39-F39)/G52</f>
+        <v/>
+      </c>
+      <c r="H40" s="23">
+        <f>(H39-G39)/H52</f>
+        <v/>
+      </c>
+      <c r="I40" s="23">
+        <f>(I39-H39)/I52</f>
+        <v/>
+      </c>
+      <c r="J40" s="24" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>Lợi ích của cổ đông thiểu số</t>
+        </is>
+      </c>
+      <c r="B41" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C41" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I41" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J41" s="24" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>Kết quả hoạt động kinh doanh</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="n"/>
+      <c r="C42" s="19" t="n"/>
+      <c r="D42" s="19" t="n"/>
+      <c r="E42" s="19" t="n"/>
+      <c r="F42" s="19" t="n"/>
+      <c r="G42" s="19" t="n"/>
+      <c r="H42" s="19" t="n"/>
+      <c r="I42" s="19" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>Doanh thu thuần</t>
         </is>
       </c>
-      <c r="B31" s="18">
+      <c r="B43" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C31" s="18">
+      <c r="C43" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D31" s="18">
+      <c r="D43" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E31" s="18">
+      <c r="E43" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F31" s="18">
+      <c r="F43" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G31" s="18">
+      <c r="G43" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H31" s="18">
+      <c r="H43" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I31" s="18">
+      <c r="I43" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="J43" s="20" t="n">
+        <v>59500000000000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>Giá vốn hàng bán</t>
         </is>
       </c>
-      <c r="B32" s="18">
+      <c r="B44" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C32" s="18">
+      <c r="C44" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D32" s="18">
+      <c r="D44" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E32" s="18">
+      <c r="E44" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F32" s="18">
+      <c r="F44" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G32" s="18">
+      <c r="G44" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H32" s="18">
+      <c r="H44" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I32" s="18">
+      <c r="I44" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>Lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B33" s="18">
+      <c r="B45" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C33" s="18">
+      <c r="C45" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D33" s="18">
+      <c r="D45" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E33" s="18">
+      <c r="E45" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F33" s="18">
+      <c r="F45" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G33" s="18">
+      <c r="G45" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H33" s="18">
+      <c r="H45" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I33" s="18">
+      <c r="I45" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="18" t="inlineStr">
         <is>
           <t>Chi phí bán hàng</t>
         </is>
       </c>
-      <c r="B34" s="18">
+      <c r="B46" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C34" s="18">
+      <c r="C46" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D34" s="18">
+      <c r="D46" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E34" s="18">
+      <c r="E46" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F34" s="18">
+      <c r="F46" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G34" s="18">
+      <c r="G46" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H34" s="18">
+      <c r="H46" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I34" s="18">
+      <c r="I46" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>Chi phí quản lý doanh nghiệp</t>
         </is>
       </c>
-      <c r="B35" s="18">
+      <c r="B47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C35" s="18">
+      <c r="C47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D35" s="18">
+      <c r="D47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E35" s="18">
+      <c r="E47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F35" s="18">
+      <c r="F47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G35" s="18">
+      <c r="G47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H35" s="18">
+      <c r="H47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I35" s="18">
+      <c r="I47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="18" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) từ hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B36" s="18">
+      <c r="B48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C36" s="18">
+      <c r="C48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D36" s="18">
+      <c r="D48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E36" s="18">
+      <c r="E48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F36" s="18">
+      <c r="F48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G36" s="18">
+      <c r="G48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H36" s="18">
+      <c r="H48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I36" s="18">
+      <c r="I48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="18" t="inlineStr">
         <is>
           <t>Chi phí lãi vay</t>
         </is>
       </c>
-      <c r="B37" s="18">
+      <c r="B49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C37" s="18">
+      <c r="C49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D37" s="18">
+      <c r="D49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E37" s="18">
+      <c r="E49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F37" s="18">
+      <c r="F49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G37" s="18">
+      <c r="G49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H37" s="18">
+      <c r="H49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I37" s="18">
+      <c r="I49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="25" t="inlineStr">
+        <is>
+          <t>Lãi/(lỗ) trước thuế</t>
+        </is>
+      </c>
+      <c r="B50" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C50" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D50" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E50" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F50" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I50" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J50" s="20" t="n">
+        <v>1550000000000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="18" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) thuần sau thuế</t>
         </is>
       </c>
-      <c r="B38" s="18">
+      <c r="B51" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C38" s="18">
+      <c r="C51" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D38" s="18">
+      <c r="D51" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E38" s="18">
+      <c r="E51" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F38" s="18">
+      <c r="F51" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G38" s="18">
+      <c r="G51" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H38" s="18">
+      <c r="H51" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I38" s="18">
+      <c r="I51" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t>Lợi nhuận của Cổ đông của Công ty mẹ</t>
         </is>
       </c>
-      <c r="B39" s="18">
+      <c r="B52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C39" s="18">
+      <c r="C52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D39" s="18">
+      <c r="D52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E39" s="18">
+      <c r="E52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F39" s="18">
+      <c r="F52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G39" s="18">
+      <c r="G52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H39" s="18">
+      <c r="H52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I39" s="18">
+      <c r="I52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>Phải thu khách hàng</t>
-        </is>
-      </c>
-      <c r="B40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="17" t="inlineStr">
-        <is>
-          <t>Phải trả người bán</t>
-        </is>
-      </c>
-      <c r="B41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>Hàng tồn kho, ròng</t>
-        </is>
-      </c>
-      <c r="B42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>Tiền và tương đương tiền</t>
-        </is>
-      </c>
-      <c r="B43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="17" t="inlineStr">
-        <is>
-          <t>TÀI SẢN NGẮN HẠN</t>
-        </is>
-      </c>
-      <c r="B44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="17" t="inlineStr">
-        <is>
-          <t>GTCL tài sản cố định vô hình</t>
-        </is>
-      </c>
-      <c r="B45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="17" t="inlineStr">
+      <c r="J52" s="20">
+        <f>J50*0.65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="18" t="inlineStr">
+        <is>
+          <t>LN cổ đông cty mẹ/ LN trước thuế</t>
+        </is>
+      </c>
+      <c r="B53" s="26">
+        <f>B52/B50</f>
+        <v/>
+      </c>
+      <c r="C53" s="26">
+        <f>C52/C50</f>
+        <v/>
+      </c>
+      <c r="D53" s="26">
+        <f>D52/D50</f>
+        <v/>
+      </c>
+      <c r="E53" s="26">
+        <f>E52/E50</f>
+        <v/>
+      </c>
+      <c r="F53" s="26">
+        <f>F52/F50</f>
+        <v/>
+      </c>
+      <c r="G53" s="26">
+        <f>G52/G50</f>
+        <v/>
+      </c>
+      <c r="H53" s="26">
+        <f>H52/H50</f>
+        <v/>
+      </c>
+      <c r="I53" s="26">
+        <f>I52/I50</f>
+        <v/>
+      </c>
+      <c r="J53" s="27" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>Lưu chuyển tiền tệ</t>
+        </is>
+      </c>
+      <c r="B54" s="19" t="n"/>
+      <c r="C54" s="19" t="n"/>
+      <c r="D54" s="19" t="n"/>
+      <c r="E54" s="19" t="n"/>
+      <c r="F54" s="19" t="n"/>
+      <c r="G54" s="19" t="n"/>
+      <c r="H54" s="19" t="n"/>
+      <c r="I54" s="19" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="18" t="inlineStr">
         <is>
           <t>Khấu hao TSCĐ và BĐSĐT</t>
         </is>
       </c>
-      <c r="B46" s="18">
+      <c r="B55" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(B$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C46" s="18">
+      <c r="C55" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(C$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D46" s="18">
+      <c r="D55" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(D$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E46" s="18">
+      <c r="E55" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(E$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F46" s="18">
+      <c r="F55" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(F$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G46" s="18">
+      <c r="G55" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(G$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H46" s="18">
+      <c r="H55" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(H$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I46" s="18">
+      <c r="I55" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(I$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="17" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="18" t="inlineStr">
         <is>
           <t>Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác</t>
         </is>
       </c>
-      <c r="B47" s="18">
+      <c r="B56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(B$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C47" s="18">
+      <c r="C56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(C$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D47" s="18">
+      <c r="D56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(D$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E47" s="18">
+      <c r="E56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(E$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F47" s="18">
+      <c r="F56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(F$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G47" s="18">
+      <c r="G56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(G$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H47" s="18">
+      <c r="H56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(H$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I47" s="18">
+      <c r="I56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(I$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="17" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="18" t="inlineStr">
         <is>
           <t>Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh</t>
         </is>
       </c>
-      <c r="B48" s="18">
+      <c r="B57" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(B$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C48" s="18">
+      <c r="C57" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(C$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D48" s="18">
+      <c r="D57" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(D$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E48" s="18">
+      <c r="E57" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(E$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F48" s="18">
+      <c r="F57" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(F$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G48" s="18">
+      <c r="G57" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(G$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H48" s="18">
+      <c r="H57" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(H$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I48" s="18">
+      <c r="I57" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(I$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" s="19" t="inlineStr">
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61">
+      <c r="A61" s="28" t="inlineStr">
         <is>
           <t>CHỈ SỐ THÊM</t>
         </is>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B61" s="16" t="n">
         <v>2018</v>
       </c>
-      <c r="C52" s="6" t="n">
+      <c r="C61" s="16" t="n">
         <v>2019</v>
       </c>
-      <c r="D52" s="6" t="n">
+      <c r="D61" s="16" t="n">
         <v>2020</v>
       </c>
-      <c r="E52" s="6" t="n">
+      <c r="E61" s="16" t="n">
         <v>2021</v>
       </c>
-      <c r="F52" s="6" t="n">
+      <c r="F61" s="16" t="n">
         <v>2022</v>
       </c>
-      <c r="G52" s="6" t="n">
+      <c r="G61" s="16" t="n">
         <v>2023</v>
       </c>
-      <c r="H52" s="6" t="n">
+      <c r="H61" s="16" t="n">
         <v>2024</v>
       </c>
-      <c r="I52" s="6" t="n">
+      <c r="I61" s="16" t="n">
         <v>2025</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="19" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="28" t="inlineStr">
         <is>
           <t>Khả năng sinh lời &amp; hiệu quả sử dụng vốn</t>
         </is>
       </c>
-      <c r="B53" s="20" t="n"/>
-      <c r="C53" s="20" t="n"/>
-      <c r="D53" s="20" t="n"/>
-      <c r="E53" s="20" t="n"/>
-      <c r="F53" s="20" t="n"/>
-      <c r="G53" s="20" t="n"/>
-      <c r="H53" s="20" t="n"/>
-      <c r="I53" s="20" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="20" t="inlineStr">
+      <c r="B62" s="29" t="n"/>
+      <c r="C62" s="29" t="n"/>
+      <c r="D62" s="29" t="n"/>
+      <c r="E62" s="29" t="n"/>
+      <c r="F62" s="29" t="n"/>
+      <c r="G62" s="29" t="n"/>
+      <c r="H62" s="29" t="n"/>
+      <c r="I62" s="29" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="29" t="inlineStr">
         <is>
           <t>ROCE</t>
         </is>
       </c>
-      <c r="B54" s="21">
-        <f>IFERROR(B$56/(B$25-B$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C54" s="21">
-        <f>IFERROR(C$56/(C$25-C$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D54" s="21">
-        <f>IFERROR(D$56/(D$25-D$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E54" s="21">
-        <f>IFERROR(E$56/(E$25-E$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F54" s="21">
-        <f>IFERROR(F$56/(F$25-F$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G54" s="21">
-        <f>IFERROR(G$56/(G$25-G$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H54" s="21">
-        <f>IFERROR(H$56/(H$25-H$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I54" s="21">
-        <f>IFERROR(I$56/(I$25-I$27),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="20" t="inlineStr">
+      <c r="B63" s="30">
+        <f>IFERROR(B$65/(B$31-B$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C63" s="30">
+        <f>IFERROR(C$65/(C$31-C$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D63" s="30">
+        <f>IFERROR(D$65/(D$31-D$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E63" s="30">
+        <f>IFERROR(E$65/(E$31-E$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F63" s="30">
+        <f>IFERROR(F$65/(F$31-F$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G63" s="30">
+        <f>IFERROR(G$65/(G$31-G$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H63" s="30">
+        <f>IFERROR(H$65/(H$31-H$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I63" s="30">
+        <f>IFERROR(I$65/(I$31-I$35),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="29" t="inlineStr">
         <is>
           <t>CROIC</t>
         </is>
       </c>
-      <c r="B55" s="21">
-        <f>IFERROR(B$60/(B$25-B$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C55" s="21">
-        <f>IFERROR(C$60/(C$25-C$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D55" s="21">
-        <f>IFERROR(D$60/(D$25-D$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E55" s="21">
-        <f>IFERROR(E$60/(E$25-E$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F55" s="21">
-        <f>IFERROR(F$60/(F$25-F$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G55" s="21">
-        <f>IFERROR(G$60/(G$25-G$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H55" s="21">
-        <f>IFERROR(H$60/(H$25-H$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I55" s="21">
-        <f>IFERROR(I$60/(I$25-I$27),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="20" t="inlineStr">
+      <c r="B64" s="30">
+        <f>IFERROR(B$69/(B$31-B$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C64" s="30">
+        <f>IFERROR(C$69/(C$31-C$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D64" s="30">
+        <f>IFERROR(D$69/(D$31-D$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E64" s="30">
+        <f>IFERROR(E$69/(E$31-E$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F64" s="30">
+        <f>IFERROR(F$69/(F$31-F$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G64" s="30">
+        <f>IFERROR(G$69/(G$31-G$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H64" s="30">
+        <f>IFERROR(H$69/(H$31-H$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I64" s="30">
+        <f>IFERROR(I$69/(I$31-I$35),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="29" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B56" s="22">
-        <f>IFERROR(B$36+ABS(B$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C56" s="22">
-        <f>IFERROR(C$36+ABS(C$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D56" s="22">
-        <f>IFERROR(D$36+ABS(D$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E56" s="22">
-        <f>IFERROR(E$36+ABS(E$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F56" s="22">
-        <f>IFERROR(F$36+ABS(F$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G56" s="22">
-        <f>IFERROR(G$36+ABS(G$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H56" s="22">
-        <f>IFERROR(H$36+ABS(H$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I56" s="22">
-        <f>IFERROR(I$36+ABS(I$37),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="20" t="inlineStr">
+      <c r="B65" s="31">
+        <f>IFERROR(B$48+ABS(B$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C65" s="31">
+        <f>IFERROR(C$48+ABS(C$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D65" s="31">
+        <f>IFERROR(D$48+ABS(D$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E65" s="31">
+        <f>IFERROR(E$48+ABS(E$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F65" s="31">
+        <f>IFERROR(F$48+ABS(F$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G65" s="31">
+        <f>IFERROR(G$48+ABS(G$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H65" s="31">
+        <f>IFERROR(H$48+ABS(H$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I65" s="31">
+        <f>IFERROR(I$48+ABS(I$49),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
         <is>
           <t>EBIT/DT</t>
         </is>
       </c>
-      <c r="B57" s="21">
-        <f>IFERROR(B$56/B$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C57" s="21">
-        <f>IFERROR(C$56/C$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D57" s="21">
-        <f>IFERROR(D$56/D$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E57" s="21">
-        <f>IFERROR(E$56/E$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F57" s="21">
-        <f>IFERROR(F$56/F$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G57" s="21">
-        <f>IFERROR(G$56/G$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H57" s="21">
-        <f>IFERROR(H$56/H$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I57" s="21">
-        <f>IFERROR(I$56/I$31,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="20" t="inlineStr">
+      <c r="B66" s="30">
+        <f>IFERROR(B$65/B$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C66" s="30">
+        <f>IFERROR(C$65/C$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D66" s="30">
+        <f>IFERROR(D$65/D$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E66" s="30">
+        <f>IFERROR(E$65/E$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F66" s="30">
+        <f>IFERROR(F$65/F$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G66" s="30">
+        <f>IFERROR(G$65/G$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H66" s="30">
+        <f>IFERROR(H$65/H$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I66" s="30">
+        <f>IFERROR(I$65/I$43,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
         <is>
           <t>DT/TS</t>
         </is>
       </c>
-      <c r="B58" s="21">
-        <f>IFERROR(B$31/B$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C58" s="21">
-        <f>IFERROR(C$31/C$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D58" s="21">
-        <f>IFERROR(D$31/D$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E58" s="21">
-        <f>IFERROR(E$31/E$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F58" s="21">
-        <f>IFERROR(F$31/F$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G58" s="21">
-        <f>IFERROR(G$31/G$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H58" s="21">
-        <f>IFERROR(H$31/H$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I58" s="21">
-        <f>IFERROR(I$31/I$25,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="19" t="inlineStr">
+      <c r="B67" s="30">
+        <f>IFERROR(B$43/B$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C67" s="30">
+        <f>IFERROR(C$43/C$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D67" s="30">
+        <f>IFERROR(D$43/D$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E67" s="30">
+        <f>IFERROR(E$43/E$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F67" s="30">
+        <f>IFERROR(F$43/F$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G67" s="30">
+        <f>IFERROR(G$43/G$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H67" s="30">
+        <f>IFERROR(H$43/H$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I67" s="30">
+        <f>IFERROR(I$43/I$31,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="28" t="inlineStr">
         <is>
           <t>Dòng tiền &amp; tái đầu tư</t>
         </is>
       </c>
-      <c r="B59" s="20" t="n"/>
-      <c r="C59" s="20" t="n"/>
-      <c r="D59" s="20" t="n"/>
-      <c r="E59" s="20" t="n"/>
-      <c r="F59" s="20" t="n"/>
-      <c r="G59" s="20" t="n"/>
-      <c r="H59" s="20" t="n"/>
-      <c r="I59" s="20" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="20" t="inlineStr">
+      <c r="B68" s="29" t="n"/>
+      <c r="C68" s="29" t="n"/>
+      <c r="D68" s="29" t="n"/>
+      <c r="E68" s="29" t="n"/>
+      <c r="F68" s="29" t="n"/>
+      <c r="G68" s="29" t="n"/>
+      <c r="H68" s="29" t="n"/>
+      <c r="I68" s="29" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>FCF</t>
         </is>
       </c>
-      <c r="B60" s="22">
-        <f>IFERROR(B$48-ABS(B$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C60" s="22">
-        <f>IFERROR(C$48-ABS(C$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D60" s="22">
-        <f>IFERROR(D$48-ABS(D$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E60" s="22">
-        <f>IFERROR(E$48-ABS(E$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F60" s="22">
-        <f>IFERROR(F$48-ABS(F$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G60" s="22">
-        <f>IFERROR(G$48-ABS(G$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H60" s="22">
-        <f>IFERROR(H$48-ABS(H$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I60" s="22">
-        <f>IFERROR(I$48-ABS(I$47),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="20" t="inlineStr">
+      <c r="B69" s="31">
+        <f>IFERROR(B$57-ABS(B$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C69" s="31">
+        <f>IFERROR(C$57-ABS(C$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D69" s="31">
+        <f>IFERROR(D$57-ABS(D$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E69" s="31">
+        <f>IFERROR(E$57-ABS(E$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F69" s="31">
+        <f>IFERROR(F$57-ABS(F$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G69" s="31">
+        <f>IFERROR(G$57-ABS(G$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H69" s="31">
+        <f>IFERROR(H$57-ABS(H$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I69" s="31">
+        <f>IFERROR(I$57-ABS(I$56),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="29" t="inlineStr">
         <is>
           <t>FCF/DT</t>
         </is>
       </c>
-      <c r="B61" s="21">
-        <f>IFERROR(B$60/B$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C61" s="21">
-        <f>IFERROR(C$60/C$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D61" s="21">
-        <f>IFERROR(D$60/D$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E61" s="21">
-        <f>IFERROR(E$60/E$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F61" s="21">
-        <f>IFERROR(F$60/F$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G61" s="21">
-        <f>IFERROR(G$60/G$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H61" s="21">
-        <f>IFERROR(H$60/H$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I61" s="21">
-        <f>IFERROR(I$60/I$31,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="20" t="inlineStr">
+      <c r="B70" s="30">
+        <f>IFERROR(B$69/B$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C70" s="30">
+        <f>IFERROR(C$69/C$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D70" s="30">
+        <f>IFERROR(D$69/D$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E70" s="30">
+        <f>IFERROR(E$69/E$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F70" s="30">
+        <f>IFERROR(F$69/F$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G70" s="30">
+        <f>IFERROR(G$69/G$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H70" s="30">
+        <f>IFERROR(H$69/H$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I70" s="30">
+        <f>IFERROR(I$69/I$43,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="29" t="inlineStr">
         <is>
           <t>FCF/Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B62" s="21">
-        <f>IFERROR(B$60/B$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C62" s="21">
-        <f>IFERROR(C$60/C$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D62" s="21">
-        <f>IFERROR(D$60/D$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E62" s="21">
-        <f>IFERROR(E$60/E$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F62" s="21">
-        <f>IFERROR(F$60/F$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G62" s="21">
-        <f>IFERROR(G$60/G$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H62" s="21">
-        <f>IFERROR(H$60/H$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I62" s="21">
-        <f>IFERROR(I$60/I$27,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="20" t="inlineStr">
+      <c r="B71" s="30">
+        <f>IFERROR(B$69/B$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C71" s="30">
+        <f>IFERROR(C$69/C$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D71" s="30">
+        <f>IFERROR(D$69/D$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E71" s="30">
+        <f>IFERROR(E$69/E$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F71" s="30">
+        <f>IFERROR(F$69/F$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G71" s="30">
+        <f>IFERROR(G$69/G$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H71" s="30">
+        <f>IFERROR(H$69/H$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I71" s="30">
+        <f>IFERROR(I$69/I$35,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="29" t="inlineStr">
         <is>
           <t>Capex</t>
         </is>
       </c>
-      <c r="B63" s="22">
-        <f>IFERROR(ABS(B$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C63" s="22">
-        <f>IFERROR(ABS(C$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D63" s="22">
-        <f>IFERROR(ABS(D$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E63" s="22">
-        <f>IFERROR(ABS(E$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F63" s="22">
-        <f>IFERROR(ABS(F$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G63" s="22">
-        <f>IFERROR(ABS(G$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H63" s="22">
-        <f>IFERROR(ABS(H$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I63" s="22">
-        <f>IFERROR(ABS(I$47),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="20" t="inlineStr">
+      <c r="B72" s="31">
+        <f>IFERROR(ABS(B$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C72" s="31">
+        <f>IFERROR(ABS(C$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D72" s="31">
+        <f>IFERROR(ABS(D$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E72" s="31">
+        <f>IFERROR(ABS(E$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F72" s="31">
+        <f>IFERROR(ABS(F$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G72" s="31">
+        <f>IFERROR(ABS(G$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H72" s="31">
+        <f>IFERROR(ABS(H$56),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I72" s="31">
+        <f>IFERROR(ABS(I$56),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="29" t="inlineStr">
         <is>
           <t>Capex/TS</t>
         </is>
       </c>
-      <c r="B64" s="21">
-        <f>IFERROR(B$63/B$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C64" s="21">
-        <f>IFERROR(C$63/C$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D64" s="21">
-        <f>IFERROR(D$63/D$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E64" s="21">
-        <f>IFERROR(E$63/E$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F64" s="21">
-        <f>IFERROR(F$63/F$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G64" s="21">
-        <f>IFERROR(G$63/G$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H64" s="21">
-        <f>IFERROR(H$63/H$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I64" s="21">
-        <f>IFERROR(I$63/I$25,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="20" t="inlineStr">
+      <c r="B73" s="30">
+        <f>IFERROR(B$72/B$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C73" s="30">
+        <f>IFERROR(C$72/C$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D73" s="30">
+        <f>IFERROR(D$72/D$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E73" s="30">
+        <f>IFERROR(E$72/E$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F73" s="30">
+        <f>IFERROR(F$72/F$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G73" s="30">
+        <f>IFERROR(G$72/G$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H73" s="30">
+        <f>IFERROR(H$72/H$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I73" s="30">
+        <f>IFERROR(I$72/I$31,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="29" t="inlineStr">
         <is>
           <t>Capex/LNST</t>
         </is>
       </c>
-      <c r="B65" s="21">
-        <f>IFERROR(B$63/ABS(B$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C65" s="21">
-        <f>IFERROR(C$63/ABS(C$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D65" s="21">
-        <f>IFERROR(D$63/ABS(D$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E65" s="21">
-        <f>IFERROR(E$63/ABS(E$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F65" s="21">
-        <f>IFERROR(F$63/ABS(F$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G65" s="21">
-        <f>IFERROR(G$63/ABS(G$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H65" s="21">
-        <f>IFERROR(H$63/ABS(H$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I65" s="21">
-        <f>IFERROR(I$63/ABS(I$38),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="20" t="inlineStr">
+      <c r="B74" s="30">
+        <f>IFERROR(B$72/ABS(B$51),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C74" s="30">
+        <f>IFERROR(C$72/ABS(C$51),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D74" s="30">
+        <f>IFERROR(D$72/ABS(D$51),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E74" s="30">
+        <f>IFERROR(E$72/ABS(E$51),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F74" s="30">
+        <f>IFERROR(F$72/ABS(F$51),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G74" s="30">
+        <f>IFERROR(G$72/ABS(G$51),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H74" s="30">
+        <f>IFERROR(H$72/ABS(H$51),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I74" s="30">
+        <f>IFERROR(I$72/ABS(I$51),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
         <is>
           <t>Chi phí khấu hao/Lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B66" s="21">
-        <f>IFERROR(ABS(B$46)/B$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C66" s="21">
-        <f>IFERROR(ABS(C$46)/C$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D66" s="21">
-        <f>IFERROR(ABS(D$46)/D$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E66" s="21">
-        <f>IFERROR(ABS(E$46)/E$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F66" s="21">
-        <f>IFERROR(ABS(F$46)/F$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G66" s="21">
-        <f>IFERROR(ABS(G$46)/G$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H66" s="21">
-        <f>IFERROR(ABS(H$46)/H$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I66" s="21">
-        <f>IFERROR(ABS(I$46)/I$33,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="20" t="inlineStr">
+      <c r="B75" s="30">
+        <f>IFERROR(ABS(B$55)/B$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C75" s="30">
+        <f>IFERROR(ABS(C$55)/C$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D75" s="30">
+        <f>IFERROR(ABS(D$55)/D$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E75" s="30">
+        <f>IFERROR(ABS(E$55)/E$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F75" s="30">
+        <f>IFERROR(ABS(F$55)/F$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G75" s="30">
+        <f>IFERROR(ABS(G$55)/G$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H75" s="30">
+        <f>IFERROR(ABS(H$55)/H$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I75" s="30">
+        <f>IFERROR(ABS(I$55)/I$45,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>EBIT/Chi phí lãi vay</t>
         </is>
       </c>
-      <c r="B67" s="23">
-        <f>IFERROR(B$56/ABS(B$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C67" s="23">
-        <f>IFERROR(C$56/ABS(C$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D67" s="23">
-        <f>IFERROR(D$56/ABS(D$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E67" s="23">
-        <f>IFERROR(E$56/ABS(E$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F67" s="23">
-        <f>IFERROR(F$56/ABS(F$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G67" s="23">
-        <f>IFERROR(G$56/ABS(G$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H67" s="23">
-        <f>IFERROR(H$56/ABS(H$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I67" s="23">
-        <f>IFERROR(I$56/ABS(I$37),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="19" t="inlineStr">
+      <c r="B76" s="32">
+        <f>IFERROR(B$65/ABS(B$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C76" s="32">
+        <f>IFERROR(C$65/ABS(C$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D76" s="32">
+        <f>IFERROR(D$65/ABS(D$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E76" s="32">
+        <f>IFERROR(E$65/ABS(E$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F76" s="32">
+        <f>IFERROR(F$65/ABS(F$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G76" s="32">
+        <f>IFERROR(G$65/ABS(G$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H76" s="32">
+        <f>IFERROR(H$65/ABS(H$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I76" s="32">
+        <f>IFERROR(I$65/ABS(I$49),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
         <is>
           <t>Vốn lưu động &amp; hiệu quả hoạt động</t>
         </is>
       </c>
-      <c r="B68" s="20" t="n"/>
-      <c r="C68" s="20" t="n"/>
-      <c r="D68" s="20" t="n"/>
-      <c r="E68" s="20" t="n"/>
-      <c r="F68" s="20" t="n"/>
-      <c r="G68" s="20" t="n"/>
-      <c r="H68" s="20" t="n"/>
-      <c r="I68" s="20" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="20" t="inlineStr">
+      <c r="B77" s="29" t="n"/>
+      <c r="C77" s="29" t="n"/>
+      <c r="D77" s="29" t="n"/>
+      <c r="E77" s="29" t="n"/>
+      <c r="F77" s="29" t="n"/>
+      <c r="G77" s="29" t="n"/>
+      <c r="H77" s="29" t="n"/>
+      <c r="I77" s="29" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="29" t="inlineStr">
         <is>
           <t>Vòng quay tiền mặt</t>
         </is>
       </c>
-      <c r="B69" s="24">
+      <c r="B78" s="33">
         <f>IFERROR(B$17+B$18-B$16,"n/a")</f>
         <v/>
       </c>
-      <c r="C69" s="24">
+      <c r="C78" s="33">
         <f>IFERROR(C$17+C$18-C$16,"n/a")</f>
         <v/>
       </c>
-      <c r="D69" s="24">
+      <c r="D78" s="33">
         <f>IFERROR(D$17+D$18-D$16,"n/a")</f>
         <v/>
       </c>
-      <c r="E69" s="24">
+      <c r="E78" s="33">
         <f>IFERROR(E$17+E$18-E$16,"n/a")</f>
         <v/>
       </c>
-      <c r="F69" s="24">
+      <c r="F78" s="33">
         <f>IFERROR(F$17+F$18-F$16,"n/a")</f>
         <v/>
       </c>
-      <c r="G69" s="24">
+      <c r="G78" s="33">
         <f>IFERROR(G$17+G$18-G$16,"n/a")</f>
         <v/>
       </c>
-      <c r="H69" s="24">
+      <c r="H78" s="33">
         <f>IFERROR(H$17+H$18-H$16,"n/a")</f>
         <v/>
       </c>
-      <c r="I69" s="24">
+      <c r="I78" s="33">
         <f>IFERROR(I$17+I$18-I$16,"n/a")</f>
         <v/>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="20" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="29" t="inlineStr">
         <is>
           <t>HTK/DT</t>
         </is>
       </c>
-      <c r="B70" s="21">
-        <f>IFERROR(B$42/B$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C70" s="21">
-        <f>IFERROR(C$42/C$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D70" s="21">
-        <f>IFERROR(D$42/D$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E70" s="21">
-        <f>IFERROR(E$42/E$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F70" s="21">
-        <f>IFERROR(F$42/F$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G70" s="21">
-        <f>IFERROR(G$42/G$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H70" s="21">
-        <f>IFERROR(H$42/H$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I70" s="21">
-        <f>IFERROR(I$42/I$31,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="20" t="inlineStr">
+      <c r="B79" s="30">
+        <f>IFERROR(B$28/B$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C79" s="30">
+        <f>IFERROR(C$28/C$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D79" s="30">
+        <f>IFERROR(D$28/D$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E79" s="30">
+        <f>IFERROR(E$28/E$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F79" s="30">
+        <f>IFERROR(F$28/F$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G79" s="30">
+        <f>IFERROR(G$28/G$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H79" s="30">
+        <f>IFERROR(H$28/H$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I79" s="30">
+        <f>IFERROR(I$28/I$43,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="29" t="inlineStr">
         <is>
           <t>HTK/TS</t>
         </is>
       </c>
-      <c r="B71" s="21">
-        <f>IFERROR(B$42/B$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C71" s="21">
-        <f>IFERROR(C$42/C$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D71" s="21">
-        <f>IFERROR(D$42/D$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E71" s="21">
-        <f>IFERROR(E$42/E$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F71" s="21">
-        <f>IFERROR(F$42/F$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G71" s="21">
-        <f>IFERROR(G$42/G$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H71" s="21">
-        <f>IFERROR(H$42/H$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I71" s="21">
-        <f>IFERROR(I$42/I$25,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="20" t="inlineStr">
+      <c r="B80" s="30">
+        <f>IFERROR(B$28/B$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C80" s="30">
+        <f>IFERROR(C$28/C$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D80" s="30">
+        <f>IFERROR(D$28/D$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E80" s="30">
+        <f>IFERROR(E$28/E$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F80" s="30">
+        <f>IFERROR(F$28/F$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G80" s="30">
+        <f>IFERROR(G$28/G$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H80" s="30">
+        <f>IFERROR(H$28/H$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I80" s="30">
+        <f>IFERROR(I$28/I$31,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="29" t="inlineStr">
         <is>
           <t>DT/TS</t>
         </is>
       </c>
-      <c r="B72" s="21">
-        <f>IFERROR(B$31/B$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C72" s="21">
-        <f>IFERROR(C$31/C$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D72" s="21">
-        <f>IFERROR(D$31/D$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E72" s="21">
-        <f>IFERROR(E$31/E$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F72" s="21">
-        <f>IFERROR(F$31/F$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G72" s="21">
-        <f>IFERROR(G$31/G$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H72" s="21">
-        <f>IFERROR(H$31/H$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I72" s="21">
-        <f>IFERROR(I$31/I$25,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="19" t="inlineStr">
+      <c r="B81" s="30">
+        <f>IFERROR(B$43/B$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C81" s="30">
+        <f>IFERROR(C$43/C$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D81" s="30">
+        <f>IFERROR(D$43/D$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E81" s="30">
+        <f>IFERROR(E$43/E$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F81" s="30">
+        <f>IFERROR(F$43/F$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G81" s="30">
+        <f>IFERROR(G$43/G$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H81" s="30">
+        <f>IFERROR(H$43/H$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I81" s="30">
+        <f>IFERROR(I$43/I$31,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="28" t="inlineStr">
         <is>
           <t>Khả năng thanh toán</t>
         </is>
       </c>
-      <c r="B73" s="20" t="n"/>
-      <c r="C73" s="20" t="n"/>
-      <c r="D73" s="20" t="n"/>
-      <c r="E73" s="20" t="n"/>
-      <c r="F73" s="20" t="n"/>
-      <c r="G73" s="20" t="n"/>
-      <c r="H73" s="20" t="n"/>
-      <c r="I73" s="20" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="20" t="inlineStr">
+      <c r="B82" s="29" t="n"/>
+      <c r="C82" s="29" t="n"/>
+      <c r="D82" s="29" t="n"/>
+      <c r="E82" s="29" t="n"/>
+      <c r="F82" s="29" t="n"/>
+      <c r="G82" s="29" t="n"/>
+      <c r="H82" s="29" t="n"/>
+      <c r="I82" s="29" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="29" t="inlineStr">
         <is>
           <t>(TS ngắn hạn − HTK)/Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B74" s="23">
-        <f>IFERROR((B$44-B$42)/B$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C74" s="23">
-        <f>IFERROR((C$44-C$42)/C$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D74" s="23">
-        <f>IFERROR((D$44-D$42)/D$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E74" s="23">
-        <f>IFERROR((E$44-E$42)/E$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F74" s="23">
-        <f>IFERROR((F$44-F$42)/F$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G74" s="23">
-        <f>IFERROR((G$44-G$42)/G$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H74" s="23">
-        <f>IFERROR((H$44-H$42)/H$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I74" s="23">
-        <f>IFERROR((I$44-I$42)/I$27,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="20" t="inlineStr">
+      <c r="B83" s="32">
+        <f>IFERROR((B$29-B$28)/B$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C83" s="32">
+        <f>IFERROR((C$29-C$28)/C$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D83" s="32">
+        <f>IFERROR((D$29-D$28)/D$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E83" s="32">
+        <f>IFERROR((E$29-E$28)/E$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F83" s="32">
+        <f>IFERROR((F$29-F$28)/F$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G83" s="32">
+        <f>IFERROR((G$29-G$28)/G$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H83" s="32">
+        <f>IFERROR((H$29-H$28)/H$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I83" s="32">
+        <f>IFERROR((I$29-I$28)/I$35,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="29" t="inlineStr">
         <is>
           <t>TS ngắn hạn/Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B75" s="23">
-        <f>IFERROR(B$44/B$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C75" s="23">
-        <f>IFERROR(C$44/C$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D75" s="23">
-        <f>IFERROR(D$44/D$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E75" s="23">
-        <f>IFERROR(E$44/E$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F75" s="23">
-        <f>IFERROR(F$44/F$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G75" s="23">
-        <f>IFERROR(G$44/G$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H75" s="23">
-        <f>IFERROR(H$44/H$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I75" s="23">
-        <f>IFERROR(I$44/I$27,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="19" t="inlineStr">
+      <c r="B84" s="32">
+        <f>IFERROR(B$29/B$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C84" s="32">
+        <f>IFERROR(C$29/C$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D84" s="32">
+        <f>IFERROR(D$29/D$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E84" s="32">
+        <f>IFERROR(E$29/E$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F84" s="32">
+        <f>IFERROR(F$29/F$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G84" s="32">
+        <f>IFERROR(G$29/G$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H84" s="32">
+        <f>IFERROR(H$29/H$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I84" s="32">
+        <f>IFERROR(I$29/I$35,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="28" t="inlineStr">
         <is>
           <t>Tài sản &amp; cơ cấu tài sản</t>
         </is>
       </c>
-      <c r="B76" s="20" t="n"/>
-      <c r="C76" s="20" t="n"/>
-      <c r="D76" s="20" t="n"/>
-      <c r="E76" s="20" t="n"/>
-      <c r="F76" s="20" t="n"/>
-      <c r="G76" s="20" t="n"/>
-      <c r="H76" s="20" t="n"/>
-      <c r="I76" s="20" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="20" t="inlineStr">
+      <c r="B85" s="29" t="n"/>
+      <c r="C85" s="29" t="n"/>
+      <c r="D85" s="29" t="n"/>
+      <c r="E85" s="29" t="n"/>
+      <c r="F85" s="29" t="n"/>
+      <c r="G85" s="29" t="n"/>
+      <c r="H85" s="29" t="n"/>
+      <c r="I85" s="29" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="29" t="inlineStr">
         <is>
           <t>TSCĐ vô hình</t>
         </is>
       </c>
-      <c r="B77" s="22">
-        <f>IFERROR(B$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C77" s="22">
-        <f>IFERROR(C$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D77" s="22">
-        <f>IFERROR(D$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E77" s="22">
-        <f>IFERROR(E$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F77" s="22">
-        <f>IFERROR(F$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G77" s="22">
-        <f>IFERROR(G$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H77" s="22">
-        <f>IFERROR(H$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I77" s="22">
-        <f>IFERROR(I$45,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="20" t="inlineStr">
+      <c r="B86" s="31">
+        <f>IFERROR(B$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C86" s="31">
+        <f>IFERROR(C$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D86" s="31">
+        <f>IFERROR(D$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E86" s="31">
+        <f>IFERROR(E$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F86" s="31">
+        <f>IFERROR(F$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G86" s="31">
+        <f>IFERROR(G$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H86" s="31">
+        <f>IFERROR(H$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I86" s="31">
+        <f>IFERROR(I$30,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="29" t="inlineStr">
         <is>
           <t>Tài sản vô hình/Giá trị sổ sách</t>
         </is>
       </c>
-      <c r="B78" s="21">
-        <f>IFERROR(B$45/B$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C78" s="21">
-        <f>IFERROR(C$45/C$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D78" s="21">
-        <f>IFERROR(D$45/D$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E78" s="21">
-        <f>IFERROR(E$45/E$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F78" s="21">
-        <f>IFERROR(F$45/F$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G78" s="21">
-        <f>IFERROR(G$45/G$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H78" s="21">
-        <f>IFERROR(H$45/H$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I78" s="21">
-        <f>IFERROR(I$45/I$24,"n/a")</f>
+      <c r="B87" s="30">
+        <f>IFERROR(B$30/B$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C87" s="30">
+        <f>IFERROR(C$30/C$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D87" s="30">
+        <f>IFERROR(D$30/D$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E87" s="30">
+        <f>IFERROR(E$30/E$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F87" s="30">
+        <f>IFERROR(F$30/F$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G87" s="30">
+        <f>IFERROR(G$30/G$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H87" s="30">
+        <f>IFERROR(H$30/H$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I87" s="30">
+        <f>IFERROR(I$30/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -9365,18 +9665,6 @@
       <formula>0.15</formula>
     </cfRule>
     <cfRule type="cellIs" priority="15" operator="lessThan" dxfId="1">
-      <formula>0.15</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4:I5">
-    <cfRule type="cellIs" priority="11" operator="lessThan" dxfId="1">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="12" operator="greaterThanOrEqual" dxfId="0">
-      <formula>0.15</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="13" operator="between" dxfId="2">
-      <formula>0.1</formula>
       <formula>0.15</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9390,11 +9678,6 @@
     <cfRule type="cellIs" priority="10" operator="between" dxfId="2">
       <formula>0.1</formula>
       <formula>0.3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7:I7">
-    <cfRule type="cellIs" priority="7" operator="greaterThanOrEqual" dxfId="0">
-      <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:I8 B11:I11">
@@ -9420,6 +9703,23 @@
       <formula>0.3</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B4:J5">
+    <cfRule type="cellIs" priority="11" operator="lessThan" dxfId="1">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0.15</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="13" operator="between" dxfId="2">
+      <formula>0.1</formula>
+      <formula>0.15</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:J7">
+    <cfRule type="cellIs" priority="7" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9430,22 +9730,1632 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11.75" customWidth="1" min="1" max="1"/>
+    <col width="17.5" customWidth="1" min="2" max="2"/>
+    <col width="11.75" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1">
-        <f>A1+B1</f>
-        <v/>
-      </c>
-    </row>
+    <row r="1" ht="13.5" customHeight="1">
+      <c r="A1" s="29" t="n"/>
+      <c r="B1" s="29" t="inlineStr">
+        <is>
+          <t>Q4/2025</t>
+        </is>
+      </c>
+      <c r="C1" s="29" t="inlineStr">
+        <is>
+          <t>Q1/2026</t>
+        </is>
+      </c>
+      <c r="D1" s="29" t="inlineStr">
+        <is>
+          <t>Q2/2026</t>
+        </is>
+      </c>
+      <c r="E1" s="29" t="inlineStr">
+        <is>
+          <t>Q3/2026</t>
+        </is>
+      </c>
+      <c r="F1" s="29" t="inlineStr">
+        <is>
+          <t>Q4/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="13.5" customHeight="1">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Số CP</t>
+        </is>
+      </c>
+      <c r="B2" s="34" t="n">
+        <v>178815054</v>
+      </c>
+      <c r="C2" s="34" t="n">
+        <v>178815054</v>
+      </c>
+      <c r="D2" s="34" t="n">
+        <v>178815054</v>
+      </c>
+      <c r="E2" s="34" t="n">
+        <v>178815054</v>
+      </c>
+      <c r="F2" s="34" t="n">
+        <v>178815054</v>
+      </c>
+    </row>
+    <row r="3" ht="13.5" customHeight="1">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>Thị giá</t>
+        </is>
+      </c>
+      <c r="B3" s="34" t="n">
+        <v>147500</v>
+      </c>
+      <c r="C3" s="34" t="n">
+        <v>147500</v>
+      </c>
+      <c r="D3" s="34" t="n">
+        <v>147500</v>
+      </c>
+      <c r="E3" s="34" t="n">
+        <v>147500</v>
+      </c>
+      <c r="F3" s="34" t="n">
+        <v>147500</v>
+      </c>
+    </row>
+    <row r="4" ht="13.5" customHeight="1">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>Vốn hoá</t>
+        </is>
+      </c>
+      <c r="B4" s="34">
+        <f>B2*B3</f>
+        <v/>
+      </c>
+      <c r="C4" s="34">
+        <f>C2*C3</f>
+        <v/>
+      </c>
+      <c r="D4" s="34">
+        <f>D2*D3</f>
+        <v/>
+      </c>
+      <c r="E4" s="34">
+        <f>E2*E3</f>
+        <v/>
+      </c>
+      <c r="F4" s="34">
+        <f>F2*F3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="13.5" customHeight="1"/>
+    <row r="6" ht="13.5" customHeight="1">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>VCSH</t>
+        </is>
+      </c>
+      <c r="B6" s="34">
+        <f>chi_so_tai_chinh!I39</f>
+        <v/>
+      </c>
+      <c r="C6" s="34" t="n">
+        <v>5514000000000</v>
+      </c>
+      <c r="D6" s="34">
+        <f>$C$6*(($F$6/$C$6)^(1/3))</f>
+        <v/>
+      </c>
+      <c r="E6" s="34">
+        <f>$C$6*(($F$6/$C$6)^(2/3))</f>
+        <v/>
+      </c>
+      <c r="F6" s="34">
+        <f>chi_so_tai_chinh!J39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="13.5" customHeight="1">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>LICĐKKS</t>
+        </is>
+      </c>
+      <c r="B7" s="34">
+        <f>chi_so_tai_chinh!I41</f>
+        <v/>
+      </c>
+      <c r="C7" s="34">
+        <f>chi_so_tai_chinh!J41</f>
+        <v/>
+      </c>
+      <c r="D7" s="34">
+        <f>chi_so_tai_chinh!K41</f>
+        <v/>
+      </c>
+      <c r="E7" s="34">
+        <f>chi_so_tai_chinh!L41</f>
+        <v/>
+      </c>
+      <c r="F7" s="34">
+        <f>chi_so_tai_chinh!M41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="13.5" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>BV</t>
+        </is>
+      </c>
+      <c r="B8" s="34">
+        <f>B6-B7</f>
+        <v/>
+      </c>
+      <c r="C8" s="34">
+        <f>C6-C7</f>
+        <v/>
+      </c>
+      <c r="D8" s="34">
+        <f>D6-D7</f>
+        <v/>
+      </c>
+      <c r="E8" s="34">
+        <f>E6-E7</f>
+        <v/>
+      </c>
+      <c r="F8" s="34">
+        <f>F6-F7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="13.5" customHeight="1">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>BVPS</t>
+        </is>
+      </c>
+      <c r="B9" s="35">
+        <f>B8/B2</f>
+        <v/>
+      </c>
+      <c r="C9" s="35">
+        <f>C8/C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="35">
+        <f>D8/D2</f>
+        <v/>
+      </c>
+      <c r="E9" s="35">
+        <f>E8/E2</f>
+        <v/>
+      </c>
+      <c r="F9" s="35">
+        <f>F8/F2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="13.5" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="B10" s="36">
+        <f>B3/B9</f>
+        <v/>
+      </c>
+      <c r="C10" s="36">
+        <f>C3/C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="36">
+        <f>D3/D9</f>
+        <v/>
+      </c>
+      <c r="E10" s="36">
+        <f>E3/E9</f>
+        <v/>
+      </c>
+      <c r="F10" s="36">
+        <f>F3/F9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="13.5" customHeight="1">
+      <c r="H11" s="37" t="n"/>
+      <c r="I11" s="37" t="n"/>
+      <c r="J11" s="37" t="n"/>
+    </row>
+    <row r="12" ht="13.5" customHeight="1">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="B12" s="34">
+        <f>chi_so_tai_chinh!I43</f>
+        <v/>
+      </c>
+      <c r="C12" s="34">
+        <f>$B$12*(($F$12/$B$12)^(1/4))</f>
+        <v/>
+      </c>
+      <c r="D12" s="34">
+        <f>$B$12*(($F$12/$B$12)^(2/4))</f>
+        <v/>
+      </c>
+      <c r="E12" s="34">
+        <f>$B$12*(($F$12/$B$12)^(3/4))</f>
+        <v/>
+      </c>
+      <c r="F12" s="34">
+        <f>chi_so_tai_chinh!J43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="13.5" customHeight="1">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>DT per share</t>
+        </is>
+      </c>
+      <c r="B13" s="35">
+        <f>B12/C2</f>
+        <v/>
+      </c>
+      <c r="C13" s="35">
+        <f>C12/C2</f>
+        <v/>
+      </c>
+      <c r="D13" s="35">
+        <f>D12/D2</f>
+        <v/>
+      </c>
+      <c r="E13" s="35">
+        <f>E12/E2</f>
+        <v/>
+      </c>
+      <c r="F13" s="35">
+        <f>F12/F2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="13.5" customHeight="1">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+      <c r="B14" s="36">
+        <f>C3/B13</f>
+        <v/>
+      </c>
+      <c r="C14" s="36">
+        <f>C4/C12</f>
+        <v/>
+      </c>
+      <c r="D14" s="36">
+        <f>D4/D12</f>
+        <v/>
+      </c>
+      <c r="E14" s="36">
+        <f>E4/E12</f>
+        <v/>
+      </c>
+      <c r="F14" s="36">
+        <f>F4/F12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="13.5" customHeight="1"/>
+    <row r="16" ht="13.5" customHeight="1">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>Earning</t>
+        </is>
+      </c>
+      <c r="B16" s="34">
+        <f>chi_so_tai_chinh!I52</f>
+        <v/>
+      </c>
+      <c r="C16" s="34">
+        <f>$B$16*(($F$16/$B$16)^(1/4))</f>
+        <v/>
+      </c>
+      <c r="D16" s="34">
+        <f>$B$16*(($F$16/$B$16)^(2/4))</f>
+        <v/>
+      </c>
+      <c r="E16" s="34">
+        <f>$B$16*(($F$16/$B$16)^(3/4))</f>
+        <v/>
+      </c>
+      <c r="F16" s="34">
+        <f>chi_so_tai_chinh!J52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="13.5" customHeight="1">
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B17" s="35">
+        <f>B16/$F$2</f>
+        <v/>
+      </c>
+      <c r="C17" s="35">
+        <f>C16/$F$2</f>
+        <v/>
+      </c>
+      <c r="D17" s="35">
+        <f>D16/$F$2</f>
+        <v/>
+      </c>
+      <c r="E17" s="35">
+        <f>E16/$F$2</f>
+        <v/>
+      </c>
+      <c r="F17" s="35">
+        <f>F16/$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="13.5" customHeight="1">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="B18" s="36">
+        <f>$F$3/B17</f>
+        <v/>
+      </c>
+      <c r="C18" s="36">
+        <f>$F$3/C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="36">
+        <f>$F$3/D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="36">
+        <f>$F$3/E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="36">
+        <f>$F$3/F17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="13.5" customHeight="1"/>
+    <row r="20" ht="13.5" customHeight="1"/>
+    <row r="21" ht="13.5" customHeight="1"/>
+    <row r="22" ht="13.5" customHeight="1"/>
+    <row r="23" ht="13.5" customHeight="1"/>
+    <row r="24" ht="13.5" customHeight="1"/>
+    <row r="25" ht="13.5" customHeight="1"/>
+    <row r="26" ht="13.5" customHeight="1"/>
+    <row r="27" ht="13.5" customHeight="1"/>
+    <row r="28" ht="13.5" customHeight="1"/>
+    <row r="29" ht="13.5" customHeight="1"/>
+    <row r="30" ht="13.5" customHeight="1"/>
+    <row r="31" ht="13.5" customHeight="1"/>
+    <row r="32" ht="13.5" customHeight="1"/>
+    <row r="33" ht="13.5" customHeight="1"/>
+    <row r="34" ht="13.5" customHeight="1"/>
+    <row r="35" ht="13.5" customHeight="1"/>
+    <row r="36" ht="13.5" customHeight="1"/>
+    <row r="37" ht="13.5" customHeight="1"/>
+    <row r="38" ht="13.5" customHeight="1"/>
+    <row r="39" ht="13.5" customHeight="1"/>
+    <row r="40" ht="13.5" customHeight="1"/>
+    <row r="41" ht="13.5" customHeight="1"/>
+    <row r="42" ht="13.5" customHeight="1"/>
+    <row r="43" ht="13.5" customHeight="1"/>
+    <row r="44" ht="13.5" customHeight="1"/>
+    <row r="45" ht="13.5" customHeight="1"/>
+    <row r="46" ht="13.5" customHeight="1"/>
+    <row r="47" ht="13.5" customHeight="1"/>
+    <row r="48" ht="13.5" customHeight="1"/>
+    <row r="49" ht="13.5" customHeight="1"/>
+    <row r="50" ht="13.5" customHeight="1"/>
+    <row r="51" ht="13.5" customHeight="1"/>
+    <row r="52" ht="13.5" customHeight="1"/>
+    <row r="53" ht="13.5" customHeight="1"/>
+    <row r="54" ht="13.5" customHeight="1"/>
+    <row r="55" ht="13.5" customHeight="1"/>
+    <row r="56" ht="13.5" customHeight="1"/>
+    <row r="57" ht="13.5" customHeight="1"/>
+    <row r="58" ht="13.5" customHeight="1"/>
+    <row r="59" ht="13.5" customHeight="1"/>
+    <row r="60" ht="13.5" customHeight="1"/>
+    <row r="61" ht="13.5" customHeight="1"/>
+    <row r="62" ht="13.5" customHeight="1"/>
+    <row r="63" ht="13.5" customHeight="1"/>
+    <row r="64" ht="13.5" customHeight="1"/>
+    <row r="65" ht="13.5" customHeight="1"/>
+    <row r="66" ht="13.5" customHeight="1"/>
+    <row r="67" ht="13.5" customHeight="1"/>
+    <row r="68" ht="13.5" customHeight="1"/>
+    <row r="69" ht="13.5" customHeight="1"/>
+    <row r="70" ht="13.5" customHeight="1"/>
+    <row r="71" ht="13.5" customHeight="1"/>
+    <row r="72" ht="13.5" customHeight="1"/>
+    <row r="73" ht="13.5" customHeight="1"/>
+    <row r="74" ht="13.5" customHeight="1"/>
+    <row r="75" ht="13.5" customHeight="1"/>
+    <row r="76" ht="13.5" customHeight="1"/>
+    <row r="77" ht="13.5" customHeight="1"/>
+    <row r="78" ht="13.5" customHeight="1"/>
+    <row r="79" ht="13.5" customHeight="1"/>
+    <row r="80" ht="13.5" customHeight="1"/>
+    <row r="81" ht="13.5" customHeight="1"/>
+    <row r="82" ht="13.5" customHeight="1"/>
+    <row r="83" ht="13.5" customHeight="1"/>
+    <row r="84" ht="13.5" customHeight="1"/>
+    <row r="85" ht="13.5" customHeight="1"/>
+    <row r="86" ht="13.5" customHeight="1"/>
+    <row r="87" ht="13.5" customHeight="1"/>
+    <row r="88" ht="13.5" customHeight="1"/>
+    <row r="89" ht="13.5" customHeight="1"/>
+    <row r="90" ht="13.5" customHeight="1"/>
+    <row r="91" ht="13.5" customHeight="1"/>
+    <row r="92" ht="13.5" customHeight="1"/>
+    <row r="93" ht="13.5" customHeight="1"/>
+    <row r="94" ht="13.5" customHeight="1"/>
+    <row r="95" ht="13.5" customHeight="1"/>
+    <row r="96" ht="13.5" customHeight="1"/>
+    <row r="97" ht="13.5" customHeight="1"/>
+    <row r="98" ht="13.5" customHeight="1"/>
+    <row r="99" ht="13.5" customHeight="1"/>
+    <row r="100" ht="13.5" customHeight="1"/>
+    <row r="101" ht="13.5" customHeight="1"/>
+    <row r="102" ht="13.5" customHeight="1"/>
+    <row r="103" ht="13.5" customHeight="1"/>
+    <row r="104" ht="13.5" customHeight="1"/>
+    <row r="105" ht="13.5" customHeight="1"/>
+    <row r="106" ht="13.5" customHeight="1"/>
+    <row r="107" ht="13.5" customHeight="1"/>
+    <row r="108" ht="13.5" customHeight="1"/>
+    <row r="109" ht="13.5" customHeight="1"/>
+    <row r="110" ht="13.5" customHeight="1"/>
+    <row r="111" ht="13.5" customHeight="1"/>
+    <row r="112" ht="13.5" customHeight="1"/>
+    <row r="113" ht="13.5" customHeight="1"/>
+    <row r="114" ht="13.5" customHeight="1"/>
+    <row r="115" ht="13.5" customHeight="1"/>
+    <row r="116" ht="13.5" customHeight="1"/>
+    <row r="117" ht="13.5" customHeight="1"/>
+    <row r="118" ht="13.5" customHeight="1"/>
+    <row r="119" ht="13.5" customHeight="1"/>
+    <row r="120" ht="13.5" customHeight="1"/>
+    <row r="121" ht="13.5" customHeight="1"/>
+    <row r="122" ht="13.5" customHeight="1"/>
+    <row r="123" ht="13.5" customHeight="1"/>
+    <row r="124" ht="13.5" customHeight="1"/>
+    <row r="125" ht="13.5" customHeight="1"/>
+    <row r="126" ht="13.5" customHeight="1"/>
+    <row r="127" ht="13.5" customHeight="1"/>
+    <row r="128" ht="13.5" customHeight="1"/>
+    <row r="129" ht="13.5" customHeight="1"/>
+    <row r="130" ht="13.5" customHeight="1"/>
+    <row r="131" ht="13.5" customHeight="1"/>
+    <row r="132" ht="13.5" customHeight="1"/>
+    <row r="133" ht="13.5" customHeight="1"/>
+    <row r="134" ht="13.5" customHeight="1"/>
+    <row r="135" ht="13.5" customHeight="1"/>
+    <row r="136" ht="13.5" customHeight="1"/>
+    <row r="137" ht="13.5" customHeight="1"/>
+    <row r="138" ht="13.5" customHeight="1"/>
+    <row r="139" ht="13.5" customHeight="1"/>
+    <row r="140" ht="13.5" customHeight="1"/>
+    <row r="141" ht="13.5" customHeight="1"/>
+    <row r="142" ht="13.5" customHeight="1"/>
+    <row r="143" ht="13.5" customHeight="1"/>
+    <row r="144" ht="13.5" customHeight="1"/>
+    <row r="145" ht="13.5" customHeight="1"/>
+    <row r="146" ht="13.5" customHeight="1"/>
+    <row r="147" ht="13.5" customHeight="1"/>
+    <row r="148" ht="13.5" customHeight="1"/>
+    <row r="149" ht="13.5" customHeight="1"/>
+    <row r="150" ht="13.5" customHeight="1"/>
+    <row r="151" ht="13.5" customHeight="1"/>
+    <row r="152" ht="13.5" customHeight="1"/>
+    <row r="153" ht="13.5" customHeight="1"/>
+    <row r="154" ht="13.5" customHeight="1"/>
+    <row r="155" ht="13.5" customHeight="1"/>
+    <row r="156" ht="13.5" customHeight="1"/>
+    <row r="157" ht="13.5" customHeight="1"/>
+    <row r="158" ht="13.5" customHeight="1"/>
+    <row r="159" ht="13.5" customHeight="1"/>
+    <row r="160" ht="13.5" customHeight="1"/>
+    <row r="161" ht="13.5" customHeight="1"/>
+    <row r="162" ht="13.5" customHeight="1"/>
+    <row r="163" ht="13.5" customHeight="1"/>
+    <row r="164" ht="13.5" customHeight="1"/>
+    <row r="165" ht="13.5" customHeight="1"/>
+    <row r="166" ht="13.5" customHeight="1"/>
+    <row r="167" ht="13.5" customHeight="1"/>
+    <row r="168" ht="13.5" customHeight="1"/>
+    <row r="169" ht="13.5" customHeight="1"/>
+    <row r="170" ht="13.5" customHeight="1"/>
+    <row r="171" ht="13.5" customHeight="1"/>
+    <row r="172" ht="13.5" customHeight="1"/>
+    <row r="173" ht="13.5" customHeight="1"/>
+    <row r="174" ht="13.5" customHeight="1"/>
+    <row r="175" ht="13.5" customHeight="1"/>
+    <row r="176" ht="13.5" customHeight="1"/>
+    <row r="177" ht="13.5" customHeight="1"/>
+    <row r="178" ht="13.5" customHeight="1"/>
+    <row r="179" ht="13.5" customHeight="1"/>
+    <row r="180" ht="13.5" customHeight="1"/>
+    <row r="181" ht="13.5" customHeight="1"/>
+    <row r="182" ht="13.5" customHeight="1"/>
+    <row r="183" ht="13.5" customHeight="1"/>
+    <row r="184" ht="13.5" customHeight="1"/>
+    <row r="185" ht="13.5" customHeight="1"/>
+    <row r="186" ht="13.5" customHeight="1"/>
+    <row r="187" ht="13.5" customHeight="1"/>
+    <row r="188" ht="13.5" customHeight="1"/>
+    <row r="189" ht="13.5" customHeight="1"/>
+    <row r="190" ht="13.5" customHeight="1"/>
+    <row r="191" ht="13.5" customHeight="1"/>
+    <row r="192" ht="13.5" customHeight="1"/>
+    <row r="193" ht="13.5" customHeight="1"/>
+    <row r="194" ht="13.5" customHeight="1"/>
+    <row r="195" ht="13.5" customHeight="1"/>
+    <row r="196" ht="13.5" customHeight="1"/>
+    <row r="197" ht="13.5" customHeight="1"/>
+    <row r="198" ht="13.5" customHeight="1"/>
+    <row r="199" ht="13.5" customHeight="1"/>
+    <row r="200" ht="13.5" customHeight="1"/>
+    <row r="201" ht="13.5" customHeight="1"/>
+    <row r="202" ht="13.5" customHeight="1"/>
+    <row r="203" ht="13.5" customHeight="1"/>
+    <row r="204" ht="13.5" customHeight="1"/>
+    <row r="205" ht="13.5" customHeight="1"/>
+    <row r="206" ht="13.5" customHeight="1"/>
+    <row r="207" ht="13.5" customHeight="1"/>
+    <row r="208" ht="13.5" customHeight="1"/>
+    <row r="209" ht="13.5" customHeight="1"/>
+    <row r="210" ht="13.5" customHeight="1"/>
+    <row r="211" ht="13.5" customHeight="1"/>
+    <row r="212" ht="13.5" customHeight="1"/>
+    <row r="213" ht="13.5" customHeight="1"/>
+    <row r="214" ht="13.5" customHeight="1"/>
+    <row r="215" ht="13.5" customHeight="1"/>
+    <row r="216" ht="13.5" customHeight="1"/>
+    <row r="217" ht="13.5" customHeight="1"/>
+    <row r="218" ht="13.5" customHeight="1"/>
+    <row r="219" ht="13.5" customHeight="1"/>
+    <row r="220" ht="13.5" customHeight="1"/>
+    <row r="221" ht="13.5" customHeight="1"/>
+    <row r="222" ht="13.5" customHeight="1"/>
+    <row r="223" ht="13.5" customHeight="1"/>
+    <row r="224" ht="13.5" customHeight="1"/>
+    <row r="225" ht="13.5" customHeight="1"/>
+    <row r="226" ht="13.5" customHeight="1"/>
+    <row r="227" ht="13.5" customHeight="1"/>
+    <row r="228" ht="13.5" customHeight="1"/>
+    <row r="229" ht="13.5" customHeight="1"/>
+    <row r="230" ht="13.5" customHeight="1"/>
+    <row r="231" ht="13.5" customHeight="1"/>
+    <row r="232" ht="13.5" customHeight="1"/>
+    <row r="233" ht="13.5" customHeight="1"/>
+    <row r="234" ht="13.5" customHeight="1"/>
+    <row r="235" ht="13.5" customHeight="1"/>
+    <row r="236" ht="13.5" customHeight="1"/>
+    <row r="237" ht="13.5" customHeight="1"/>
+    <row r="238" ht="13.5" customHeight="1"/>
+    <row r="239" ht="13.5" customHeight="1"/>
+    <row r="240" ht="13.5" customHeight="1"/>
+    <row r="241" ht="13.5" customHeight="1"/>
+    <row r="242" ht="13.5" customHeight="1"/>
+    <row r="243" ht="13.5" customHeight="1"/>
+    <row r="244" ht="13.5" customHeight="1"/>
+    <row r="245" ht="13.5" customHeight="1"/>
+    <row r="246" ht="13.5" customHeight="1"/>
+    <row r="247" ht="13.5" customHeight="1"/>
+    <row r="248" ht="13.5" customHeight="1"/>
+    <row r="249" ht="13.5" customHeight="1"/>
+    <row r="250" ht="13.5" customHeight="1"/>
+    <row r="251" ht="13.5" customHeight="1"/>
+    <row r="252" ht="13.5" customHeight="1"/>
+    <row r="253" ht="13.5" customHeight="1"/>
+    <row r="254" ht="13.5" customHeight="1"/>
+    <row r="255" ht="13.5" customHeight="1"/>
+    <row r="256" ht="13.5" customHeight="1"/>
+    <row r="257" ht="13.5" customHeight="1"/>
+    <row r="258" ht="13.5" customHeight="1"/>
+    <row r="259" ht="13.5" customHeight="1"/>
+    <row r="260" ht="13.5" customHeight="1"/>
+    <row r="261" ht="13.5" customHeight="1"/>
+    <row r="262" ht="13.5" customHeight="1"/>
+    <row r="263" ht="13.5" customHeight="1"/>
+    <row r="264" ht="13.5" customHeight="1"/>
+    <row r="265" ht="13.5" customHeight="1"/>
+    <row r="266" ht="13.5" customHeight="1"/>
+    <row r="267" ht="13.5" customHeight="1"/>
+    <row r="268" ht="13.5" customHeight="1"/>
+    <row r="269" ht="13.5" customHeight="1"/>
+    <row r="270" ht="13.5" customHeight="1"/>
+    <row r="271" ht="13.5" customHeight="1"/>
+    <row r="272" ht="13.5" customHeight="1"/>
+    <row r="273" ht="13.5" customHeight="1"/>
+    <row r="274" ht="13.5" customHeight="1"/>
+    <row r="275" ht="13.5" customHeight="1"/>
+    <row r="276" ht="13.5" customHeight="1"/>
+    <row r="277" ht="13.5" customHeight="1"/>
+    <row r="278" ht="13.5" customHeight="1"/>
+    <row r="279" ht="13.5" customHeight="1"/>
+    <row r="280" ht="13.5" customHeight="1"/>
+    <row r="281" ht="13.5" customHeight="1"/>
+    <row r="282" ht="13.5" customHeight="1"/>
+    <row r="283" ht="13.5" customHeight="1"/>
+    <row r="284" ht="13.5" customHeight="1"/>
+    <row r="285" ht="13.5" customHeight="1"/>
+    <row r="286" ht="13.5" customHeight="1"/>
+    <row r="287" ht="13.5" customHeight="1"/>
+    <row r="288" ht="13.5" customHeight="1"/>
+    <row r="289" ht="13.5" customHeight="1"/>
+    <row r="290" ht="13.5" customHeight="1"/>
+    <row r="291" ht="13.5" customHeight="1"/>
+    <row r="292" ht="13.5" customHeight="1"/>
+    <row r="293" ht="13.5" customHeight="1"/>
+    <row r="294" ht="13.5" customHeight="1"/>
+    <row r="295" ht="13.5" customHeight="1"/>
+    <row r="296" ht="13.5" customHeight="1"/>
+    <row r="297" ht="13.5" customHeight="1"/>
+    <row r="298" ht="13.5" customHeight="1"/>
+    <row r="299" ht="13.5" customHeight="1"/>
+    <row r="300" ht="13.5" customHeight="1"/>
+    <row r="301" ht="13.5" customHeight="1"/>
+    <row r="302" ht="13.5" customHeight="1"/>
+    <row r="303" ht="13.5" customHeight="1"/>
+    <row r="304" ht="13.5" customHeight="1"/>
+    <row r="305" ht="13.5" customHeight="1"/>
+    <row r="306" ht="13.5" customHeight="1"/>
+    <row r="307" ht="13.5" customHeight="1"/>
+    <row r="308" ht="13.5" customHeight="1"/>
+    <row r="309" ht="13.5" customHeight="1"/>
+    <row r="310" ht="13.5" customHeight="1"/>
+    <row r="311" ht="13.5" customHeight="1"/>
+    <row r="312" ht="13.5" customHeight="1"/>
+    <row r="313" ht="13.5" customHeight="1"/>
+    <row r="314" ht="13.5" customHeight="1"/>
+    <row r="315" ht="13.5" customHeight="1"/>
+    <row r="316" ht="13.5" customHeight="1"/>
+    <row r="317" ht="13.5" customHeight="1"/>
+    <row r="318" ht="13.5" customHeight="1"/>
+    <row r="319" ht="13.5" customHeight="1"/>
+    <row r="320" ht="13.5" customHeight="1"/>
+    <row r="321" ht="13.5" customHeight="1"/>
+    <row r="322" ht="13.5" customHeight="1"/>
+    <row r="323" ht="13.5" customHeight="1"/>
+    <row r="324" ht="13.5" customHeight="1"/>
+    <row r="325" ht="13.5" customHeight="1"/>
+    <row r="326" ht="13.5" customHeight="1"/>
+    <row r="327" ht="13.5" customHeight="1"/>
+    <row r="328" ht="13.5" customHeight="1"/>
+    <row r="329" ht="13.5" customHeight="1"/>
+    <row r="330" ht="13.5" customHeight="1"/>
+    <row r="331" ht="13.5" customHeight="1"/>
+    <row r="332" ht="13.5" customHeight="1"/>
+    <row r="333" ht="13.5" customHeight="1"/>
+    <row r="334" ht="13.5" customHeight="1"/>
+    <row r="335" ht="13.5" customHeight="1"/>
+    <row r="336" ht="13.5" customHeight="1"/>
+    <row r="337" ht="13.5" customHeight="1"/>
+    <row r="338" ht="13.5" customHeight="1"/>
+    <row r="339" ht="13.5" customHeight="1"/>
+    <row r="340" ht="13.5" customHeight="1"/>
+    <row r="341" ht="13.5" customHeight="1"/>
+    <row r="342" ht="13.5" customHeight="1"/>
+    <row r="343" ht="13.5" customHeight="1"/>
+    <row r="344" ht="13.5" customHeight="1"/>
+    <row r="345" ht="13.5" customHeight="1"/>
+    <row r="346" ht="13.5" customHeight="1"/>
+    <row r="347" ht="13.5" customHeight="1"/>
+    <row r="348" ht="13.5" customHeight="1"/>
+    <row r="349" ht="13.5" customHeight="1"/>
+    <row r="350" ht="13.5" customHeight="1"/>
+    <row r="351" ht="13.5" customHeight="1"/>
+    <row r="352" ht="13.5" customHeight="1"/>
+    <row r="353" ht="13.5" customHeight="1"/>
+    <row r="354" ht="13.5" customHeight="1"/>
+    <row r="355" ht="13.5" customHeight="1"/>
+    <row r="356" ht="13.5" customHeight="1"/>
+    <row r="357" ht="13.5" customHeight="1"/>
+    <row r="358" ht="13.5" customHeight="1"/>
+    <row r="359" ht="13.5" customHeight="1"/>
+    <row r="360" ht="13.5" customHeight="1"/>
+    <row r="361" ht="13.5" customHeight="1"/>
+    <row r="362" ht="13.5" customHeight="1"/>
+    <row r="363" ht="13.5" customHeight="1"/>
+    <row r="364" ht="13.5" customHeight="1"/>
+    <row r="365" ht="13.5" customHeight="1"/>
+    <row r="366" ht="13.5" customHeight="1"/>
+    <row r="367" ht="13.5" customHeight="1"/>
+    <row r="368" ht="13.5" customHeight="1"/>
+    <row r="369" ht="13.5" customHeight="1"/>
+    <row r="370" ht="13.5" customHeight="1"/>
+    <row r="371" ht="13.5" customHeight="1"/>
+    <row r="372" ht="13.5" customHeight="1"/>
+    <row r="373" ht="13.5" customHeight="1"/>
+    <row r="374" ht="13.5" customHeight="1"/>
+    <row r="375" ht="13.5" customHeight="1"/>
+    <row r="376" ht="13.5" customHeight="1"/>
+    <row r="377" ht="13.5" customHeight="1"/>
+    <row r="378" ht="13.5" customHeight="1"/>
+    <row r="379" ht="13.5" customHeight="1"/>
+    <row r="380" ht="13.5" customHeight="1"/>
+    <row r="381" ht="13.5" customHeight="1"/>
+    <row r="382" ht="13.5" customHeight="1"/>
+    <row r="383" ht="13.5" customHeight="1"/>
+    <row r="384" ht="13.5" customHeight="1"/>
+    <row r="385" ht="13.5" customHeight="1"/>
+    <row r="386" ht="13.5" customHeight="1"/>
+    <row r="387" ht="13.5" customHeight="1"/>
+    <row r="388" ht="13.5" customHeight="1"/>
+    <row r="389" ht="13.5" customHeight="1"/>
+    <row r="390" ht="13.5" customHeight="1"/>
+    <row r="391" ht="13.5" customHeight="1"/>
+    <row r="392" ht="13.5" customHeight="1"/>
+    <row r="393" ht="13.5" customHeight="1"/>
+    <row r="394" ht="13.5" customHeight="1"/>
+    <row r="395" ht="13.5" customHeight="1"/>
+    <row r="396" ht="13.5" customHeight="1"/>
+    <row r="397" ht="13.5" customHeight="1"/>
+    <row r="398" ht="13.5" customHeight="1"/>
+    <row r="399" ht="13.5" customHeight="1"/>
+    <row r="400" ht="13.5" customHeight="1"/>
+    <row r="401" ht="13.5" customHeight="1"/>
+    <row r="402" ht="13.5" customHeight="1"/>
+    <row r="403" ht="13.5" customHeight="1"/>
+    <row r="404" ht="13.5" customHeight="1"/>
+    <row r="405" ht="13.5" customHeight="1"/>
+    <row r="406" ht="13.5" customHeight="1"/>
+    <row r="407" ht="13.5" customHeight="1"/>
+    <row r="408" ht="13.5" customHeight="1"/>
+    <row r="409" ht="13.5" customHeight="1"/>
+    <row r="410" ht="13.5" customHeight="1"/>
+    <row r="411" ht="13.5" customHeight="1"/>
+    <row r="412" ht="13.5" customHeight="1"/>
+    <row r="413" ht="13.5" customHeight="1"/>
+    <row r="414" ht="13.5" customHeight="1"/>
+    <row r="415" ht="13.5" customHeight="1"/>
+    <row r="416" ht="13.5" customHeight="1"/>
+    <row r="417" ht="13.5" customHeight="1"/>
+    <row r="418" ht="13.5" customHeight="1"/>
+    <row r="419" ht="13.5" customHeight="1"/>
+    <row r="420" ht="13.5" customHeight="1"/>
+    <row r="421" ht="13.5" customHeight="1"/>
+    <row r="422" ht="13.5" customHeight="1"/>
+    <row r="423" ht="13.5" customHeight="1"/>
+    <row r="424" ht="13.5" customHeight="1"/>
+    <row r="425" ht="13.5" customHeight="1"/>
+    <row r="426" ht="13.5" customHeight="1"/>
+    <row r="427" ht="13.5" customHeight="1"/>
+    <row r="428" ht="13.5" customHeight="1"/>
+    <row r="429" ht="13.5" customHeight="1"/>
+    <row r="430" ht="13.5" customHeight="1"/>
+    <row r="431" ht="13.5" customHeight="1"/>
+    <row r="432" ht="13.5" customHeight="1"/>
+    <row r="433" ht="13.5" customHeight="1"/>
+    <row r="434" ht="13.5" customHeight="1"/>
+    <row r="435" ht="13.5" customHeight="1"/>
+    <row r="436" ht="13.5" customHeight="1"/>
+    <row r="437" ht="13.5" customHeight="1"/>
+    <row r="438" ht="13.5" customHeight="1"/>
+    <row r="439" ht="13.5" customHeight="1"/>
+    <row r="440" ht="13.5" customHeight="1"/>
+    <row r="441" ht="13.5" customHeight="1"/>
+    <row r="442" ht="13.5" customHeight="1"/>
+    <row r="443" ht="13.5" customHeight="1"/>
+    <row r="444" ht="13.5" customHeight="1"/>
+    <row r="445" ht="13.5" customHeight="1"/>
+    <row r="446" ht="13.5" customHeight="1"/>
+    <row r="447" ht="13.5" customHeight="1"/>
+    <row r="448" ht="13.5" customHeight="1"/>
+    <row r="449" ht="13.5" customHeight="1"/>
+    <row r="450" ht="13.5" customHeight="1"/>
+    <row r="451" ht="13.5" customHeight="1"/>
+    <row r="452" ht="13.5" customHeight="1"/>
+    <row r="453" ht="13.5" customHeight="1"/>
+    <row r="454" ht="13.5" customHeight="1"/>
+    <row r="455" ht="13.5" customHeight="1"/>
+    <row r="456" ht="13.5" customHeight="1"/>
+    <row r="457" ht="13.5" customHeight="1"/>
+    <row r="458" ht="13.5" customHeight="1"/>
+    <row r="459" ht="13.5" customHeight="1"/>
+    <row r="460" ht="13.5" customHeight="1"/>
+    <row r="461" ht="13.5" customHeight="1"/>
+    <row r="462" ht="13.5" customHeight="1"/>
+    <row r="463" ht="13.5" customHeight="1"/>
+    <row r="464" ht="13.5" customHeight="1"/>
+    <row r="465" ht="13.5" customHeight="1"/>
+    <row r="466" ht="13.5" customHeight="1"/>
+    <row r="467" ht="13.5" customHeight="1"/>
+    <row r="468" ht="13.5" customHeight="1"/>
+    <row r="469" ht="13.5" customHeight="1"/>
+    <row r="470" ht="13.5" customHeight="1"/>
+    <row r="471" ht="13.5" customHeight="1"/>
+    <row r="472" ht="13.5" customHeight="1"/>
+    <row r="473" ht="13.5" customHeight="1"/>
+    <row r="474" ht="13.5" customHeight="1"/>
+    <row r="475" ht="13.5" customHeight="1"/>
+    <row r="476" ht="13.5" customHeight="1"/>
+    <row r="477" ht="13.5" customHeight="1"/>
+    <row r="478" ht="13.5" customHeight="1"/>
+    <row r="479" ht="13.5" customHeight="1"/>
+    <row r="480" ht="13.5" customHeight="1"/>
+    <row r="481" ht="13.5" customHeight="1"/>
+    <row r="482" ht="13.5" customHeight="1"/>
+    <row r="483" ht="13.5" customHeight="1"/>
+    <row r="484" ht="13.5" customHeight="1"/>
+    <row r="485" ht="13.5" customHeight="1"/>
+    <row r="486" ht="13.5" customHeight="1"/>
+    <row r="487" ht="13.5" customHeight="1"/>
+    <row r="488" ht="13.5" customHeight="1"/>
+    <row r="489" ht="13.5" customHeight="1"/>
+    <row r="490" ht="13.5" customHeight="1"/>
+    <row r="491" ht="13.5" customHeight="1"/>
+    <row r="492" ht="13.5" customHeight="1"/>
+    <row r="493" ht="13.5" customHeight="1"/>
+    <row r="494" ht="13.5" customHeight="1"/>
+    <row r="495" ht="13.5" customHeight="1"/>
+    <row r="496" ht="13.5" customHeight="1"/>
+    <row r="497" ht="13.5" customHeight="1"/>
+    <row r="498" ht="13.5" customHeight="1"/>
+    <row r="499" ht="13.5" customHeight="1"/>
+    <row r="500" ht="13.5" customHeight="1"/>
+    <row r="501" ht="13.5" customHeight="1"/>
+    <row r="502" ht="13.5" customHeight="1"/>
+    <row r="503" ht="13.5" customHeight="1"/>
+    <row r="504" ht="13.5" customHeight="1"/>
+    <row r="505" ht="13.5" customHeight="1"/>
+    <row r="506" ht="13.5" customHeight="1"/>
+    <row r="507" ht="13.5" customHeight="1"/>
+    <row r="508" ht="13.5" customHeight="1"/>
+    <row r="509" ht="13.5" customHeight="1"/>
+    <row r="510" ht="13.5" customHeight="1"/>
+    <row r="511" ht="13.5" customHeight="1"/>
+    <row r="512" ht="13.5" customHeight="1"/>
+    <row r="513" ht="13.5" customHeight="1"/>
+    <row r="514" ht="13.5" customHeight="1"/>
+    <row r="515" ht="13.5" customHeight="1"/>
+    <row r="516" ht="13.5" customHeight="1"/>
+    <row r="517" ht="13.5" customHeight="1"/>
+    <row r="518" ht="13.5" customHeight="1"/>
+    <row r="519" ht="13.5" customHeight="1"/>
+    <row r="520" ht="13.5" customHeight="1"/>
+    <row r="521" ht="13.5" customHeight="1"/>
+    <row r="522" ht="13.5" customHeight="1"/>
+    <row r="523" ht="13.5" customHeight="1"/>
+    <row r="524" ht="13.5" customHeight="1"/>
+    <row r="525" ht="13.5" customHeight="1"/>
+    <row r="526" ht="13.5" customHeight="1"/>
+    <row r="527" ht="13.5" customHeight="1"/>
+    <row r="528" ht="13.5" customHeight="1"/>
+    <row r="529" ht="13.5" customHeight="1"/>
+    <row r="530" ht="13.5" customHeight="1"/>
+    <row r="531" ht="13.5" customHeight="1"/>
+    <row r="532" ht="13.5" customHeight="1"/>
+    <row r="533" ht="13.5" customHeight="1"/>
+    <row r="534" ht="13.5" customHeight="1"/>
+    <row r="535" ht="13.5" customHeight="1"/>
+    <row r="536" ht="13.5" customHeight="1"/>
+    <row r="537" ht="13.5" customHeight="1"/>
+    <row r="538" ht="13.5" customHeight="1"/>
+    <row r="539" ht="13.5" customHeight="1"/>
+    <row r="540" ht="13.5" customHeight="1"/>
+    <row r="541" ht="13.5" customHeight="1"/>
+    <row r="542" ht="13.5" customHeight="1"/>
+    <row r="543" ht="13.5" customHeight="1"/>
+    <row r="544" ht="13.5" customHeight="1"/>
+    <row r="545" ht="13.5" customHeight="1"/>
+    <row r="546" ht="13.5" customHeight="1"/>
+    <row r="547" ht="13.5" customHeight="1"/>
+    <row r="548" ht="13.5" customHeight="1"/>
+    <row r="549" ht="13.5" customHeight="1"/>
+    <row r="550" ht="13.5" customHeight="1"/>
+    <row r="551" ht="13.5" customHeight="1"/>
+    <row r="552" ht="13.5" customHeight="1"/>
+    <row r="553" ht="13.5" customHeight="1"/>
+    <row r="554" ht="13.5" customHeight="1"/>
+    <row r="555" ht="13.5" customHeight="1"/>
+    <row r="556" ht="13.5" customHeight="1"/>
+    <row r="557" ht="13.5" customHeight="1"/>
+    <row r="558" ht="13.5" customHeight="1"/>
+    <row r="559" ht="13.5" customHeight="1"/>
+    <row r="560" ht="13.5" customHeight="1"/>
+    <row r="561" ht="13.5" customHeight="1"/>
+    <row r="562" ht="13.5" customHeight="1"/>
+    <row r="563" ht="13.5" customHeight="1"/>
+    <row r="564" ht="13.5" customHeight="1"/>
+    <row r="565" ht="13.5" customHeight="1"/>
+    <row r="566" ht="13.5" customHeight="1"/>
+    <row r="567" ht="13.5" customHeight="1"/>
+    <row r="568" ht="13.5" customHeight="1"/>
+    <row r="569" ht="13.5" customHeight="1"/>
+    <row r="570" ht="13.5" customHeight="1"/>
+    <row r="571" ht="13.5" customHeight="1"/>
+    <row r="572" ht="13.5" customHeight="1"/>
+    <row r="573" ht="13.5" customHeight="1"/>
+    <row r="574" ht="13.5" customHeight="1"/>
+    <row r="575" ht="13.5" customHeight="1"/>
+    <row r="576" ht="13.5" customHeight="1"/>
+    <row r="577" ht="13.5" customHeight="1"/>
+    <row r="578" ht="13.5" customHeight="1"/>
+    <row r="579" ht="13.5" customHeight="1"/>
+    <row r="580" ht="13.5" customHeight="1"/>
+    <row r="581" ht="13.5" customHeight="1"/>
+    <row r="582" ht="13.5" customHeight="1"/>
+    <row r="583" ht="13.5" customHeight="1"/>
+    <row r="584" ht="13.5" customHeight="1"/>
+    <row r="585" ht="13.5" customHeight="1"/>
+    <row r="586" ht="13.5" customHeight="1"/>
+    <row r="587" ht="13.5" customHeight="1"/>
+    <row r="588" ht="13.5" customHeight="1"/>
+    <row r="589" ht="13.5" customHeight="1"/>
+    <row r="590" ht="13.5" customHeight="1"/>
+    <row r="591" ht="13.5" customHeight="1"/>
+    <row r="592" ht="13.5" customHeight="1"/>
+    <row r="593" ht="13.5" customHeight="1"/>
+    <row r="594" ht="13.5" customHeight="1"/>
+    <row r="595" ht="13.5" customHeight="1"/>
+    <row r="596" ht="13.5" customHeight="1"/>
+    <row r="597" ht="13.5" customHeight="1"/>
+    <row r="598" ht="13.5" customHeight="1"/>
+    <row r="599" ht="13.5" customHeight="1"/>
+    <row r="600" ht="13.5" customHeight="1"/>
+    <row r="601" ht="13.5" customHeight="1"/>
+    <row r="602" ht="13.5" customHeight="1"/>
+    <row r="603" ht="13.5" customHeight="1"/>
+    <row r="604" ht="13.5" customHeight="1"/>
+    <row r="605" ht="13.5" customHeight="1"/>
+    <row r="606" ht="13.5" customHeight="1"/>
+    <row r="607" ht="13.5" customHeight="1"/>
+    <row r="608" ht="13.5" customHeight="1"/>
+    <row r="609" ht="13.5" customHeight="1"/>
+    <row r="610" ht="13.5" customHeight="1"/>
+    <row r="611" ht="13.5" customHeight="1"/>
+    <row r="612" ht="13.5" customHeight="1"/>
+    <row r="613" ht="13.5" customHeight="1"/>
+    <row r="614" ht="13.5" customHeight="1"/>
+    <row r="615" ht="13.5" customHeight="1"/>
+    <row r="616" ht="13.5" customHeight="1"/>
+    <row r="617" ht="13.5" customHeight="1"/>
+    <row r="618" ht="13.5" customHeight="1"/>
+    <row r="619" ht="13.5" customHeight="1"/>
+    <row r="620" ht="13.5" customHeight="1"/>
+    <row r="621" ht="13.5" customHeight="1"/>
+    <row r="622" ht="13.5" customHeight="1"/>
+    <row r="623" ht="13.5" customHeight="1"/>
+    <row r="624" ht="13.5" customHeight="1"/>
+    <row r="625" ht="13.5" customHeight="1"/>
+    <row r="626" ht="13.5" customHeight="1"/>
+    <row r="627" ht="13.5" customHeight="1"/>
+    <row r="628" ht="13.5" customHeight="1"/>
+    <row r="629" ht="13.5" customHeight="1"/>
+    <row r="630" ht="13.5" customHeight="1"/>
+    <row r="631" ht="13.5" customHeight="1"/>
+    <row r="632" ht="13.5" customHeight="1"/>
+    <row r="633" ht="13.5" customHeight="1"/>
+    <row r="634" ht="13.5" customHeight="1"/>
+    <row r="635" ht="13.5" customHeight="1"/>
+    <row r="636" ht="13.5" customHeight="1"/>
+    <row r="637" ht="13.5" customHeight="1"/>
+    <row r="638" ht="13.5" customHeight="1"/>
+    <row r="639" ht="13.5" customHeight="1"/>
+    <row r="640" ht="13.5" customHeight="1"/>
+    <row r="641" ht="13.5" customHeight="1"/>
+    <row r="642" ht="13.5" customHeight="1"/>
+    <row r="643" ht="13.5" customHeight="1"/>
+    <row r="644" ht="13.5" customHeight="1"/>
+    <row r="645" ht="13.5" customHeight="1"/>
+    <row r="646" ht="13.5" customHeight="1"/>
+    <row r="647" ht="13.5" customHeight="1"/>
+    <row r="648" ht="13.5" customHeight="1"/>
+    <row r="649" ht="13.5" customHeight="1"/>
+    <row r="650" ht="13.5" customHeight="1"/>
+    <row r="651" ht="13.5" customHeight="1"/>
+    <row r="652" ht="13.5" customHeight="1"/>
+    <row r="653" ht="13.5" customHeight="1"/>
+    <row r="654" ht="13.5" customHeight="1"/>
+    <row r="655" ht="13.5" customHeight="1"/>
+    <row r="656" ht="13.5" customHeight="1"/>
+    <row r="657" ht="13.5" customHeight="1"/>
+    <row r="658" ht="13.5" customHeight="1"/>
+    <row r="659" ht="13.5" customHeight="1"/>
+    <row r="660" ht="13.5" customHeight="1"/>
+    <row r="661" ht="13.5" customHeight="1"/>
+    <row r="662" ht="13.5" customHeight="1"/>
+    <row r="663" ht="13.5" customHeight="1"/>
+    <row r="664" ht="13.5" customHeight="1"/>
+    <row r="665" ht="13.5" customHeight="1"/>
+    <row r="666" ht="13.5" customHeight="1"/>
+    <row r="667" ht="13.5" customHeight="1"/>
+    <row r="668" ht="13.5" customHeight="1"/>
+    <row r="669" ht="13.5" customHeight="1"/>
+    <row r="670" ht="13.5" customHeight="1"/>
+    <row r="671" ht="13.5" customHeight="1"/>
+    <row r="672" ht="13.5" customHeight="1"/>
+    <row r="673" ht="13.5" customHeight="1"/>
+    <row r="674" ht="13.5" customHeight="1"/>
+    <row r="675" ht="13.5" customHeight="1"/>
+    <row r="676" ht="13.5" customHeight="1"/>
+    <row r="677" ht="13.5" customHeight="1"/>
+    <row r="678" ht="13.5" customHeight="1"/>
+    <row r="679" ht="13.5" customHeight="1"/>
+    <row r="680" ht="13.5" customHeight="1"/>
+    <row r="681" ht="13.5" customHeight="1"/>
+    <row r="682" ht="13.5" customHeight="1"/>
+    <row r="683" ht="13.5" customHeight="1"/>
+    <row r="684" ht="13.5" customHeight="1"/>
+    <row r="685" ht="13.5" customHeight="1"/>
+    <row r="686" ht="13.5" customHeight="1"/>
+    <row r="687" ht="13.5" customHeight="1"/>
+    <row r="688" ht="13.5" customHeight="1"/>
+    <row r="689" ht="13.5" customHeight="1"/>
+    <row r="690" ht="13.5" customHeight="1"/>
+    <row r="691" ht="13.5" customHeight="1"/>
+    <row r="692" ht="13.5" customHeight="1"/>
+    <row r="693" ht="13.5" customHeight="1"/>
+    <row r="694" ht="13.5" customHeight="1"/>
+    <row r="695" ht="13.5" customHeight="1"/>
+    <row r="696" ht="13.5" customHeight="1"/>
+    <row r="697" ht="13.5" customHeight="1"/>
+    <row r="698" ht="13.5" customHeight="1"/>
+    <row r="699" ht="13.5" customHeight="1"/>
+    <row r="700" ht="13.5" customHeight="1"/>
+    <row r="701" ht="13.5" customHeight="1"/>
+    <row r="702" ht="13.5" customHeight="1"/>
+    <row r="703" ht="13.5" customHeight="1"/>
+    <row r="704" ht="13.5" customHeight="1"/>
+    <row r="705" ht="13.5" customHeight="1"/>
+    <row r="706" ht="13.5" customHeight="1"/>
+    <row r="707" ht="13.5" customHeight="1"/>
+    <row r="708" ht="13.5" customHeight="1"/>
+    <row r="709" ht="13.5" customHeight="1"/>
+    <row r="710" ht="13.5" customHeight="1"/>
+    <row r="711" ht="13.5" customHeight="1"/>
+    <row r="712" ht="13.5" customHeight="1"/>
+    <row r="713" ht="13.5" customHeight="1"/>
+    <row r="714" ht="13.5" customHeight="1"/>
+    <row r="715" ht="13.5" customHeight="1"/>
+    <row r="716" ht="13.5" customHeight="1"/>
+    <row r="717" ht="13.5" customHeight="1"/>
+    <row r="718" ht="13.5" customHeight="1"/>
+    <row r="719" ht="13.5" customHeight="1"/>
+    <row r="720" ht="13.5" customHeight="1"/>
+    <row r="721" ht="13.5" customHeight="1"/>
+    <row r="722" ht="13.5" customHeight="1"/>
+    <row r="723" ht="13.5" customHeight="1"/>
+    <row r="724" ht="13.5" customHeight="1"/>
+    <row r="725" ht="13.5" customHeight="1"/>
+    <row r="726" ht="13.5" customHeight="1"/>
+    <row r="727" ht="13.5" customHeight="1"/>
+    <row r="728" ht="13.5" customHeight="1"/>
+    <row r="729" ht="13.5" customHeight="1"/>
+    <row r="730" ht="13.5" customHeight="1"/>
+    <row r="731" ht="13.5" customHeight="1"/>
+    <row r="732" ht="13.5" customHeight="1"/>
+    <row r="733" ht="13.5" customHeight="1"/>
+    <row r="734" ht="13.5" customHeight="1"/>
+    <row r="735" ht="13.5" customHeight="1"/>
+    <row r="736" ht="13.5" customHeight="1"/>
+    <row r="737" ht="13.5" customHeight="1"/>
+    <row r="738" ht="13.5" customHeight="1"/>
+    <row r="739" ht="13.5" customHeight="1"/>
+    <row r="740" ht="13.5" customHeight="1"/>
+    <row r="741" ht="13.5" customHeight="1"/>
+    <row r="742" ht="13.5" customHeight="1"/>
+    <row r="743" ht="13.5" customHeight="1"/>
+    <row r="744" ht="13.5" customHeight="1"/>
+    <row r="745" ht="13.5" customHeight="1"/>
+    <row r="746" ht="13.5" customHeight="1"/>
+    <row r="747" ht="13.5" customHeight="1"/>
+    <row r="748" ht="13.5" customHeight="1"/>
+    <row r="749" ht="13.5" customHeight="1"/>
+    <row r="750" ht="13.5" customHeight="1"/>
+    <row r="751" ht="13.5" customHeight="1"/>
+    <row r="752" ht="13.5" customHeight="1"/>
+    <row r="753" ht="13.5" customHeight="1"/>
+    <row r="754" ht="13.5" customHeight="1"/>
+    <row r="755" ht="13.5" customHeight="1"/>
+    <row r="756" ht="13.5" customHeight="1"/>
+    <row r="757" ht="13.5" customHeight="1"/>
+    <row r="758" ht="13.5" customHeight="1"/>
+    <row r="759" ht="13.5" customHeight="1"/>
+    <row r="760" ht="13.5" customHeight="1"/>
+    <row r="761" ht="13.5" customHeight="1"/>
+    <row r="762" ht="13.5" customHeight="1"/>
+    <row r="763" ht="13.5" customHeight="1"/>
+    <row r="764" ht="13.5" customHeight="1"/>
+    <row r="765" ht="13.5" customHeight="1"/>
+    <row r="766" ht="13.5" customHeight="1"/>
+    <row r="767" ht="13.5" customHeight="1"/>
+    <row r="768" ht="13.5" customHeight="1"/>
+    <row r="769" ht="13.5" customHeight="1"/>
+    <row r="770" ht="13.5" customHeight="1"/>
+    <row r="771" ht="13.5" customHeight="1"/>
+    <row r="772" ht="13.5" customHeight="1"/>
+    <row r="773" ht="13.5" customHeight="1"/>
+    <row r="774" ht="13.5" customHeight="1"/>
+    <row r="775" ht="13.5" customHeight="1"/>
+    <row r="776" ht="13.5" customHeight="1"/>
+    <row r="777" ht="13.5" customHeight="1"/>
+    <row r="778" ht="13.5" customHeight="1"/>
+    <row r="779" ht="13.5" customHeight="1"/>
+    <row r="780" ht="13.5" customHeight="1"/>
+    <row r="781" ht="13.5" customHeight="1"/>
+    <row r="782" ht="13.5" customHeight="1"/>
+    <row r="783" ht="13.5" customHeight="1"/>
+    <row r="784" ht="13.5" customHeight="1"/>
+    <row r="785" ht="13.5" customHeight="1"/>
+    <row r="786" ht="13.5" customHeight="1"/>
+    <row r="787" ht="13.5" customHeight="1"/>
+    <row r="788" ht="13.5" customHeight="1"/>
+    <row r="789" ht="13.5" customHeight="1"/>
+    <row r="790" ht="13.5" customHeight="1"/>
+    <row r="791" ht="13.5" customHeight="1"/>
+    <row r="792" ht="13.5" customHeight="1"/>
+    <row r="793" ht="13.5" customHeight="1"/>
+    <row r="794" ht="13.5" customHeight="1"/>
+    <row r="795" ht="13.5" customHeight="1"/>
+    <row r="796" ht="13.5" customHeight="1"/>
+    <row r="797" ht="13.5" customHeight="1"/>
+    <row r="798" ht="13.5" customHeight="1"/>
+    <row r="799" ht="13.5" customHeight="1"/>
+    <row r="800" ht="13.5" customHeight="1"/>
+    <row r="801" ht="13.5" customHeight="1"/>
+    <row r="802" ht="13.5" customHeight="1"/>
+    <row r="803" ht="13.5" customHeight="1"/>
+    <row r="804" ht="13.5" customHeight="1"/>
+    <row r="805" ht="13.5" customHeight="1"/>
+    <row r="806" ht="13.5" customHeight="1"/>
+    <row r="807" ht="13.5" customHeight="1"/>
+    <row r="808" ht="13.5" customHeight="1"/>
+    <row r="809" ht="13.5" customHeight="1"/>
+    <row r="810" ht="13.5" customHeight="1"/>
+    <row r="811" ht="13.5" customHeight="1"/>
+    <row r="812" ht="13.5" customHeight="1"/>
+    <row r="813" ht="13.5" customHeight="1"/>
+    <row r="814" ht="13.5" customHeight="1"/>
+    <row r="815" ht="13.5" customHeight="1"/>
+    <row r="816" ht="13.5" customHeight="1"/>
+    <row r="817" ht="13.5" customHeight="1"/>
+    <row r="818" ht="13.5" customHeight="1"/>
+    <row r="819" ht="13.5" customHeight="1"/>
+    <row r="820" ht="13.5" customHeight="1"/>
+    <row r="821" ht="13.5" customHeight="1"/>
+    <row r="822" ht="13.5" customHeight="1"/>
+    <row r="823" ht="13.5" customHeight="1"/>
+    <row r="824" ht="13.5" customHeight="1"/>
+    <row r="825" ht="13.5" customHeight="1"/>
+    <row r="826" ht="13.5" customHeight="1"/>
+    <row r="827" ht="13.5" customHeight="1"/>
+    <row r="828" ht="13.5" customHeight="1"/>
+    <row r="829" ht="13.5" customHeight="1"/>
+    <row r="830" ht="13.5" customHeight="1"/>
+    <row r="831" ht="13.5" customHeight="1"/>
+    <row r="832" ht="13.5" customHeight="1"/>
+    <row r="833" ht="13.5" customHeight="1"/>
+    <row r="834" ht="13.5" customHeight="1"/>
+    <row r="835" ht="13.5" customHeight="1"/>
+    <row r="836" ht="13.5" customHeight="1"/>
+    <row r="837" ht="13.5" customHeight="1"/>
+    <row r="838" ht="13.5" customHeight="1"/>
+    <row r="839" ht="13.5" customHeight="1"/>
+    <row r="840" ht="13.5" customHeight="1"/>
+    <row r="841" ht="13.5" customHeight="1"/>
+    <row r="842" ht="13.5" customHeight="1"/>
+    <row r="843" ht="13.5" customHeight="1"/>
+    <row r="844" ht="13.5" customHeight="1"/>
+    <row r="845" ht="13.5" customHeight="1"/>
+    <row r="846" ht="13.5" customHeight="1"/>
+    <row r="847" ht="13.5" customHeight="1"/>
+    <row r="848" ht="13.5" customHeight="1"/>
+    <row r="849" ht="13.5" customHeight="1"/>
+    <row r="850" ht="13.5" customHeight="1"/>
+    <row r="851" ht="13.5" customHeight="1"/>
+    <row r="852" ht="13.5" customHeight="1"/>
+    <row r="853" ht="13.5" customHeight="1"/>
+    <row r="854" ht="13.5" customHeight="1"/>
+    <row r="855" ht="13.5" customHeight="1"/>
+    <row r="856" ht="13.5" customHeight="1"/>
+    <row r="857" ht="13.5" customHeight="1"/>
+    <row r="858" ht="13.5" customHeight="1"/>
+    <row r="859" ht="13.5" customHeight="1"/>
+    <row r="860" ht="13.5" customHeight="1"/>
+    <row r="861" ht="13.5" customHeight="1"/>
+    <row r="862" ht="13.5" customHeight="1"/>
+    <row r="863" ht="13.5" customHeight="1"/>
+    <row r="864" ht="13.5" customHeight="1"/>
+    <row r="865" ht="13.5" customHeight="1"/>
+    <row r="866" ht="13.5" customHeight="1"/>
+    <row r="867" ht="13.5" customHeight="1"/>
+    <row r="868" ht="13.5" customHeight="1"/>
+    <row r="869" ht="13.5" customHeight="1"/>
+    <row r="870" ht="13.5" customHeight="1"/>
+    <row r="871" ht="13.5" customHeight="1"/>
+    <row r="872" ht="13.5" customHeight="1"/>
+    <row r="873" ht="13.5" customHeight="1"/>
+    <row r="874" ht="13.5" customHeight="1"/>
+    <row r="875" ht="13.5" customHeight="1"/>
+    <row r="876" ht="13.5" customHeight="1"/>
+    <row r="877" ht="13.5" customHeight="1"/>
+    <row r="878" ht="13.5" customHeight="1"/>
+    <row r="879" ht="13.5" customHeight="1"/>
+    <row r="880" ht="13.5" customHeight="1"/>
+    <row r="881" ht="13.5" customHeight="1"/>
+    <row r="882" ht="13.5" customHeight="1"/>
+    <row r="883" ht="13.5" customHeight="1"/>
+    <row r="884" ht="13.5" customHeight="1"/>
+    <row r="885" ht="13.5" customHeight="1"/>
+    <row r="886" ht="13.5" customHeight="1"/>
+    <row r="887" ht="13.5" customHeight="1"/>
+    <row r="888" ht="13.5" customHeight="1"/>
+    <row r="889" ht="13.5" customHeight="1"/>
+    <row r="890" ht="13.5" customHeight="1"/>
+    <row r="891" ht="13.5" customHeight="1"/>
+    <row r="892" ht="13.5" customHeight="1"/>
+    <row r="893" ht="13.5" customHeight="1"/>
+    <row r="894" ht="13.5" customHeight="1"/>
+    <row r="895" ht="13.5" customHeight="1"/>
+    <row r="896" ht="13.5" customHeight="1"/>
+    <row r="897" ht="13.5" customHeight="1"/>
+    <row r="898" ht="13.5" customHeight="1"/>
+    <row r="899" ht="13.5" customHeight="1"/>
+    <row r="900" ht="13.5" customHeight="1"/>
+    <row r="901" ht="13.5" customHeight="1"/>
+    <row r="902" ht="13.5" customHeight="1"/>
+    <row r="903" ht="13.5" customHeight="1"/>
+    <row r="904" ht="13.5" customHeight="1"/>
+    <row r="905" ht="13.5" customHeight="1"/>
+    <row r="906" ht="13.5" customHeight="1"/>
+    <row r="907" ht="13.5" customHeight="1"/>
+    <row r="908" ht="13.5" customHeight="1"/>
+    <row r="909" ht="13.5" customHeight="1"/>
+    <row r="910" ht="13.5" customHeight="1"/>
+    <row r="911" ht="13.5" customHeight="1"/>
+    <row r="912" ht="13.5" customHeight="1"/>
+    <row r="913" ht="13.5" customHeight="1"/>
+    <row r="914" ht="13.5" customHeight="1"/>
+    <row r="915" ht="13.5" customHeight="1"/>
+    <row r="916" ht="13.5" customHeight="1"/>
+    <row r="917" ht="13.5" customHeight="1"/>
+    <row r="918" ht="13.5" customHeight="1"/>
+    <row r="919" ht="13.5" customHeight="1"/>
+    <row r="920" ht="13.5" customHeight="1"/>
+    <row r="921" ht="13.5" customHeight="1"/>
+    <row r="922" ht="13.5" customHeight="1"/>
+    <row r="923" ht="13.5" customHeight="1"/>
+    <row r="924" ht="13.5" customHeight="1"/>
+    <row r="925" ht="13.5" customHeight="1"/>
+    <row r="926" ht="13.5" customHeight="1"/>
+    <row r="927" ht="13.5" customHeight="1"/>
+    <row r="928" ht="13.5" customHeight="1"/>
+    <row r="929" ht="13.5" customHeight="1"/>
+    <row r="930" ht="13.5" customHeight="1"/>
+    <row r="931" ht="13.5" customHeight="1"/>
+    <row r="932" ht="13.5" customHeight="1"/>
+    <row r="933" ht="13.5" customHeight="1"/>
+    <row r="934" ht="13.5" customHeight="1"/>
+    <row r="935" ht="13.5" customHeight="1"/>
+    <row r="936" ht="13.5" customHeight="1"/>
+    <row r="937" ht="13.5" customHeight="1"/>
+    <row r="938" ht="13.5" customHeight="1"/>
+    <row r="939" ht="13.5" customHeight="1"/>
+    <row r="940" ht="13.5" customHeight="1"/>
+    <row r="941" ht="13.5" customHeight="1"/>
+    <row r="942" ht="13.5" customHeight="1"/>
+    <row r="943" ht="13.5" customHeight="1"/>
+    <row r="944" ht="13.5" customHeight="1"/>
+    <row r="945" ht="13.5" customHeight="1"/>
+    <row r="946" ht="13.5" customHeight="1"/>
+    <row r="947" ht="13.5" customHeight="1"/>
+    <row r="948" ht="13.5" customHeight="1"/>
+    <row r="949" ht="13.5" customHeight="1"/>
+    <row r="950" ht="13.5" customHeight="1"/>
+    <row r="951" ht="13.5" customHeight="1"/>
+    <row r="952" ht="13.5" customHeight="1"/>
+    <row r="953" ht="13.5" customHeight="1"/>
+    <row r="954" ht="13.5" customHeight="1"/>
+    <row r="955" ht="13.5" customHeight="1"/>
+    <row r="956" ht="13.5" customHeight="1"/>
+    <row r="957" ht="13.5" customHeight="1"/>
+    <row r="958" ht="13.5" customHeight="1"/>
+    <row r="959" ht="13.5" customHeight="1"/>
+    <row r="960" ht="13.5" customHeight="1"/>
+    <row r="961" ht="13.5" customHeight="1"/>
+    <row r="962" ht="13.5" customHeight="1"/>
+    <row r="963" ht="13.5" customHeight="1"/>
+    <row r="964" ht="13.5" customHeight="1"/>
+    <row r="965" ht="13.5" customHeight="1"/>
+    <row r="966" ht="13.5" customHeight="1"/>
+    <row r="967" ht="13.5" customHeight="1"/>
+    <row r="968" ht="13.5" customHeight="1"/>
+    <row r="969" ht="13.5" customHeight="1"/>
+    <row r="970" ht="13.5" customHeight="1"/>
+    <row r="971" ht="13.5" customHeight="1"/>
+    <row r="972" ht="13.5" customHeight="1"/>
+    <row r="973" ht="13.5" customHeight="1"/>
+    <row r="974" ht="13.5" customHeight="1"/>
+    <row r="975" ht="13.5" customHeight="1"/>
+    <row r="976" ht="13.5" customHeight="1"/>
+    <row r="977" ht="13.5" customHeight="1"/>
+    <row r="978" ht="13.5" customHeight="1"/>
+    <row r="979" ht="13.5" customHeight="1"/>
+    <row r="980" ht="13.5" customHeight="1"/>
+    <row r="981" ht="13.5" customHeight="1"/>
+    <row r="982" ht="13.5" customHeight="1"/>
+    <row r="983" ht="13.5" customHeight="1"/>
+    <row r="984" ht="13.5" customHeight="1"/>
+    <row r="985" ht="13.5" customHeight="1"/>
+    <row r="986" ht="13.5" customHeight="1"/>
+    <row r="987" ht="13.5" customHeight="1"/>
+    <row r="988" ht="13.5" customHeight="1"/>
+    <row r="989" ht="13.5" customHeight="1"/>
+    <row r="990" ht="13.5" customHeight="1"/>
+    <row r="991" ht="13.5" customHeight="1"/>
+    <row r="992" ht="13.5" customHeight="1"/>
+    <row r="993" ht="13.5" customHeight="1"/>
+    <row r="994" ht="13.5" customHeight="1"/>
+    <row r="995" ht="13.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48.5" customWidth="1" min="1" max="1"/>
+    <col width="12.625" customWidth="1" min="2" max="2"/>
+    <col width="11.375" customWidth="1" min="6" max="6"/>
+    <col width="8.875" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>Chỉ tiêu</t>
+        </is>
+      </c>
+      <c r="B1" s="29" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C1" s="29" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D1" s="29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E1" s="29" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F1" s="29" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Doanh thu kế hoạch</t>
+        </is>
+      </c>
+      <c r="B2" s="34" t="n">
+        <v>27000000</v>
+      </c>
+      <c r="C2" s="34" t="n">
+        <v>34000000</v>
+      </c>
+      <c r="D2" s="34" t="n">
+        <v>37300000</v>
+      </c>
+      <c r="E2" s="34" t="n">
+        <v>48100000</v>
+      </c>
+      <c r="F2" s="34" t="n">
+        <v>59500000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>Doanh thu thuần về bán hàng và cung cấp dịch vụ</t>
+        </is>
+      </c>
+      <c r="B3" s="34">
+        <f>chi_so_tai_chinh!F43/1000000</f>
+        <v/>
+      </c>
+      <c r="C3" s="34">
+        <f>chi_so_tai_chinh!G43/1000000</f>
+        <v/>
+      </c>
+      <c r="D3" s="34">
+        <f>chi_so_tai_chinh!H43/1000000</f>
+        <v/>
+      </c>
+      <c r="E3" s="34">
+        <f>chi_so_tai_chinh!I43/1000000</f>
+        <v/>
+      </c>
+      <c r="F3" s="29" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>%thực hiện</t>
+        </is>
+      </c>
+      <c r="B4" s="38">
+        <f>B3/B2</f>
+        <v/>
+      </c>
+      <c r="C4" s="38">
+        <f>C3/C2</f>
+        <v/>
+      </c>
+      <c r="D4" s="38">
+        <f>D3/D2</f>
+        <v/>
+      </c>
+      <c r="E4" s="38">
+        <f>E3/E2</f>
+        <v/>
+      </c>
+      <c r="F4" s="29" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>Lợi nhuận trước thuế kế hoạch</t>
+        </is>
+      </c>
+      <c r="B5" s="34" t="n">
+        <v>720000</v>
+      </c>
+      <c r="C5" s="34" t="n">
+        <v>240000</v>
+      </c>
+      <c r="D5" s="34" t="n">
+        <v>125000</v>
+      </c>
+      <c r="E5" s="34" t="n">
+        <v>900000</v>
+      </c>
+      <c r="F5" s="34" t="n">
+        <v>1550000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>Lợi nhuận trước thuế thu nhập doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="B6" s="34">
+        <f>chi_so_tai_chinh!F50/1000000</f>
+        <v/>
+      </c>
+      <c r="C6" s="34">
+        <f>chi_so_tai_chinh!G50/1000000</f>
+        <v/>
+      </c>
+      <c r="D6" s="34">
+        <f>chi_so_tai_chinh!H50/1000000</f>
+        <v/>
+      </c>
+      <c r="E6" s="34">
+        <f>chi_so_tai_chinh!I50/1000000</f>
+        <v/>
+      </c>
+      <c r="F6" s="29" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>%thực hiện</t>
+        </is>
+      </c>
+      <c r="B7" s="38">
+        <f>B6/B5</f>
+        <v/>
+      </c>
+      <c r="C7" s="38">
+        <f>C6/C5</f>
+        <v/>
+      </c>
+      <c r="D7" s="38">
+        <f>D6/D5</f>
+        <v/>
+      </c>
+      <c r="E7" s="38">
+        <f>E6/E5</f>
+        <v/>
+      </c>
+      <c r="F7" s="29" t="n"/>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>Trung vị %thực hiện DT</t>
+        </is>
+      </c>
+      <c r="B9" s="38">
+        <f>MEDIAN(B4:D4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Trung vị %thực hiện LNST</t>
+        </is>
+      </c>
+      <c r="B10" s="38">
+        <f>MEDIAN(B7:D7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành DT trên 95%</t>
+        </is>
+      </c>
+      <c r="B12" s="38">
+        <f>COUNTIF(B4:E4,"&gt;=95%")/COUNT(B4:E4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành LNST trên 95%</t>
+        </is>
+      </c>
+      <c r="B13" s="38">
+        <f>COUNTIF(B7:F7,"&gt;=95%")/COUNT(B7:F7)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B9:B10">
+    <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="3">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:E4 B7:E7">
+    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" dxfId="3">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/financials/FRT/FRT.xlsx
+++ b/financials/FRT/FRT.xlsx
@@ -832,16 +832,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0</v>
+        <v>4140042971</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0</v>
+        <v>494643176666</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0</v>
+        <v>788158684912</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0</v>
+        <v>1820500000000</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>0</v>
@@ -862,10 +862,18 @@
           <t>Đầu tư ngắn hạn</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
+      <c r="B7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F7" s="4" t="n">
         <v>0</v>
       </c>
@@ -1227,16 +1235,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>0</v>
+        <v>149775001626</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0</v>
+        <v>247334664854</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0</v>
+        <v>145377223905</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0</v>
+        <v>380498040707</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>0</v>
@@ -1350,10 +1358,18 @@
           <t>Tài sản lưu động khác</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr"/>
-      <c r="C23" s="4" t="inlineStr"/>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr"/>
+      <c r="B23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F23" s="4" t="n">
         <v>0</v>
       </c>
@@ -2245,13 +2261,13 @@
         <v>0</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>6279401759</v>
+        <v>0</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>0</v>
+        <v>2984578546</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0</v>
+        <v>868124774</v>
       </c>
       <c r="F52" s="4" t="n">
         <v>0</v>
@@ -2892,10 +2908,18 @@
           <t>Thuế thu nhập hoãn lại</t>
         </is>
       </c>
-      <c r="B73" s="4" t="inlineStr"/>
-      <c r="C73" s="4" t="inlineStr"/>
-      <c r="D73" s="4" t="inlineStr"/>
-      <c r="E73" s="4" t="inlineStr"/>
+      <c r="B73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>6279401759</v>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F73" s="4" t="n">
         <v>0</v>
       </c>
@@ -3629,16 +3653,16 @@
         </is>
       </c>
       <c r="B97" s="4" t="n">
-        <v>0</v>
+        <v>4140042971</v>
       </c>
       <c r="C97" s="4" t="n">
-        <v>0</v>
+        <v>494643176666</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>0</v>
+        <v>788158684912</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>0</v>
+        <v>1820500000000</v>
       </c>
       <c r="F97" s="4" t="n">
         <v>0</v>
@@ -3907,10 +3931,18 @@
           <t>Đầu tư nắm giữ đến ngày đáo hạn</t>
         </is>
       </c>
-      <c r="B106" s="4" t="inlineStr"/>
-      <c r="C106" s="4" t="inlineStr"/>
-      <c r="D106" s="4" t="inlineStr"/>
-      <c r="E106" s="4" t="inlineStr"/>
+      <c r="B106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F106" s="4" t="n">
         <v>0</v>
       </c>
@@ -4178,10 +4210,18 @@
           <t>Cổ phiếu ưu đãi</t>
         </is>
       </c>
-      <c r="B115" s="4" t="inlineStr"/>
-      <c r="C115" s="4" t="inlineStr"/>
-      <c r="D115" s="4" t="inlineStr"/>
-      <c r="E115" s="4" t="inlineStr"/>
+      <c r="B115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F115" s="4" t="n">
         <v>0</v>
       </c>
